--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,6 +643,59 @@
       </c>
       <c r="Q2" t="n">
         <v>0.004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104838</v>
+      </c>
+      <c r="C3" t="n">
+        <v>80620</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22876</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20038</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2838</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1270</v>
+      </c>
+      <c r="H3" t="n">
+        <v>72</v>
+      </c>
+      <c r="I3" t="n">
+        <v>123</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.368</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.359</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.005</v>
       </c>
     </row>
   </sheetData>
@@ -656,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,12 +745,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Mazar</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -731,16 +784,48 @@
         <v>3724</v>
       </c>
       <c r="G2" t="n">
+        <v>2301</v>
+      </c>
+      <c r="H2" t="n">
         <v>2768</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2301</v>
       </c>
       <c r="I2" t="n">
         <v>2003</v>
       </c>
       <c r="J2" t="n">
         <v>239</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B3" t="n">
+        <v>23420</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20069</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16681</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8424</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3644</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2554</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2477</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1820</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1531</v>
       </c>
     </row>
   </sheetData>
@@ -754,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2047,6 +2132,1254 @@
         <v>4329.400000000001</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2983.49</v>
+      </c>
+      <c r="C50" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>956.03</v>
+      </c>
+      <c r="F50" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4005.83</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3990.12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46293.02083333334</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2896.35</v>
+      </c>
+      <c r="C51" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>935.74</v>
+      </c>
+      <c r="F51" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3895.39</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3879.480000000001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46293.04166666666</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2805.38</v>
+      </c>
+      <c r="C52" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="D52" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="E52" t="n">
+        <v>933.62</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3794.67</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3794.67</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46293.0625</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2714.15</v>
+      </c>
+      <c r="C53" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>939.65</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3707.37</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3701.53</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46293.08333333334</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2644.53</v>
+      </c>
+      <c r="C54" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>946.14</v>
+      </c>
+      <c r="F54" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3656.11</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3637.56</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46293.10416666666</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2585.34</v>
+      </c>
+      <c r="C55" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>948.75</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3591.42</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3583.68</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46293.125</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2554.69</v>
+      </c>
+      <c r="C56" t="n">
+        <v>60.33</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>947.86</v>
+      </c>
+      <c r="F56" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3576.04</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3562.88</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46293.14583333334</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2487.63</v>
+      </c>
+      <c r="C57" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E57" t="n">
+        <v>944.6799999999999</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3488.05</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3488.05</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46293.16666666666</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2521.17</v>
+      </c>
+      <c r="C58" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>932.4400000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3500.54</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3497.12</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46293.1875</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2519.56</v>
+      </c>
+      <c r="C59" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="D59" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="E59" t="n">
+        <v>942.5599999999999</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3514.03</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3514.03</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46293.20833333334</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2564.03</v>
+      </c>
+      <c r="C60" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E60" t="n">
+        <v>941.08</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3549.93</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3549.93</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46293.22916666666</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2650.21</v>
+      </c>
+      <c r="C61" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="D61" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="E61" t="n">
+        <v>954.0599999999999</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3661.86</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3661.86</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46293.25</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2735.93</v>
+      </c>
+      <c r="C62" t="n">
+        <v>47.41</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>949.92</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3741.26</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3733.26</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46293.27083333334</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2512.24</v>
+      </c>
+      <c r="C63" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>950.75</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3515.91</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3511.84</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46293.29166666666</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2474.44</v>
+      </c>
+      <c r="C64" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>952.0700000000001</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3483.27</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3476.55</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46293.3125</v>
+      </c>
+      <c r="B65" t="n">
+        <v>2688.96</v>
+      </c>
+      <c r="C65" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>949.03</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3683.38</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3683.38</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46293.33333333334</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2859.45</v>
+      </c>
+      <c r="C66" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>950.13</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3863.12</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3859.170000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46293.35416666666</v>
+      </c>
+      <c r="B67" t="n">
+        <v>3079.11</v>
+      </c>
+      <c r="C67" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="D67" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="E67" t="n">
+        <v>945.88</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4082.400000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4082.400000000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46293.375</v>
+      </c>
+      <c r="B68" t="n">
+        <v>3236.25</v>
+      </c>
+      <c r="C68" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="D68" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="E68" t="n">
+        <v>944.1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4256.95</v>
+      </c>
+      <c r="H68" t="n">
+        <v>4256.95</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46293.39583333334</v>
+      </c>
+      <c r="B69" t="n">
+        <v>3409.6</v>
+      </c>
+      <c r="C69" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>945.3200000000001</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4398.32</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4393.78</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46293.41666666666</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3508.5</v>
+      </c>
+      <c r="C70" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>974.9299999999999</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4522.61</v>
+      </c>
+      <c r="H70" t="n">
+        <v>4522.61</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46293.4375</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3596.6</v>
+      </c>
+      <c r="C71" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="D71" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="E71" t="n">
+        <v>966.7</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4616.88</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4616.88</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46293.45833333334</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3718.03</v>
+      </c>
+      <c r="C72" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>962.59</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4721.68</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4721.68</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46293.47916666666</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3753.94</v>
+      </c>
+      <c r="C73" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>980.97</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4794.55</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4794.55</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46293.5</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3766.64</v>
+      </c>
+      <c r="C74" t="n">
+        <v>90.66</v>
+      </c>
+      <c r="D74" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E74" t="n">
+        <v>972.22</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4845.42</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4845.42</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46293.52083333334</v>
+      </c>
+      <c r="B75" t="n">
+        <v>3768.13</v>
+      </c>
+      <c r="C75" t="n">
+        <v>97.29000000000001</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>978.41</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4855.62</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4843.83</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46293.54166666666</v>
+      </c>
+      <c r="B76" t="n">
+        <v>3806.06</v>
+      </c>
+      <c r="C76" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>984.47</v>
+      </c>
+      <c r="F76" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4899.01</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4879.08</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B77" t="n">
+        <v>3834</v>
+      </c>
+      <c r="C77" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>984.6799999999999</v>
+      </c>
+      <c r="F77" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4923.679999999999</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4909.36</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46293.58333333334</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3917.35</v>
+      </c>
+      <c r="C78" t="n">
+        <v>93.09</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>983.8099999999999</v>
+      </c>
+      <c r="F78" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5009.84</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4994.25</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46293.60416666666</v>
+      </c>
+      <c r="B79" t="n">
+        <v>4025.02</v>
+      </c>
+      <c r="C79" t="n">
+        <v>84.01000000000001</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>964.33</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5073.36</v>
+      </c>
+      <c r="H79" t="n">
+        <v>5073.36</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46293.625</v>
+      </c>
+      <c r="B80" t="n">
+        <v>4035.4</v>
+      </c>
+      <c r="C80" t="n">
+        <v>90.54000000000001</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>967.39</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5093.330000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>5093.330000000001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46293.64583333334</v>
+      </c>
+      <c r="B81" t="n">
+        <v>4029.62</v>
+      </c>
+      <c r="C81" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>969.85</v>
+      </c>
+      <c r="F81" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5108.280000000001</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5092.97</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46293.66666666666</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3978.12</v>
+      </c>
+      <c r="C82" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>989.3099999999999</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5050.05</v>
+      </c>
+      <c r="H82" t="n">
+        <v>5045.35</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46293.6875</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3946.6</v>
+      </c>
+      <c r="C83" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>990.0700000000001</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5021.249999999999</v>
+      </c>
+      <c r="H83" t="n">
+        <v>5018.06</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46293.70833333334</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3852.77</v>
+      </c>
+      <c r="C84" t="n">
+        <v>73.98</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>991.21</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>4917.96</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4917.96</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46293.72916666666</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3746.24</v>
+      </c>
+      <c r="C85" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1010.93</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4820.849999999999</v>
+      </c>
+      <c r="H85" t="n">
+        <v>4820.849999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46293.75</v>
+      </c>
+      <c r="B86" t="n">
+        <v>3594.44</v>
+      </c>
+      <c r="C86" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>994.91</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4656.46</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4656.46</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46293.77083333334</v>
+      </c>
+      <c r="B87" t="n">
+        <v>4107.94</v>
+      </c>
+      <c r="C87" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1000.32</v>
+      </c>
+      <c r="F87" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="G87" t="n">
+        <v>5180.759999999999</v>
+      </c>
+      <c r="H87" t="n">
+        <v>5165.329999999999</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46293.79166666666</v>
+      </c>
+      <c r="B88" t="n">
+        <v>4245.78</v>
+      </c>
+      <c r="C88" t="n">
+        <v>47</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1005.06</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5300.09</v>
+      </c>
+      <c r="H88" t="n">
+        <v>5297.84</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46293.8125</v>
+      </c>
+      <c r="B89" t="n">
+        <v>4296.99</v>
+      </c>
+      <c r="C89" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1003.7</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>5334.099999999999</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5334.099999999999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46293.83333333334</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4271.67</v>
+      </c>
+      <c r="C90" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1011.49</v>
+      </c>
+      <c r="F90" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5324.38</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5309.28</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46293.85416666666</v>
+      </c>
+      <c r="B91" t="n">
+        <v>4242.08</v>
+      </c>
+      <c r="C91" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1028.94</v>
+      </c>
+      <c r="F91" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5314.52</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5295.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46293.875</v>
+      </c>
+      <c r="B92" t="n">
+        <v>4203.12</v>
+      </c>
+      <c r="C92" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1015.72</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5247.41</v>
+      </c>
+      <c r="H92" t="n">
+        <v>5247.41</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46293.89583333334</v>
+      </c>
+      <c r="B93" t="n">
+        <v>4130.15</v>
+      </c>
+      <c r="C93" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="D93" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1013.35</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>5181.32</v>
+      </c>
+      <c r="H93" t="n">
+        <v>5181.32</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46293.91666666666</v>
+      </c>
+      <c r="B94" t="n">
+        <v>3979.99</v>
+      </c>
+      <c r="C94" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1000.91</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5008.83</v>
+      </c>
+      <c r="H94" t="n">
+        <v>5008.83</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46293.9375</v>
+      </c>
+      <c r="B95" t="n">
+        <v>3846.25</v>
+      </c>
+      <c r="C95" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="D95" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1024.9</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4918.92</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4918.92</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46293.95833333334</v>
+      </c>
+      <c r="B96" t="n">
+        <v>3644.69</v>
+      </c>
+      <c r="C96" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="D96" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1024.17</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4705.27</v>
+      </c>
+      <c r="H96" t="n">
+        <v>4705.27</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46293.97916666666</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3432.94</v>
+      </c>
+      <c r="C97" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1050.71</v>
+      </c>
+      <c r="F97" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4532.389999999999</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4512.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Daily" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Plants" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Half-hourly" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Plants by region" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Half-hourly" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -453,7 +454,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>'Daily': MWh generated that day by source, then the same as mean GW (MWh / 24 / 1000). 'Plants': MWh per large plant. 'Half-hourly': MW.</t>
+          <t>'Daily': MWh generated that day by source, then the same as mean GW (MWh / 24 / 1000). 'Plants': MWh per large plant, one column each. 'Plants by region': the same plant-level MWh reshaped long, with province/region/country columns added. 'Half-hourly': MW.</t>
         </is>
       </c>
     </row>
@@ -480,12 +481,29 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>REGIONS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>CENACE reports no location for any plant - province/region in 'Plants by region' is this script's own mapping (PLANT_LOCATION), looked up by hand: province, then Ecuador's standard Costa/Sierra/Oriente zoning. 'Otras Hidro' is CENACE's own catch-all for every smaller hydro plant not named individually, so it can't be assigned a single location - tagged region 'Nacional (agregado)' instead of guessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CENACE Informacion Operativa (cenace.gob.ec/info-operativa/InformacionOperativa.htm), 'Informacion operativa diaria' tab - the last complete day only, so history starts at the first run and grows daily.</t>
         </is>
@@ -502,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,6 +714,59 @@
       </c>
       <c r="Q3" t="n">
         <v>0.005</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103276</v>
+      </c>
+      <c r="C4" t="n">
+        <v>76881</v>
+      </c>
+      <c r="D4" t="n">
+        <v>25249</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22411</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2838</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1064</v>
+      </c>
+      <c r="H4" t="n">
+        <v>82</v>
+      </c>
+      <c r="I4" t="n">
+        <v>133</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.303</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.203</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.006</v>
       </c>
     </row>
   </sheetData>
@@ -709,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,6 +897,38 @@
       </c>
       <c r="J3" t="n">
         <v>1531</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4" t="n">
+        <v>19992</v>
+      </c>
+      <c r="C4" t="n">
+        <v>19095</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17645</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9735</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3194</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2604</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2491</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1820</v>
+      </c>
+      <c r="J4" t="n">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +942,878 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>plant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>province</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mwh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>24721</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>23420</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>19992</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nacional (agregado)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>16882</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Nacional (agregado)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>20069</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nacional (agregado)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>19095</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>13964</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>16681</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>17645</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sopladora</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>8114</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sopladora</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>8424</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sopladora</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>9735</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Delsitanisagua</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Zamora Chinchipe</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Delsitanisagua</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zamora Chinchipe</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Delsitanisagua</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Zamora Chinchipe</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>306</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3380,6 +4354,1254 @@
         <v>4512.57</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3303.07</v>
+      </c>
+      <c r="C98" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1044.72</v>
+      </c>
+      <c r="F98" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4391.2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>4375.33</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46294.02083333334</v>
+      </c>
+      <c r="B99" t="n">
+        <v>3179.34</v>
+      </c>
+      <c r="C99" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="D99" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1027.02</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>4247.190000000001</v>
+      </c>
+      <c r="H99" t="n">
+        <v>4247.190000000001</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46294.04166666666</v>
+      </c>
+      <c r="B100" t="n">
+        <v>3040.24</v>
+      </c>
+      <c r="C100" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1063.54</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4129.07</v>
+      </c>
+      <c r="H100" t="n">
+        <v>4129.07</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46294.0625</v>
+      </c>
+      <c r="B101" t="n">
+        <v>2906.79</v>
+      </c>
+      <c r="C101" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1076.98</v>
+      </c>
+      <c r="F101" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4029.33</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4010.52</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46294.08333333334</v>
+      </c>
+      <c r="B102" t="n">
+        <v>2823.58</v>
+      </c>
+      <c r="C102" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1084.68</v>
+      </c>
+      <c r="F102" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3959.230000000001</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3936.14</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46294.10416666666</v>
+      </c>
+      <c r="B103" t="n">
+        <v>2764.49</v>
+      </c>
+      <c r="C103" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1068.28</v>
+      </c>
+      <c r="F103" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3914.82</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3864.09</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46294.125</v>
+      </c>
+      <c r="B104" t="n">
+        <v>2764.81</v>
+      </c>
+      <c r="C104" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="D104" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1066.48</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3874.1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3874.1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46294.14583333334</v>
+      </c>
+      <c r="B105" t="n">
+        <v>2697.41</v>
+      </c>
+      <c r="C105" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1076.23</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3806.76</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3806.76</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46294.16666666666</v>
+      </c>
+      <c r="B106" t="n">
+        <v>2630.54</v>
+      </c>
+      <c r="C106" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1086.92</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3754.84</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3751.43</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46294.1875</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2621.08</v>
+      </c>
+      <c r="C107" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1098.75</v>
+      </c>
+      <c r="F107" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3772.82</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3753.64</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46294.20833333334</v>
+      </c>
+      <c r="B108" t="n">
+        <v>2636.53</v>
+      </c>
+      <c r="C108" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1091.72</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3764.71</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3764.71</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46294.22916666666</v>
+      </c>
+      <c r="B109" t="n">
+        <v>2768.46</v>
+      </c>
+      <c r="C109" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="D109" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1093.61</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3908.2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3908.2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46294.25</v>
+      </c>
+      <c r="B110" t="n">
+        <v>2741.76</v>
+      </c>
+      <c r="C110" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1092.54</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3868.49</v>
+      </c>
+      <c r="H110" t="n">
+        <v>3868.49</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46294.27083333334</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2575.68</v>
+      </c>
+      <c r="C111" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1090.84</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>3698.94</v>
+      </c>
+      <c r="H111" t="n">
+        <v>3698.94</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46294.29166666666</v>
+      </c>
+      <c r="B112" t="n">
+        <v>2606.34</v>
+      </c>
+      <c r="C112" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1093.55</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>3733.37</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3733.37</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46294.3125</v>
+      </c>
+      <c r="B113" t="n">
+        <v>2709.41</v>
+      </c>
+      <c r="C113" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1093.21</v>
+      </c>
+      <c r="F113" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3876.39</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3836.02</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46294.33333333334</v>
+      </c>
+      <c r="B114" t="n">
+        <v>2930.36</v>
+      </c>
+      <c r="C114" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1089.78</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4054.64</v>
+      </c>
+      <c r="H114" t="n">
+        <v>4054.64</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46294.35416666666</v>
+      </c>
+      <c r="B115" t="n">
+        <v>3057.74</v>
+      </c>
+      <c r="C115" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="D115" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1076.22</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4178.48</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4178.48</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46294.375</v>
+      </c>
+      <c r="B116" t="n">
+        <v>3257.08</v>
+      </c>
+      <c r="C116" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1076.58</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>4389.08</v>
+      </c>
+      <c r="H116" t="n">
+        <v>4389.08</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46294.39583333334</v>
+      </c>
+      <c r="B117" t="n">
+        <v>3320.03</v>
+      </c>
+      <c r="C117" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1076.17</v>
+      </c>
+      <c r="F117" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G117" t="n">
+        <v>4480.240000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>4452.040000000001</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46294.41666666666</v>
+      </c>
+      <c r="B118" t="n">
+        <v>3411.92</v>
+      </c>
+      <c r="C118" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1059.81</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>4561.549999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>4561.549999999999</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46294.4375</v>
+      </c>
+      <c r="B119" t="n">
+        <v>3512.65</v>
+      </c>
+      <c r="C119" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>24</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1051</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4672.08</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4672.08</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46294.45833333334</v>
+      </c>
+      <c r="B120" t="n">
+        <v>3529.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1059.62</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4675.1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4675.1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46294.47916666666</v>
+      </c>
+      <c r="B121" t="n">
+        <v>3608.28</v>
+      </c>
+      <c r="C121" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1057.15</v>
+      </c>
+      <c r="F121" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4761.48</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4757.18</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46294.5</v>
+      </c>
+      <c r="B122" t="n">
+        <v>3593.99</v>
+      </c>
+      <c r="C122" t="n">
+        <v>90.58</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1072.7</v>
+      </c>
+      <c r="F122" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4768.6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>4757.27</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46294.52083333334</v>
+      </c>
+      <c r="B123" t="n">
+        <v>3578.77</v>
+      </c>
+      <c r="C123" t="n">
+        <v>85.56</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1072.81</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>4737.139999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>4737.139999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46294.54166666666</v>
+      </c>
+      <c r="B124" t="n">
+        <v>3608.92</v>
+      </c>
+      <c r="C124" t="n">
+        <v>80.54000000000001</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1073.24</v>
+      </c>
+      <c r="F124" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G124" t="n">
+        <v>4769.87</v>
+      </c>
+      <c r="H124" t="n">
+        <v>4762.7</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3614.22</v>
+      </c>
+      <c r="C125" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1078.29</v>
+      </c>
+      <c r="F125" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4778.28</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4772.67</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46294.58333333334</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3627.67</v>
+      </c>
+      <c r="C126" t="n">
+        <v>79.64</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1053.68</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4760.99</v>
+      </c>
+      <c r="H126" t="n">
+        <v>4760.99</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46294.60416666666</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3645.63</v>
+      </c>
+      <c r="C127" t="n">
+        <v>71.73</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1054.52</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4774.12</v>
+      </c>
+      <c r="H127" t="n">
+        <v>4774.12</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46294.625</v>
+      </c>
+      <c r="B128" t="n">
+        <v>3630.39</v>
+      </c>
+      <c r="C128" t="n">
+        <v>63.02</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1051.72</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4745.13</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4745.13</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46294.64583333334</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3570.82</v>
+      </c>
+      <c r="C129" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1059.97</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4700</v>
+      </c>
+      <c r="H129" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46294.66666666666</v>
+      </c>
+      <c r="B130" t="n">
+        <v>3501.66</v>
+      </c>
+      <c r="C130" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1060.3</v>
+      </c>
+      <c r="F130" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="G130" t="n">
+        <v>4629.05</v>
+      </c>
+      <c r="H130" t="n">
+        <v>4619.06</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46294.6875</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3447.44</v>
+      </c>
+      <c r="C131" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="D131" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1061.68</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>4570.55</v>
+      </c>
+      <c r="H131" t="n">
+        <v>4570.55</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46294.70833333334</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3358.99</v>
+      </c>
+      <c r="C132" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="D132" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1067.13</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>4492.799999999999</v>
+      </c>
+      <c r="H132" t="n">
+        <v>4492.799999999999</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46294.72916666666</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3290.6</v>
+      </c>
+      <c r="C133" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1077.52</v>
+      </c>
+      <c r="F133" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="G133" t="n">
+        <v>4421.79</v>
+      </c>
+      <c r="H133" t="n">
+        <v>4415.37</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46294.75</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3356.6</v>
+      </c>
+      <c r="C134" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1076.14</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4470.85</v>
+      </c>
+      <c r="H134" t="n">
+        <v>4470.85</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46294.77083333334</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3761.66</v>
+      </c>
+      <c r="C135" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="D135" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1073.74</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>4888.31</v>
+      </c>
+      <c r="H135" t="n">
+        <v>4888.31</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46294.79166666666</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3808.94</v>
+      </c>
+      <c r="C136" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1097.84</v>
+      </c>
+      <c r="F136" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="G136" t="n">
+        <v>4936.59</v>
+      </c>
+      <c r="H136" t="n">
+        <v>4932.2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46294.8125</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3843.85</v>
+      </c>
+      <c r="C137" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1097.68</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>4966.8</v>
+      </c>
+      <c r="H137" t="n">
+        <v>4966.8</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46294.83333333334</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3820.12</v>
+      </c>
+      <c r="C138" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="D138" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1097.31</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>4955.37</v>
+      </c>
+      <c r="H138" t="n">
+        <v>4955.37</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46294.85416666666</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3843.26</v>
+      </c>
+      <c r="C139" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1051.59</v>
+      </c>
+      <c r="F139" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4935.84</v>
+      </c>
+      <c r="H139" t="n">
+        <v>4921.37</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46294.875</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3766.66</v>
+      </c>
+      <c r="C140" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1042.55</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>4834.76</v>
+      </c>
+      <c r="H140" t="n">
+        <v>4834.76</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46294.89583333334</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3667.55</v>
+      </c>
+      <c r="C141" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1056.63</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>4745.65</v>
+      </c>
+      <c r="H141" t="n">
+        <v>4745.65</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46294.91666666666</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3517.62</v>
+      </c>
+      <c r="C142" t="n">
+        <v>22</v>
+      </c>
+      <c r="D142" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1066.32</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>4611.46</v>
+      </c>
+      <c r="H142" t="n">
+        <v>4611.46</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46294.9375</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3294.62</v>
+      </c>
+      <c r="C143" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1110.63</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4432.96</v>
+      </c>
+      <c r="H143" t="n">
+        <v>4432.96</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46294.95833333334</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3124.02</v>
+      </c>
+      <c r="C144" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1111.56</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4261.43</v>
+      </c>
+      <c r="H144" t="n">
+        <v>4261.43</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46294.97916666666</v>
+      </c>
+      <c r="B145" t="n">
+        <v>2954.14</v>
+      </c>
+      <c r="C145" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1117.74</v>
+      </c>
+      <c r="F145" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="G145" t="n">
+        <v>4115.35</v>
+      </c>
+      <c r="H145" t="n">
+        <v>4094.860000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,6 +767,59 @@
       </c>
       <c r="Q4" t="n">
         <v>0.006</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98975</v>
+      </c>
+      <c r="C5" t="n">
+        <v>71273</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26674</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23864</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="G5" t="n">
+        <v>920</v>
+      </c>
+      <c r="H5" t="n">
+        <v>107</v>
+      </c>
+      <c r="I5" t="n">
+        <v>96</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.124</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.004</v>
       </c>
     </row>
   </sheetData>
@@ -780,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,14 +844,14 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Coca Codo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>Paute</t>
@@ -816,12 +869,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Mazar</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -840,10 +893,10 @@
         <v>46291</v>
       </c>
       <c r="B2" t="n">
+        <v>16882</v>
+      </c>
+      <c r="C2" t="n">
         <v>24721</v>
-      </c>
-      <c r="C2" t="n">
-        <v>16882</v>
       </c>
       <c r="D2" t="n">
         <v>13964</v>
@@ -855,10 +908,10 @@
         <v>3724</v>
       </c>
       <c r="G2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="H2" t="n">
         <v>2301</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2768</v>
       </c>
       <c r="I2" t="n">
         <v>2003</v>
@@ -872,10 +925,10 @@
         <v>46293</v>
       </c>
       <c r="B3" t="n">
+        <v>20069</v>
+      </c>
+      <c r="C3" t="n">
         <v>23420</v>
-      </c>
-      <c r="C3" t="n">
-        <v>20069</v>
       </c>
       <c r="D3" t="n">
         <v>16681</v>
@@ -887,10 +940,10 @@
         <v>3644</v>
       </c>
       <c r="G3" t="n">
+        <v>2477</v>
+      </c>
+      <c r="H3" t="n">
         <v>2554</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2477</v>
       </c>
       <c r="I3" t="n">
         <v>1820</v>
@@ -904,10 +957,10 @@
         <v>46294</v>
       </c>
       <c r="B4" t="n">
+        <v>19095</v>
+      </c>
+      <c r="C4" t="n">
         <v>19992</v>
-      </c>
-      <c r="C4" t="n">
-        <v>19095</v>
       </c>
       <c r="D4" t="n">
         <v>17645</v>
@@ -919,16 +972,48 @@
         <v>3194</v>
       </c>
       <c r="G4" t="n">
+        <v>2491</v>
+      </c>
+      <c r="H4" t="n">
         <v>2604</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2491</v>
       </c>
       <c r="I4" t="n">
         <v>1820</v>
       </c>
       <c r="J4" t="n">
         <v>306</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B5" t="n">
+        <v>19098</v>
+      </c>
+      <c r="C5" t="n">
+        <v>17987</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14882</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8469</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3026</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2773</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2307</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J5" t="n">
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -942,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,17 +1071,13 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1005,7 +1086,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>24721</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="3">
@@ -1017,17 +1098,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1036,7 +1113,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23420</v>
+        <v>20069</v>
       </c>
     </row>
     <row r="4">
@@ -1048,17 +1125,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1067,7 +1140,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19992</v>
+        <v>19095</v>
       </c>
     </row>
     <row r="5">
@@ -1075,7 +1148,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1094,7 +1167,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>16882</v>
+        <v>19098</v>
       </c>
     </row>
     <row r="6">
@@ -1102,17 +1175,21 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1121,7 +1198,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20069</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="7">
@@ -1129,17 +1206,21 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1148,7 +1229,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>19095</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="8">
@@ -1156,21 +1237,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1179,7 +1260,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>13964</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="9">
@@ -1187,21 +1268,21 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1210,7 +1291,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>16681</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="10">
@@ -1218,7 +1299,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1241,7 +1322,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>17645</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="11">
@@ -1249,11 +1330,11 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1272,7 +1353,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8114</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="12">
@@ -1280,11 +1361,11 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1303,7 +1384,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8424</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="13">
@@ -1311,11 +1392,11 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1334,7 +1415,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>9735</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="14">
@@ -1346,17 +1427,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1365,7 +1446,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3724</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="15">
@@ -1377,17 +1458,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1396,7 +1477,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3644</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="16">
@@ -1408,17 +1489,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1427,7 +1508,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3194</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="17">
@@ -1435,11 +1516,11 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1458,7 +1539,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2301</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="18">
@@ -1466,21 +1547,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1489,7 +1570,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2554</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="19">
@@ -1497,21 +1578,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1520,7 +1601,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2604</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="20">
@@ -1528,21 +1609,21 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1551,7 +1632,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2768</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="21">
@@ -1559,21 +1640,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1582,7 +1663,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2477</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="22">
@@ -1590,7 +1671,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1613,7 +1694,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2491</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="23">
@@ -1621,11 +1702,11 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1644,7 +1725,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2003</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="24">
@@ -1652,11 +1733,11 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1675,7 +1756,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1820</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="25">
@@ -1683,11 +1764,11 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1706,7 +1787,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1820</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="26">
@@ -1718,7 +1799,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1737,7 +1818,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>239</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="27">
@@ -1749,7 +1830,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1768,7 +1849,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1531</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="28">
@@ -1780,26 +1861,305 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Minas San Francisco</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G34" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>306</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -1813,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5602,6 +5962,1254 @@
         <v>4094.860000000001</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B146" t="n">
+        <v>2767.29</v>
+      </c>
+      <c r="C146" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1131.03</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3922.69</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3922.69</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46295.02083333334</v>
+      </c>
+      <c r="B147" t="n">
+        <v>2681.16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1079.92</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3790.51</v>
+      </c>
+      <c r="H147" t="n">
+        <v>3788.28</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46295.04166666666</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2583.53</v>
+      </c>
+      <c r="C148" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1079.66</v>
+      </c>
+      <c r="F148" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="G148" t="n">
+        <v>3700.33</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3692.27</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46295.0625</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2494.13</v>
+      </c>
+      <c r="C149" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="D149" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1082.18</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3614.66</v>
+      </c>
+      <c r="H149" t="n">
+        <v>3614.66</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46295.08333333334</v>
+      </c>
+      <c r="B150" t="n">
+        <v>2405.18</v>
+      </c>
+      <c r="C150" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="D150" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1099.91</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3545.11</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3545.11</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46295.10416666666</v>
+      </c>
+      <c r="B151" t="n">
+        <v>2333.45</v>
+      </c>
+      <c r="C151" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1101.53</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>3466.15</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3466.15</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46295.125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2283.12</v>
+      </c>
+      <c r="C152" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1108.85</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>3424.52</v>
+      </c>
+      <c r="H152" t="n">
+        <v>3424.52</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46295.14583333334</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2241.82</v>
+      </c>
+      <c r="C153" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1110.95</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3387.05</v>
+      </c>
+      <c r="H153" t="n">
+        <v>3387.05</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46295.16666666666</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2213.88</v>
+      </c>
+      <c r="C154" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1109.63</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>3355.17</v>
+      </c>
+      <c r="H154" t="n">
+        <v>3355.17</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46295.1875</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2208.33</v>
+      </c>
+      <c r="C155" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="D155" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1105.99</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3357.48</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3357.48</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46295.20833333334</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2229.77</v>
+      </c>
+      <c r="C156" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="D156" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1101.24</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3379.63</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3379.63</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46295.22916666666</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2332.49</v>
+      </c>
+      <c r="C157" t="n">
+        <v>31.13</v>
+      </c>
+      <c r="D157" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1109.06</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3486.93</v>
+      </c>
+      <c r="H157" t="n">
+        <v>3486.93</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46295.25</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2329.19</v>
+      </c>
+      <c r="C158" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1120.53</v>
+      </c>
+      <c r="F158" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G158" t="n">
+        <v>3490.04</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3481.44</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46295.27083333334</v>
+      </c>
+      <c r="B159" t="n">
+        <v>2156.19</v>
+      </c>
+      <c r="C159" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1141.19</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3329.4</v>
+      </c>
+      <c r="H159" t="n">
+        <v>3329.4</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46295.29166666666</v>
+      </c>
+      <c r="B160" t="n">
+        <v>2148.89</v>
+      </c>
+      <c r="C160" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1136.34</v>
+      </c>
+      <c r="F160" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="G160" t="n">
+        <v>3332.69</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3316.139999999999</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46295.3125</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2349.71</v>
+      </c>
+      <c r="C161" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1131.69</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>3508.1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3508.1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46295.33333333334</v>
+      </c>
+      <c r="B162" t="n">
+        <v>2486.11</v>
+      </c>
+      <c r="C162" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="D162" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1127.97</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>3652.4</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3652.4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46295.35416666666</v>
+      </c>
+      <c r="B163" t="n">
+        <v>2697.93</v>
+      </c>
+      <c r="C163" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1131.91</v>
+      </c>
+      <c r="F163" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="G163" t="n">
+        <v>3865.34</v>
+      </c>
+      <c r="H163" t="n">
+        <v>3851.82</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46295.375</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2814.81</v>
+      </c>
+      <c r="C164" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1144.16</v>
+      </c>
+      <c r="F164" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="G164" t="n">
+        <v>4017.01</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3983.12</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46295.39583333334</v>
+      </c>
+      <c r="B165" t="n">
+        <v>2987.71</v>
+      </c>
+      <c r="C165" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1137.79</v>
+      </c>
+      <c r="F165" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G165" t="n">
+        <v>4164.7</v>
+      </c>
+      <c r="H165" t="n">
+        <v>4158.69</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46295.41666666666</v>
+      </c>
+      <c r="B166" t="n">
+        <v>3083.47</v>
+      </c>
+      <c r="C166" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="D166" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1132.31</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>4268.46</v>
+      </c>
+      <c r="H166" t="n">
+        <v>4268.46</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46295.4375</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3180.35</v>
+      </c>
+      <c r="C167" t="n">
+        <v>63.91</v>
+      </c>
+      <c r="D167" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1109.18</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>4369.139999999999</v>
+      </c>
+      <c r="H167" t="n">
+        <v>4369.139999999999</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46295.45833333334</v>
+      </c>
+      <c r="B168" t="n">
+        <v>3298.91</v>
+      </c>
+      <c r="C168" t="n">
+        <v>72.83</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1100.9</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>4472.639999999999</v>
+      </c>
+      <c r="H168" t="n">
+        <v>4472.639999999999</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46295.47916666666</v>
+      </c>
+      <c r="B169" t="n">
+        <v>3314.2</v>
+      </c>
+      <c r="C169" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="D169" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1113.8</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>4530.259999999999</v>
+      </c>
+      <c r="H169" t="n">
+        <v>4530.259999999999</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46295.5</v>
+      </c>
+      <c r="B170" t="n">
+        <v>3309.66</v>
+      </c>
+      <c r="C170" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="D170" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1120.86</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>4518.54</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4518.54</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46295.52083333334</v>
+      </c>
+      <c r="B171" t="n">
+        <v>3308.78</v>
+      </c>
+      <c r="C171" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="D171" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1118.28</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>4525.92</v>
+      </c>
+      <c r="H171" t="n">
+        <v>4525.92</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46295.54166666666</v>
+      </c>
+      <c r="B172" t="n">
+        <v>3380.69</v>
+      </c>
+      <c r="C172" t="n">
+        <v>80.66</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1116.51</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>4577.86</v>
+      </c>
+      <c r="H172" t="n">
+        <v>4577.86</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B173" t="n">
+        <v>3398.1</v>
+      </c>
+      <c r="C173" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="D173" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1119.14</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>4609.92</v>
+      </c>
+      <c r="H173" t="n">
+        <v>4609.92</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46295.58333333334</v>
+      </c>
+      <c r="B174" t="n">
+        <v>3475.45</v>
+      </c>
+      <c r="C174" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1114.76</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>4661.96</v>
+      </c>
+      <c r="H174" t="n">
+        <v>4661.96</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46295.60416666666</v>
+      </c>
+      <c r="B175" t="n">
+        <v>3507.77</v>
+      </c>
+      <c r="C175" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1115.93</v>
+      </c>
+      <c r="F175" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="G175" t="n">
+        <v>4717.7</v>
+      </c>
+      <c r="H175" t="n">
+        <v>4698.42</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46295.625</v>
+      </c>
+      <c r="B176" t="n">
+        <v>3525.36</v>
+      </c>
+      <c r="C176" t="n">
+        <v>68.86</v>
+      </c>
+      <c r="D176" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1124.98</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>4722.83</v>
+      </c>
+      <c r="H176" t="n">
+        <v>4722.83</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46295.64583333334</v>
+      </c>
+      <c r="B177" t="n">
+        <v>3514.38</v>
+      </c>
+      <c r="C177" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1134.96</v>
+      </c>
+      <c r="F177" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="G177" t="n">
+        <v>4721.070000000001</v>
+      </c>
+      <c r="H177" t="n">
+        <v>4706.1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46295.66666666666</v>
+      </c>
+      <c r="B178" t="n">
+        <v>3482.25</v>
+      </c>
+      <c r="C178" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1138.86</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>4668.62</v>
+      </c>
+      <c r="H178" t="n">
+        <v>4668.62</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46295.6875</v>
+      </c>
+      <c r="B179" t="n">
+        <v>3436.06</v>
+      </c>
+      <c r="C179" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1155.62</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>4638.79</v>
+      </c>
+      <c r="H179" t="n">
+        <v>4638.79</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46295.70833333334</v>
+      </c>
+      <c r="B180" t="n">
+        <v>3376.74</v>
+      </c>
+      <c r="C180" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1148.05</v>
+      </c>
+      <c r="F180" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="G180" t="n">
+        <v>4583.71</v>
+      </c>
+      <c r="H180" t="n">
+        <v>4568.67</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46295.72916666666</v>
+      </c>
+      <c r="B181" t="n">
+        <v>3308.95</v>
+      </c>
+      <c r="C181" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1147.46</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>4492.95</v>
+      </c>
+      <c r="H181" t="n">
+        <v>4492.95</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46295.75</v>
+      </c>
+      <c r="B182" t="n">
+        <v>3380.46</v>
+      </c>
+      <c r="C182" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="D182" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1152.76</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>4580.32</v>
+      </c>
+      <c r="H182" t="n">
+        <v>4580.32</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46295.77083333334</v>
+      </c>
+      <c r="B183" t="n">
+        <v>3742.87</v>
+      </c>
+      <c r="C183" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1171.17</v>
+      </c>
+      <c r="F183" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G183" t="n">
+        <v>4947.61</v>
+      </c>
+      <c r="H183" t="n">
+        <v>4944.21</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46295.79166666666</v>
+      </c>
+      <c r="B184" t="n">
+        <v>3823.96</v>
+      </c>
+      <c r="C184" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1172.88</v>
+      </c>
+      <c r="F184" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="G184" t="n">
+        <v>5042.02</v>
+      </c>
+      <c r="H184" t="n">
+        <v>5022.700000000001</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46295.8125</v>
+      </c>
+      <c r="B185" t="n">
+        <v>3853.09</v>
+      </c>
+      <c r="C185" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1174.91</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>5049.780000000001</v>
+      </c>
+      <c r="H185" t="n">
+        <v>5049.780000000001</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46295.83333333334</v>
+      </c>
+      <c r="B186" t="n">
+        <v>3840.25</v>
+      </c>
+      <c r="C186" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1174.77</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>5034.82</v>
+      </c>
+      <c r="H186" t="n">
+        <v>5034.82</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46295.85416666666</v>
+      </c>
+      <c r="B187" t="n">
+        <v>3781.34</v>
+      </c>
+      <c r="C187" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="D187" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1182.66</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>4998.51</v>
+      </c>
+      <c r="H187" t="n">
+        <v>4998.51</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46295.875</v>
+      </c>
+      <c r="B188" t="n">
+        <v>3677.91</v>
+      </c>
+      <c r="C188" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1202.46</v>
+      </c>
+      <c r="F188" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="G188" t="n">
+        <v>4929.429999999999</v>
+      </c>
+      <c r="H188" t="n">
+        <v>4899.86</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46295.89583333334</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3577.86</v>
+      </c>
+      <c r="C189" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1196.53</v>
+      </c>
+      <c r="F189" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G189" t="n">
+        <v>4799.68</v>
+      </c>
+      <c r="H189" t="n">
+        <v>4797.440000000001</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46295.91666666666</v>
+      </c>
+      <c r="B190" t="n">
+        <v>3461.9</v>
+      </c>
+      <c r="C190" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1200.8</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>4679.96</v>
+      </c>
+      <c r="H190" t="n">
+        <v>4679.96</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46295.9375</v>
+      </c>
+      <c r="B191" t="n">
+        <v>3308.9</v>
+      </c>
+      <c r="C191" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="D191" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1191.56</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>4526.14</v>
+      </c>
+      <c r="H191" t="n">
+        <v>4526.14</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46295.95833333334</v>
+      </c>
+      <c r="B192" t="n">
+        <v>3152.86</v>
+      </c>
+      <c r="C192" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1192.67</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>4360.88</v>
+      </c>
+      <c r="H192" t="n">
+        <v>4360.88</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46295.97916666666</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2978.7</v>
+      </c>
+      <c r="C193" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1196.17</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>4184.23</v>
+      </c>
+      <c r="H193" t="n">
+        <v>4184.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,6 +819,59 @@
         <v>0.004</v>
       </c>
       <c r="Q5" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101684</v>
+      </c>
+      <c r="C6" t="n">
+        <v>73375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>27619</v>
+      </c>
+      <c r="E6" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2794</v>
+      </c>
+      <c r="G6" t="n">
+        <v>584</v>
+      </c>
+      <c r="H6" t="n">
+        <v>105</v>
+      </c>
+      <c r="I6" t="n">
+        <v>88</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.237</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.057</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -833,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,12 +922,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Mazar</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -908,10 +961,10 @@
         <v>3724</v>
       </c>
       <c r="G2" t="n">
+        <v>2301</v>
+      </c>
+      <c r="H2" t="n">
         <v>2768</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2301</v>
       </c>
       <c r="I2" t="n">
         <v>2003</v>
@@ -940,10 +993,10 @@
         <v>3644</v>
       </c>
       <c r="G3" t="n">
+        <v>2554</v>
+      </c>
+      <c r="H3" t="n">
         <v>2477</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2554</v>
       </c>
       <c r="I3" t="n">
         <v>1820</v>
@@ -972,10 +1025,10 @@
         <v>3194</v>
       </c>
       <c r="G4" t="n">
+        <v>2604</v>
+      </c>
+      <c r="H4" t="n">
         <v>2491</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2604</v>
       </c>
       <c r="I4" t="n">
         <v>1820</v>
@@ -1004,16 +1057,48 @@
         <v>3026</v>
       </c>
       <c r="G5" t="n">
+        <v>2307</v>
+      </c>
+      <c r="H5" t="n">
         <v>2773</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2307</v>
       </c>
       <c r="I5" t="n">
         <v>2009</v>
       </c>
       <c r="J5" t="n">
         <v>721</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>20810</v>
+      </c>
+      <c r="C6" t="n">
+        <v>17990</v>
+      </c>
+      <c r="D6" t="n">
+        <v>14644</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8416</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3345</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3102</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2472</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1847</v>
+      </c>
+      <c r="J6" t="n">
+        <v>750</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,21 +1260,17 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1198,7 +1279,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>24721</v>
+        <v>20810</v>
       </c>
     </row>
     <row r="7">
@@ -1206,7 +1287,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,7 +1310,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>23420</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="8">
@@ -1237,7 +1318,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1260,7 +1341,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>19992</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="9">
@@ -1268,7 +1349,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1291,7 +1372,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>17987</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="10">
@@ -1299,21 +1380,21 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1322,7 +1403,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>13964</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="11">
@@ -1330,21 +1411,21 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1353,7 +1434,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>16681</v>
+        <v>17990</v>
       </c>
     </row>
     <row r="12">
@@ -1361,7 +1442,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1384,7 +1465,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>17645</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="13">
@@ -1392,7 +1473,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1415,7 +1496,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14882</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="14">
@@ -1423,11 +1504,11 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1446,7 +1527,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8114</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="15">
@@ -1454,11 +1535,11 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1477,7 +1558,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>8424</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="16">
@@ -1485,11 +1566,11 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1508,7 +1589,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>9735</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="17">
@@ -1516,7 +1597,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1539,7 +1620,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>8469</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="18">
@@ -1547,21 +1628,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1570,7 +1651,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3724</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="19">
@@ -1578,21 +1659,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1601,7 +1682,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3644</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="20">
@@ -1609,21 +1690,21 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1632,7 +1713,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3194</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="21">
@@ -1640,21 +1721,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1663,7 +1744,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3026</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="22">
@@ -1675,17 +1756,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1694,7 +1775,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2768</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="23">
@@ -1706,17 +1787,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1725,7 +1806,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2477</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="24">
@@ -1737,17 +1818,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1756,7 +1837,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2491</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="25">
@@ -1768,17 +1849,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1787,7 +1868,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2773</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="26">
@@ -1795,21 +1876,21 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1818,7 +1899,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2301</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="27">
@@ -1826,7 +1907,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1849,7 +1930,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2554</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="28">
@@ -1857,7 +1938,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1880,7 +1961,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2604</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="29">
@@ -1888,7 +1969,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1911,7 +1992,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2307</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="30">
@@ -1919,16 +2000,16 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1942,7 +2023,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2003</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="31">
@@ -1950,16 +2031,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1973,7 +2054,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1820</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="32">
@@ -1981,11 +2062,11 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2004,7 +2085,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1820</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="33">
@@ -2012,11 +2093,11 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2035,7 +2116,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2009</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="34">
@@ -2043,16 +2124,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2066,7 +2147,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>239</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="35">
@@ -2074,16 +2155,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2097,7 +2178,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1531</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="36">
@@ -2105,16 +2186,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2128,7 +2209,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>306</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="37">
@@ -2136,30 +2217,309 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Minas San Francisco</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="G42" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
         <v>721</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>750</v>
       </c>
     </row>
   </sheetData>
@@ -2173,7 +2533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7210,6 +7570,1254 @@
         <v>4184.23</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2778.63</v>
+      </c>
+      <c r="C194" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1200.5</v>
+      </c>
+      <c r="F194" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="G194" t="n">
+        <v>3994.36</v>
+      </c>
+      <c r="H194" t="n">
+        <v>3987.14</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46296.02083333334</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2771.65</v>
+      </c>
+      <c r="C195" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1134.02</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G195" t="n">
+        <v>3915.29</v>
+      </c>
+      <c r="H195" t="n">
+        <v>3913.32</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46296.04166666666</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2678.83</v>
+      </c>
+      <c r="C196" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1141.77</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>3827.77</v>
+      </c>
+      <c r="H196" t="n">
+        <v>3827.77</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46296.0625</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2599.04</v>
+      </c>
+      <c r="C197" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D197" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1140.13</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>3751.42</v>
+      </c>
+      <c r="H197" t="n">
+        <v>3751.42</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46296.08333333334</v>
+      </c>
+      <c r="B198" t="n">
+        <v>2496.61</v>
+      </c>
+      <c r="C198" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1180.15</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3683.11</v>
+      </c>
+      <c r="H198" t="n">
+        <v>3683.11</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46296.10416666666</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2431.74</v>
+      </c>
+      <c r="C199" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1186.14</v>
+      </c>
+      <c r="F199" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="G199" t="n">
+        <v>3633.84</v>
+      </c>
+      <c r="H199" t="n">
+        <v>3624.23</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46296.125</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2378.15</v>
+      </c>
+      <c r="C200" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1191.43</v>
+      </c>
+      <c r="F200" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G200" t="n">
+        <v>3583.37</v>
+      </c>
+      <c r="H200" t="n">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46296.14583333334</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2341.49</v>
+      </c>
+      <c r="C201" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="D201" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1186.38</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>3543.96</v>
+      </c>
+      <c r="H201" t="n">
+        <v>3543.96</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46296.16666666666</v>
+      </c>
+      <c r="B202" t="n">
+        <v>2283.36</v>
+      </c>
+      <c r="C202" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1187.46</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>3487.37</v>
+      </c>
+      <c r="H202" t="n">
+        <v>3487.37</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46296.1875</v>
+      </c>
+      <c r="B203" t="n">
+        <v>2250.63</v>
+      </c>
+      <c r="C203" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="D203" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1198.15</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>3471.68</v>
+      </c>
+      <c r="H203" t="n">
+        <v>3471.68</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46296.20833333334</v>
+      </c>
+      <c r="B204" t="n">
+        <v>2296.22</v>
+      </c>
+      <c r="C204" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1199.21</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>3512.74</v>
+      </c>
+      <c r="H204" t="n">
+        <v>3512.74</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46296.22916666666</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2383.51</v>
+      </c>
+      <c r="C205" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1205.84</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G205" t="n">
+        <v>3606.61</v>
+      </c>
+      <c r="H205" t="n">
+        <v>3604.77</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46296.25</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2512.02</v>
+      </c>
+      <c r="C206" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1202.17</v>
+      </c>
+      <c r="F206" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="G206" t="n">
+        <v>3739.55</v>
+      </c>
+      <c r="H206" t="n">
+        <v>3730.66</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46296.27083333334</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2301.01</v>
+      </c>
+      <c r="C207" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="D207" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1199.05</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>3527.37</v>
+      </c>
+      <c r="H207" t="n">
+        <v>3527.37</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46296.29166666666</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2254.81</v>
+      </c>
+      <c r="C208" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1192.3</v>
+      </c>
+      <c r="F208" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="G208" t="n">
+        <v>3482.92</v>
+      </c>
+      <c r="H208" t="n">
+        <v>3464.63</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46296.3125</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2465.24</v>
+      </c>
+      <c r="C209" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1177.12</v>
+      </c>
+      <c r="F209" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="G209" t="n">
+        <v>3693.74</v>
+      </c>
+      <c r="H209" t="n">
+        <v>3663.2</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46296.33333333334</v>
+      </c>
+      <c r="B210" t="n">
+        <v>2566.8</v>
+      </c>
+      <c r="C210" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1170.81</v>
+      </c>
+      <c r="F210" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="G210" t="n">
+        <v>3787.3</v>
+      </c>
+      <c r="H210" t="n">
+        <v>3757.81</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46296.35416666666</v>
+      </c>
+      <c r="B211" t="n">
+        <v>2798.6</v>
+      </c>
+      <c r="C211" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="D211" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1171.1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>3992.58</v>
+      </c>
+      <c r="H211" t="n">
+        <v>3992.58</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46296.375</v>
+      </c>
+      <c r="B212" t="n">
+        <v>2901.82</v>
+      </c>
+      <c r="C212" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1154.1</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>4075.57</v>
+      </c>
+      <c r="H212" t="n">
+        <v>4075.57</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46296.39583333334</v>
+      </c>
+      <c r="B213" t="n">
+        <v>3065.99</v>
+      </c>
+      <c r="C213" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1142.76</v>
+      </c>
+      <c r="F213" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="G213" t="n">
+        <v>4244.84</v>
+      </c>
+      <c r="H213" t="n">
+        <v>4229.01</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46296.41666666666</v>
+      </c>
+      <c r="B214" t="n">
+        <v>3157.63</v>
+      </c>
+      <c r="C214" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1147.85</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>4327.29</v>
+      </c>
+      <c r="H214" t="n">
+        <v>4327.29</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46296.4375</v>
+      </c>
+      <c r="B215" t="n">
+        <v>3257.87</v>
+      </c>
+      <c r="C215" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="D215" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1144.25</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>4437.78</v>
+      </c>
+      <c r="H215" t="n">
+        <v>4437.78</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46296.45833333334</v>
+      </c>
+      <c r="B216" t="n">
+        <v>3318.14</v>
+      </c>
+      <c r="C216" t="n">
+        <v>35.89</v>
+      </c>
+      <c r="D216" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1131.76</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>4496.3</v>
+      </c>
+      <c r="H216" t="n">
+        <v>4496.3</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46296.47916666666</v>
+      </c>
+      <c r="B217" t="n">
+        <v>3425.91</v>
+      </c>
+      <c r="C217" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="D217" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1146.13</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>4629.87</v>
+      </c>
+      <c r="H217" t="n">
+        <v>4629.87</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46296.5</v>
+      </c>
+      <c r="B218" t="n">
+        <v>3406.36</v>
+      </c>
+      <c r="C218" t="n">
+        <v>60.18</v>
+      </c>
+      <c r="D218" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1142.61</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>4624.42</v>
+      </c>
+      <c r="H218" t="n">
+        <v>4624.42</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46296.52083333334</v>
+      </c>
+      <c r="B219" t="n">
+        <v>3437.5</v>
+      </c>
+      <c r="C219" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1157.37</v>
+      </c>
+      <c r="F219" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="G219" t="n">
+        <v>4656.959999999999</v>
+      </c>
+      <c r="H219" t="n">
+        <v>4654.469999999999</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46296.54166666666</v>
+      </c>
+      <c r="B220" t="n">
+        <v>3432.98</v>
+      </c>
+      <c r="C220" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1158.65</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>4657.67</v>
+      </c>
+      <c r="H220" t="n">
+        <v>4657.67</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B221" t="n">
+        <v>3507.86</v>
+      </c>
+      <c r="C221" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="D221" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1162.78</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>4720.74</v>
+      </c>
+      <c r="H221" t="n">
+        <v>4720.74</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46296.58333333334</v>
+      </c>
+      <c r="B222" t="n">
+        <v>3537.99</v>
+      </c>
+      <c r="C222" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="D222" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1169.65</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>4776.79</v>
+      </c>
+      <c r="H222" t="n">
+        <v>4776.79</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46296.60416666666</v>
+      </c>
+      <c r="B223" t="n">
+        <v>3666.66</v>
+      </c>
+      <c r="C223" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1172.63</v>
+      </c>
+      <c r="F223" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G223" t="n">
+        <v>4883.530000000001</v>
+      </c>
+      <c r="H223" t="n">
+        <v>4876.56</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46296.625</v>
+      </c>
+      <c r="B224" t="n">
+        <v>3697.47</v>
+      </c>
+      <c r="C224" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="D224" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1170.14</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>4908.72</v>
+      </c>
+      <c r="H224" t="n">
+        <v>4908.72</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46296.64583333334</v>
+      </c>
+      <c r="B225" t="n">
+        <v>3672.32</v>
+      </c>
+      <c r="C225" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="D225" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1170.68</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>4873.910000000001</v>
+      </c>
+      <c r="H225" t="n">
+        <v>4873.910000000001</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46296.66666666666</v>
+      </c>
+      <c r="B226" t="n">
+        <v>3669.35</v>
+      </c>
+      <c r="C226" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="D226" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1152.94</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>4850.870000000001</v>
+      </c>
+      <c r="H226" t="n">
+        <v>4850.870000000001</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46296.6875</v>
+      </c>
+      <c r="B227" t="n">
+        <v>3603.45</v>
+      </c>
+      <c r="C227" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1154.71</v>
+      </c>
+      <c r="F227" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G227" t="n">
+        <v>4782.71</v>
+      </c>
+      <c r="H227" t="n">
+        <v>4779.47</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46296.70833333334</v>
+      </c>
+      <c r="B228" t="n">
+        <v>3495.99</v>
+      </c>
+      <c r="C228" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="D228" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1155.43</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>4682.41</v>
+      </c>
+      <c r="H228" t="n">
+        <v>4682.41</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46296.72916666666</v>
+      </c>
+      <c r="B229" t="n">
+        <v>3389.94</v>
+      </c>
+      <c r="C229" t="n">
+        <v>25</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1162.58</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>4580.219999999999</v>
+      </c>
+      <c r="H229" t="n">
+        <v>4580.219999999999</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46296.75</v>
+      </c>
+      <c r="B230" t="n">
+        <v>3316.87</v>
+      </c>
+      <c r="C230" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="D230" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1164.98</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>4539.76</v>
+      </c>
+      <c r="H230" t="n">
+        <v>4539.76</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46296.77083333334</v>
+      </c>
+      <c r="B231" t="n">
+        <v>3736.33</v>
+      </c>
+      <c r="C231" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1192.54</v>
+      </c>
+      <c r="F231" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G231" t="n">
+        <v>4972.91</v>
+      </c>
+      <c r="H231" t="n">
+        <v>4970.4</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46296.79166666666</v>
+      </c>
+      <c r="B232" t="n">
+        <v>3840.9</v>
+      </c>
+      <c r="C232" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1203.22</v>
+      </c>
+      <c r="F232" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="G232" t="n">
+        <v>5085.749999999999</v>
+      </c>
+      <c r="H232" t="n">
+        <v>5080.429999999999</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46296.8125</v>
+      </c>
+      <c r="B233" t="n">
+        <v>3872.97</v>
+      </c>
+      <c r="C233" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1199.75</v>
+      </c>
+      <c r="F233" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="G233" t="n">
+        <v>5109.48</v>
+      </c>
+      <c r="H233" t="n">
+        <v>5105.639999999999</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46296.83333333334</v>
+      </c>
+      <c r="B234" t="n">
+        <v>3874.41</v>
+      </c>
+      <c r="C234" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1199.79</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>5097.95</v>
+      </c>
+      <c r="H234" t="n">
+        <v>5097.95</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46296.85416666666</v>
+      </c>
+      <c r="B235" t="n">
+        <v>3818.1</v>
+      </c>
+      <c r="C235" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="D235" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E235" t="n">
+        <v>1205.47</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>5057.05</v>
+      </c>
+      <c r="H235" t="n">
+        <v>5057.05</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46296.875</v>
+      </c>
+      <c r="B236" t="n">
+        <v>3766.36</v>
+      </c>
+      <c r="C236" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1205.87</v>
+      </c>
+      <c r="F236" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="G236" t="n">
+        <v>5005.089999999999</v>
+      </c>
+      <c r="H236" t="n">
+        <v>4992.81</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46296.89583333334</v>
+      </c>
+      <c r="B237" t="n">
+        <v>3681.97</v>
+      </c>
+      <c r="C237" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="D237" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1205.73</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>4910.85</v>
+      </c>
+      <c r="H237" t="n">
+        <v>4910.85</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46296.91666666666</v>
+      </c>
+      <c r="B238" t="n">
+        <v>3575.49</v>
+      </c>
+      <c r="C238" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="D238" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1206.23</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>4812.31</v>
+      </c>
+      <c r="H238" t="n">
+        <v>4812.31</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46296.9375</v>
+      </c>
+      <c r="B239" t="n">
+        <v>3432.76</v>
+      </c>
+      <c r="C239" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="D239" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1195.3</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>4662</v>
+      </c>
+      <c r="H239" t="n">
+        <v>4662</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46296.95833333334</v>
+      </c>
+      <c r="B240" t="n">
+        <v>3266.84</v>
+      </c>
+      <c r="C240" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1198.18</v>
+      </c>
+      <c r="F240" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="G240" t="n">
+        <v>4503</v>
+      </c>
+      <c r="H240" t="n">
+        <v>4486.51</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46296.97916666666</v>
+      </c>
+      <c r="B241" t="n">
+        <v>3096.26</v>
+      </c>
+      <c r="C241" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="D241" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1202.14</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>4327.150000000001</v>
+      </c>
+      <c r="H241" t="n">
+        <v>4327.150000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,6 +872,59 @@
         <v>0.004</v>
       </c>
       <c r="Q6" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95778</v>
+      </c>
+      <c r="C7" t="n">
+        <v>67455</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27634</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24855</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2779</v>
+      </c>
+      <c r="G7" t="n">
+        <v>600</v>
+      </c>
+      <c r="H7" t="n">
+        <v>89</v>
+      </c>
+      <c r="I7" t="n">
+        <v>91</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.991</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -886,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,14 +950,14 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Otras Hidro</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>Paute</t>
@@ -922,12 +975,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Mazar</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -946,10 +999,10 @@
         <v>46291</v>
       </c>
       <c r="B2" t="n">
+        <v>24721</v>
+      </c>
+      <c r="C2" t="n">
         <v>16882</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24721</v>
       </c>
       <c r="D2" t="n">
         <v>13964</v>
@@ -961,10 +1014,10 @@
         <v>3724</v>
       </c>
       <c r="G2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="H2" t="n">
         <v>2301</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2768</v>
       </c>
       <c r="I2" t="n">
         <v>2003</v>
@@ -978,10 +1031,10 @@
         <v>46293</v>
       </c>
       <c r="B3" t="n">
+        <v>23420</v>
+      </c>
+      <c r="C3" t="n">
         <v>20069</v>
-      </c>
-      <c r="C3" t="n">
-        <v>23420</v>
       </c>
       <c r="D3" t="n">
         <v>16681</v>
@@ -993,10 +1046,10 @@
         <v>3644</v>
       </c>
       <c r="G3" t="n">
+        <v>2477</v>
+      </c>
+      <c r="H3" t="n">
         <v>2554</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2477</v>
       </c>
       <c r="I3" t="n">
         <v>1820</v>
@@ -1010,10 +1063,10 @@
         <v>46294</v>
       </c>
       <c r="B4" t="n">
+        <v>19992</v>
+      </c>
+      <c r="C4" t="n">
         <v>19095</v>
-      </c>
-      <c r="C4" t="n">
-        <v>19992</v>
       </c>
       <c r="D4" t="n">
         <v>17645</v>
@@ -1025,10 +1078,10 @@
         <v>3194</v>
       </c>
       <c r="G4" t="n">
+        <v>2491</v>
+      </c>
+      <c r="H4" t="n">
         <v>2604</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2491</v>
       </c>
       <c r="I4" t="n">
         <v>1820</v>
@@ -1042,10 +1095,10 @@
         <v>46295</v>
       </c>
       <c r="B5" t="n">
+        <v>17987</v>
+      </c>
+      <c r="C5" t="n">
         <v>19098</v>
-      </c>
-      <c r="C5" t="n">
-        <v>17987</v>
       </c>
       <c r="D5" t="n">
         <v>14882</v>
@@ -1057,10 +1110,10 @@
         <v>3026</v>
       </c>
       <c r="G5" t="n">
+        <v>2773</v>
+      </c>
+      <c r="H5" t="n">
         <v>2307</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2773</v>
       </c>
       <c r="I5" t="n">
         <v>2009</v>
@@ -1074,10 +1127,10 @@
         <v>46296</v>
       </c>
       <c r="B6" t="n">
+        <v>17990</v>
+      </c>
+      <c r="C6" t="n">
         <v>20810</v>
-      </c>
-      <c r="C6" t="n">
-        <v>17990</v>
       </c>
       <c r="D6" t="n">
         <v>14644</v>
@@ -1089,16 +1142,48 @@
         <v>3345</v>
       </c>
       <c r="G6" t="n">
+        <v>2472</v>
+      </c>
+      <c r="H6" t="n">
         <v>3102</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2472</v>
       </c>
       <c r="I6" t="n">
         <v>1847</v>
       </c>
       <c r="J6" t="n">
         <v>750</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B7" t="n">
+        <v>22254</v>
+      </c>
+      <c r="C7" t="n">
+        <v>19280</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10078</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5868</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2963</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2512</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2187</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1853</v>
+      </c>
+      <c r="J7" t="n">
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,13 +1241,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1171,7 +1260,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16882</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="3">
@@ -1183,13 +1272,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1198,7 +1291,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>20069</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="4">
@@ -1210,13 +1303,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1225,7 +1322,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19095</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="5">
@@ -1237,13 +1334,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1252,7 +1353,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>19098</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="6">
@@ -1264,13 +1365,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1279,7 +1384,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20810</v>
+        <v>17990</v>
       </c>
     </row>
     <row r="7">
@@ -1287,7 +1392,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,7 +1415,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>24721</v>
+        <v>22254</v>
       </c>
     </row>
     <row r="8">
@@ -1318,21 +1423,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1341,7 +1442,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>23420</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="9">
@@ -1349,21 +1450,17 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1372,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>19992</v>
+        <v>20069</v>
       </c>
     </row>
     <row r="10">
@@ -1380,21 +1477,17 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1403,7 +1496,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>17987</v>
+        <v>19095</v>
       </c>
     </row>
     <row r="11">
@@ -1411,21 +1504,17 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1434,7 +1523,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>17990</v>
+        <v>19098</v>
       </c>
     </row>
     <row r="12">
@@ -1442,21 +1531,17 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1465,7 +1550,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>13964</v>
+        <v>20810</v>
       </c>
     </row>
     <row r="13">
@@ -1473,21 +1558,17 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1496,7 +1577,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>16681</v>
+        <v>19280</v>
       </c>
     </row>
     <row r="14">
@@ -1504,7 +1585,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1527,7 +1608,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>17645</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="15">
@@ -1535,7 +1616,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1558,7 +1639,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>14882</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="16">
@@ -1566,7 +1647,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1589,7 +1670,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>14644</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="17">
@@ -1597,11 +1678,11 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1620,7 +1701,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>8114</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="18">
@@ -1628,11 +1709,11 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1651,7 +1732,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>8424</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="19">
@@ -1659,11 +1740,11 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1682,7 +1763,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9735</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="20">
@@ -1690,7 +1771,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1713,7 +1794,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8469</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="21">
@@ -1721,7 +1802,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1744,7 +1825,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>8416</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="22">
@@ -1752,21 +1833,21 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1775,7 +1856,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3724</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="23">
@@ -1783,21 +1864,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1806,7 +1887,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3644</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="24">
@@ -1814,21 +1895,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1837,7 +1918,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3194</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="25">
@@ -1845,21 +1926,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1868,7 +1949,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3026</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="26">
@@ -1876,7 +1957,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1899,7 +1980,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3345</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="27">
@@ -1907,21 +1988,21 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1930,7 +2011,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2301</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="28">
@@ -1938,21 +2019,21 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1961,7 +2042,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2554</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="29">
@@ -1969,21 +2050,21 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1992,7 +2073,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2604</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="30">
@@ -2000,21 +2081,21 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2023,7 +2104,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2307</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="31">
@@ -2031,21 +2112,21 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2054,7 +2135,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3102</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="32">
@@ -2217,11 +2298,11 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2240,7 +2321,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2003</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="38">
@@ -2248,16 +2329,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2271,7 +2352,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1820</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="39">
@@ -2279,16 +2360,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2302,7 +2383,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1820</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="40">
@@ -2310,16 +2391,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2333,7 +2414,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2009</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="41">
@@ -2341,16 +2422,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2364,7 +2445,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1847</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="42">
@@ -2372,11 +2453,11 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2395,7 +2476,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>239</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="43">
@@ -2403,11 +2484,11 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2426,7 +2507,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1531</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="44">
@@ -2434,16 +2515,16 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2457,7 +2538,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>306</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="45">
@@ -2465,16 +2546,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2488,7 +2569,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>721</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="46">
@@ -2496,30 +2577,309 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="n">
         <v>46296</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Minas San Francisco</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="G50" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
         <v>750</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -2533,7 +2893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8818,6 +9178,1254 @@
         <v>4327.150000000001</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B242" t="n">
+        <v>2913.65</v>
+      </c>
+      <c r="C242" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="D242" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1206.31</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>4144.39</v>
+      </c>
+      <c r="H242" t="n">
+        <v>4144.39</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46297.02083333334</v>
+      </c>
+      <c r="B243" t="n">
+        <v>2853.09</v>
+      </c>
+      <c r="C243" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1158.03</v>
+      </c>
+      <c r="F243" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="G243" t="n">
+        <v>4048.77</v>
+      </c>
+      <c r="H243" t="n">
+        <v>4032.6</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46297.04166666666</v>
+      </c>
+      <c r="B244" t="n">
+        <v>2718.37</v>
+      </c>
+      <c r="C244" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D244" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1156.96</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>3909.17</v>
+      </c>
+      <c r="H244" t="n">
+        <v>3909.17</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46297.0625</v>
+      </c>
+      <c r="B245" t="n">
+        <v>2632.62</v>
+      </c>
+      <c r="C245" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1166.64</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>3823.5</v>
+      </c>
+      <c r="H245" t="n">
+        <v>3823.5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46297.08333333334</v>
+      </c>
+      <c r="B246" t="n">
+        <v>2556.39</v>
+      </c>
+      <c r="C246" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1168.49</v>
+      </c>
+      <c r="F246" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="G246" t="n">
+        <v>3750.46</v>
+      </c>
+      <c r="H246" t="n">
+        <v>3746.13</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46297.10416666666</v>
+      </c>
+      <c r="B247" t="n">
+        <v>2442.85</v>
+      </c>
+      <c r="C247" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="D247" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1187.34</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>3652.73</v>
+      </c>
+      <c r="H247" t="n">
+        <v>3652.73</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46297.125</v>
+      </c>
+      <c r="B248" t="n">
+        <v>2394.26</v>
+      </c>
+      <c r="C248" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1171.92</v>
+      </c>
+      <c r="F248" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="G248" t="n">
+        <v>3590.08</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3582.79</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46297.14583333334</v>
+      </c>
+      <c r="B249" t="n">
+        <v>2341.25</v>
+      </c>
+      <c r="C249" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1194.6</v>
+      </c>
+      <c r="F249" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G249" t="n">
+        <v>3554.48</v>
+      </c>
+      <c r="H249" t="n">
+        <v>3551.88</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46297.16666666666</v>
+      </c>
+      <c r="B250" t="n">
+        <v>2291.7</v>
+      </c>
+      <c r="C250" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="D250" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1196.42</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>3512.829999999999</v>
+      </c>
+      <c r="H250" t="n">
+        <v>3512.829999999999</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46297.1875</v>
+      </c>
+      <c r="B251" t="n">
+        <v>2286.89</v>
+      </c>
+      <c r="C251" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="D251" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1202.56</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>3513.13</v>
+      </c>
+      <c r="H251" t="n">
+        <v>3513.13</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46297.20833333334</v>
+      </c>
+      <c r="B252" t="n">
+        <v>2300.4</v>
+      </c>
+      <c r="C252" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="D252" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="E252" t="n">
+        <v>1205.16</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>3535.99</v>
+      </c>
+      <c r="H252" t="n">
+        <v>3535.99</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46297.22916666666</v>
+      </c>
+      <c r="B253" t="n">
+        <v>2390.4</v>
+      </c>
+      <c r="C253" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="D253" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1203.15</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>3627.81</v>
+      </c>
+      <c r="H253" t="n">
+        <v>3627.81</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46297.25</v>
+      </c>
+      <c r="B254" t="n">
+        <v>2470.4</v>
+      </c>
+      <c r="C254" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1209.03</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>3696.03</v>
+      </c>
+      <c r="H254" t="n">
+        <v>3696.03</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46297.27083333334</v>
+      </c>
+      <c r="B255" t="n">
+        <v>2272.91</v>
+      </c>
+      <c r="C255" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1208.97</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>3502.18</v>
+      </c>
+      <c r="H255" t="n">
+        <v>3502.18</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46297.29166666666</v>
+      </c>
+      <c r="B256" t="n">
+        <v>2225.47</v>
+      </c>
+      <c r="C256" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="D256" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1206.61</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>3466.33</v>
+      </c>
+      <c r="H256" t="n">
+        <v>3466.33</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46297.3125</v>
+      </c>
+      <c r="B257" t="n">
+        <v>2357.66</v>
+      </c>
+      <c r="C257" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="D257" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1207.66</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>3587.03</v>
+      </c>
+      <c r="H257" t="n">
+        <v>3587.03</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46297.33333333334</v>
+      </c>
+      <c r="B258" t="n">
+        <v>2486.95</v>
+      </c>
+      <c r="C258" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1209.22</v>
+      </c>
+      <c r="F258" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G258" t="n">
+        <v>3718.08</v>
+      </c>
+      <c r="H258" t="n">
+        <v>3715.92</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46297.35416666666</v>
+      </c>
+      <c r="B259" t="n">
+        <v>2665.32</v>
+      </c>
+      <c r="C259" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D259" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1199.35</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>3894.97</v>
+      </c>
+      <c r="H259" t="n">
+        <v>3894.97</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46297.375</v>
+      </c>
+      <c r="B260" t="n">
+        <v>2787.1</v>
+      </c>
+      <c r="C260" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1198.13</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>4004.76</v>
+      </c>
+      <c r="H260" t="n">
+        <v>4004.76</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46297.39583333334</v>
+      </c>
+      <c r="B261" t="n">
+        <v>2886.77</v>
+      </c>
+      <c r="C261" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1196.8</v>
+      </c>
+      <c r="F261" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G261" t="n">
+        <v>4111.12</v>
+      </c>
+      <c r="H261" t="n">
+        <v>4109.03</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46297.41666666666</v>
+      </c>
+      <c r="B262" t="n">
+        <v>2936.15</v>
+      </c>
+      <c r="C262" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1178.02</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>4156.95</v>
+      </c>
+      <c r="H262" t="n">
+        <v>4156.95</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46297.4375</v>
+      </c>
+      <c r="B263" t="n">
+        <v>2976.39</v>
+      </c>
+      <c r="C263" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="D263" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1189.02</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>4234.23</v>
+      </c>
+      <c r="H263" t="n">
+        <v>4234.23</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46297.45833333334</v>
+      </c>
+      <c r="B264" t="n">
+        <v>3016.12</v>
+      </c>
+      <c r="C264" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1191.13</v>
+      </c>
+      <c r="F264" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="G264" t="n">
+        <v>4294.21</v>
+      </c>
+      <c r="H264" t="n">
+        <v>4263.66</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46297.47916666666</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3094.96</v>
+      </c>
+      <c r="C265" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1180.82</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>4339.56</v>
+      </c>
+      <c r="H265" t="n">
+        <v>4339.56</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46297.5</v>
+      </c>
+      <c r="B266" t="n">
+        <v>3097.51</v>
+      </c>
+      <c r="C266" t="n">
+        <v>66.84999999999999</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1160.04</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>4324.4</v>
+      </c>
+      <c r="H266" t="n">
+        <v>4324.4</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46297.52083333334</v>
+      </c>
+      <c r="B267" t="n">
+        <v>3082.11</v>
+      </c>
+      <c r="C267" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1147.39</v>
+      </c>
+      <c r="F267" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="G267" t="n">
+        <v>4308.929999999999</v>
+      </c>
+      <c r="H267" t="n">
+        <v>4295.15</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46297.54166666666</v>
+      </c>
+      <c r="B268" t="n">
+        <v>3102.87</v>
+      </c>
+      <c r="C268" t="n">
+        <v>62.31</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1123.85</v>
+      </c>
+      <c r="F268" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="G268" t="n">
+        <v>4305.259999999999</v>
+      </c>
+      <c r="H268" t="n">
+        <v>4289.03</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B269" t="n">
+        <v>3098.33</v>
+      </c>
+      <c r="C269" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1135.28</v>
+      </c>
+      <c r="F269" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="G269" t="n">
+        <v>4306.339999999999</v>
+      </c>
+      <c r="H269" t="n">
+        <v>4291.36</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46297.58333333334</v>
+      </c>
+      <c r="B270" t="n">
+        <v>3110.88</v>
+      </c>
+      <c r="C270" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1141.46</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>4304.860000000001</v>
+      </c>
+      <c r="H270" t="n">
+        <v>4304.860000000001</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46297.60416666666</v>
+      </c>
+      <c r="B271" t="n">
+        <v>3152.69</v>
+      </c>
+      <c r="C271" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1125.19</v>
+      </c>
+      <c r="F271" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="G271" t="n">
+        <v>4333.56</v>
+      </c>
+      <c r="H271" t="n">
+        <v>4323.79</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46297.625</v>
+      </c>
+      <c r="B272" t="n">
+        <v>3132.07</v>
+      </c>
+      <c r="C272" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1151.52</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>4319.13</v>
+      </c>
+      <c r="H272" t="n">
+        <v>4319.13</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46297.64583333334</v>
+      </c>
+      <c r="B273" t="n">
+        <v>3093.42</v>
+      </c>
+      <c r="C273" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1164.19</v>
+      </c>
+      <c r="F273" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="G273" t="n">
+        <v>4301.790000000001</v>
+      </c>
+      <c r="H273" t="n">
+        <v>4291.940000000001</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46297.66666666666</v>
+      </c>
+      <c r="B274" t="n">
+        <v>3085.14</v>
+      </c>
+      <c r="C274" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1131.89</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>4243.07</v>
+      </c>
+      <c r="H274" t="n">
+        <v>4243.07</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46297.6875</v>
+      </c>
+      <c r="B275" t="n">
+        <v>3037.94</v>
+      </c>
+      <c r="C275" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="D275" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1148.17</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>4214.97</v>
+      </c>
+      <c r="H275" t="n">
+        <v>4214.97</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46297.70833333334</v>
+      </c>
+      <c r="B276" t="n">
+        <v>2979.62</v>
+      </c>
+      <c r="C276" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1156.24</v>
+      </c>
+      <c r="F276" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G276" t="n">
+        <v>4160.81</v>
+      </c>
+      <c r="H276" t="n">
+        <v>4158.64</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46297.72916666666</v>
+      </c>
+      <c r="B277" t="n">
+        <v>2927.01</v>
+      </c>
+      <c r="C277" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1180.89</v>
+      </c>
+      <c r="F277" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G277" t="n">
+        <v>4132.690000000001</v>
+      </c>
+      <c r="H277" t="n">
+        <v>4124.360000000001</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46297.75</v>
+      </c>
+      <c r="B278" t="n">
+        <v>3029.74</v>
+      </c>
+      <c r="C278" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="D278" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1168.37</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>4245.74</v>
+      </c>
+      <c r="H278" t="n">
+        <v>4245.74</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46297.77083333334</v>
+      </c>
+      <c r="B279" t="n">
+        <v>3404.63</v>
+      </c>
+      <c r="C279" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="D279" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1177.11</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>4593.11</v>
+      </c>
+      <c r="H279" t="n">
+        <v>4593.11</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>46297.79166666666</v>
+      </c>
+      <c r="B280" t="n">
+        <v>3437.88</v>
+      </c>
+      <c r="C280" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1177.62</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>4622.98</v>
+      </c>
+      <c r="H280" t="n">
+        <v>4622.98</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>46297.8125</v>
+      </c>
+      <c r="B281" t="n">
+        <v>3451.51</v>
+      </c>
+      <c r="C281" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="D281" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1159.8</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>4639.190000000001</v>
+      </c>
+      <c r="H281" t="n">
+        <v>4639.190000000001</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>46297.83333333334</v>
+      </c>
+      <c r="B282" t="n">
+        <v>3428.16</v>
+      </c>
+      <c r="C282" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>1155.65</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
+        <v>4591.57</v>
+      </c>
+      <c r="H282" t="n">
+        <v>4591.57</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>46297.85416666666</v>
+      </c>
+      <c r="B283" t="n">
+        <v>3385.06</v>
+      </c>
+      <c r="C283" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1156.08</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>4547.78</v>
+      </c>
+      <c r="H283" t="n">
+        <v>4547.78</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>46297.875</v>
+      </c>
+      <c r="B284" t="n">
+        <v>3294.64</v>
+      </c>
+      <c r="C284" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1176.15</v>
+      </c>
+      <c r="F284" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="G284" t="n">
+        <v>4505.47</v>
+      </c>
+      <c r="H284" t="n">
+        <v>4477.33</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>46297.89583333334</v>
+      </c>
+      <c r="B285" t="n">
+        <v>3216.03</v>
+      </c>
+      <c r="C285" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1173.03</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>4397.690000000001</v>
+      </c>
+      <c r="H285" t="n">
+        <v>4397.690000000001</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>46297.91666666666</v>
+      </c>
+      <c r="B286" t="n">
+        <v>3121.13</v>
+      </c>
+      <c r="C286" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1176.95</v>
+      </c>
+      <c r="F286" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="G286" t="n">
+        <v>4312.89</v>
+      </c>
+      <c r="H286" t="n">
+        <v>4307.940000000001</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>46297.9375</v>
+      </c>
+      <c r="B287" t="n">
+        <v>2982.54</v>
+      </c>
+      <c r="C287" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1196.59</v>
+      </c>
+      <c r="F287" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G287" t="n">
+        <v>4192.62</v>
+      </c>
+      <c r="H287" t="n">
+        <v>4190.39</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>46297.95833333334</v>
+      </c>
+      <c r="B288" t="n">
+        <v>2873.65</v>
+      </c>
+      <c r="C288" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1196.81</v>
+      </c>
+      <c r="F288" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="G288" t="n">
+        <v>4087.41</v>
+      </c>
+      <c r="H288" t="n">
+        <v>4080.19</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>46297.97916666666</v>
+      </c>
+      <c r="B289" t="n">
+        <v>2724.43</v>
+      </c>
+      <c r="C289" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="D289" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1196.26</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="n">
+        <v>3934.95</v>
+      </c>
+      <c r="H289" t="n">
+        <v>3934.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,59 @@
         <v>0.004</v>
       </c>
       <c r="Q7" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93081</v>
+      </c>
+      <c r="C8" t="n">
+        <v>65572</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26888</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24045</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2843</v>
+      </c>
+      <c r="G8" t="n">
+        <v>568</v>
+      </c>
+      <c r="H8" t="n">
+        <v>54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>84</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.878</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.732</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -939,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,14 +1018,14 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Delsitanisagua</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Sopladora</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Delsitanisagua</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>San Francisco</t>
@@ -980,17 +1033,17 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Mazar</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Agoyán</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Minas San Francisco</t>
         </is>
       </c>
     </row>
@@ -1008,22 +1061,22 @@
         <v>13964</v>
       </c>
       <c r="E2" t="n">
+        <v>3724</v>
+      </c>
+      <c r="F2" t="n">
         <v>8114</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3724</v>
       </c>
       <c r="G2" t="n">
         <v>2768</v>
       </c>
       <c r="H2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="I2" t="n">
+        <v>239</v>
+      </c>
+      <c r="J2" t="n">
         <v>2301</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="J2" t="n">
-        <v>239</v>
       </c>
     </row>
     <row r="3">
@@ -1040,22 +1093,22 @@
         <v>16681</v>
       </c>
       <c r="E3" t="n">
+        <v>3644</v>
+      </c>
+      <c r="F3" t="n">
         <v>8424</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3644</v>
       </c>
       <c r="G3" t="n">
         <v>2477</v>
       </c>
       <c r="H3" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1531</v>
+      </c>
+      <c r="J3" t="n">
         <v>2554</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1820</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1531</v>
       </c>
     </row>
     <row r="4">
@@ -1072,22 +1125,22 @@
         <v>17645</v>
       </c>
       <c r="E4" t="n">
+        <v>3194</v>
+      </c>
+      <c r="F4" t="n">
         <v>9735</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3194</v>
       </c>
       <c r="G4" t="n">
         <v>2491</v>
       </c>
       <c r="H4" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I4" t="n">
+        <v>306</v>
+      </c>
+      <c r="J4" t="n">
         <v>2604</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1820</v>
-      </c>
-      <c r="J4" t="n">
-        <v>306</v>
       </c>
     </row>
     <row r="5">
@@ -1104,22 +1157,22 @@
         <v>14882</v>
       </c>
       <c r="E5" t="n">
+        <v>3026</v>
+      </c>
+      <c r="F5" t="n">
         <v>8469</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3026</v>
       </c>
       <c r="G5" t="n">
         <v>2773</v>
       </c>
       <c r="H5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="I5" t="n">
+        <v>721</v>
+      </c>
+      <c r="J5" t="n">
         <v>2307</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2009</v>
-      </c>
-      <c r="J5" t="n">
-        <v>721</v>
       </c>
     </row>
     <row r="6">
@@ -1136,22 +1189,22 @@
         <v>14644</v>
       </c>
       <c r="E6" t="n">
+        <v>3345</v>
+      </c>
+      <c r="F6" t="n">
         <v>8416</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3345</v>
       </c>
       <c r="G6" t="n">
         <v>2472</v>
       </c>
       <c r="H6" t="n">
+        <v>1847</v>
+      </c>
+      <c r="I6" t="n">
+        <v>750</v>
+      </c>
+      <c r="J6" t="n">
         <v>3102</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1847</v>
-      </c>
-      <c r="J6" t="n">
-        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -1168,23 +1221,53 @@
         <v>10078</v>
       </c>
       <c r="E7" t="n">
+        <v>2963</v>
+      </c>
+      <c r="F7" t="n">
         <v>5868</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2963</v>
       </c>
       <c r="G7" t="n">
         <v>2512</v>
       </c>
       <c r="H7" t="n">
+        <v>1853</v>
+      </c>
+      <c r="I7" t="n">
+        <v>461</v>
+      </c>
+      <c r="J7" t="n">
         <v>2187</v>
       </c>
-      <c r="I7" t="n">
-        <v>1853</v>
-      </c>
-      <c r="J7" t="n">
-        <v>461</v>
-      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B8" t="n">
+        <v>26473</v>
+      </c>
+      <c r="C8" t="n">
+        <v>21755</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5014</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3431</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2907</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2854</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2034</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1105</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1197,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1423,17 +1506,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1442,7 +1529,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>16882</v>
+        <v>26473</v>
       </c>
     </row>
     <row r="9">
@@ -1450,7 +1537,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,7 +1556,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>20069</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="10">
@@ -1477,7 +1564,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1496,7 +1583,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>19095</v>
+        <v>20069</v>
       </c>
     </row>
     <row r="11">
@@ -1504,7 +1591,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1523,7 +1610,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>19098</v>
+        <v>19095</v>
       </c>
     </row>
     <row r="12">
@@ -1531,7 +1618,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1550,7 +1637,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>20810</v>
+        <v>19098</v>
       </c>
     </row>
     <row r="13">
@@ -1558,7 +1645,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1577,7 +1664,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>19280</v>
+        <v>20810</v>
       </c>
     </row>
     <row r="14">
@@ -1585,21 +1672,17 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1608,7 +1691,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>13964</v>
+        <v>19280</v>
       </c>
     </row>
     <row r="15">
@@ -1616,21 +1699,17 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1639,7 +1718,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>16681</v>
+        <v>21755</v>
       </c>
     </row>
     <row r="16">
@@ -1647,7 +1726,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1670,7 +1749,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>17645</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="17">
@@ -1678,7 +1757,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1701,7 +1780,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>14882</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="18">
@@ -1709,7 +1788,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1732,7 +1811,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>14644</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="19">
@@ -1740,7 +1819,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1763,7 +1842,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>10078</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="20">
@@ -1771,11 +1850,11 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1794,7 +1873,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8114</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="21">
@@ -1802,11 +1881,11 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1825,7 +1904,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>8424</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="22">
@@ -1833,11 +1912,11 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1856,7 +1935,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>9735</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="23">
@@ -1864,21 +1943,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1887,7 +1966,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>8469</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="24">
@@ -1895,21 +1974,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1918,7 +1997,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>8416</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="25">
@@ -1926,21 +2005,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1949,7 +2028,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5868</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="26">
@@ -1957,7 +2036,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1980,7 +2059,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3724</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="27">
@@ -1988,7 +2067,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2011,7 +2090,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3644</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="28">
@@ -2019,7 +2098,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2042,7 +2121,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3194</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="29">
@@ -2050,7 +2129,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2073,7 +2152,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3026</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="30">
@@ -2081,21 +2160,21 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2104,7 +2183,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3345</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="31">
@@ -2112,21 +2191,21 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2135,7 +2214,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2963</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="32">
@@ -2143,16 +2222,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2166,7 +2245,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2768</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="33">
@@ -2174,16 +2253,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2197,7 +2276,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2477</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="34">
@@ -2205,16 +2284,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2228,7 +2307,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2491</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="35">
@@ -2236,16 +2315,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2259,7 +2338,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2773</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="36">
@@ -2267,16 +2346,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2290,7 +2369,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2472</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="37">
@@ -2298,7 +2377,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2321,7 +2400,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2512</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="38">
@@ -2329,16 +2408,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2352,7 +2431,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2301</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="39">
@@ -2360,16 +2439,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2383,7 +2462,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2554</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="40">
@@ -2391,16 +2470,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2414,7 +2493,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2604</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="41">
@@ -2422,16 +2501,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2445,7 +2524,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2307</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="42">
@@ -2453,16 +2532,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2476,7 +2555,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3102</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="43">
@@ -2484,16 +2563,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2507,7 +2586,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2187</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="44">
@@ -2701,16 +2780,16 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2724,7 +2803,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>239</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="51">
@@ -2732,7 +2811,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2755,7 +2834,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1531</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52">
@@ -2763,7 +2842,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2786,7 +2865,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>306</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="53">
@@ -2794,7 +2873,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2817,7 +2896,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>721</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54">
@@ -2825,7 +2904,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2848,7 +2927,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>750</v>
+        <v>721</v>
       </c>
     </row>
     <row r="55">
@@ -2856,30 +2935,278 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Minas San Francisco</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="G56" t="n">
         <v>461</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>2187</v>
       </c>
     </row>
   </sheetData>
@@ -2893,7 +3220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10426,6 +10753,1254 @@
         <v>3934.95</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B290" t="n">
+        <v>2587.74</v>
+      </c>
+      <c r="C290" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1197.94</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>3795.75</v>
+      </c>
+      <c r="H290" t="n">
+        <v>3795.75</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>46298.02083333334</v>
+      </c>
+      <c r="B291" t="n">
+        <v>2559.42</v>
+      </c>
+      <c r="C291" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1143.59</v>
+      </c>
+      <c r="F291" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="G291" t="n">
+        <v>3723.96</v>
+      </c>
+      <c r="H291" t="n">
+        <v>3713.07</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>46298.04166666666</v>
+      </c>
+      <c r="B292" t="n">
+        <v>2476.42</v>
+      </c>
+      <c r="C292" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1140.81</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="n">
+        <v>3631.79</v>
+      </c>
+      <c r="H292" t="n">
+        <v>3631.79</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>46298.0625</v>
+      </c>
+      <c r="B293" t="n">
+        <v>2340.98</v>
+      </c>
+      <c r="C293" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="D293" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1158.02</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>3524.11</v>
+      </c>
+      <c r="H293" t="n">
+        <v>3524.11</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>46298.08333333334</v>
+      </c>
+      <c r="B294" t="n">
+        <v>2337.17</v>
+      </c>
+      <c r="C294" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1141.56</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
+        <v>3490.99</v>
+      </c>
+      <c r="H294" t="n">
+        <v>3490.99</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>46298.10416666666</v>
+      </c>
+      <c r="B295" t="n">
+        <v>2262.97</v>
+      </c>
+      <c r="C295" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="D295" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1143.61</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>3434.47</v>
+      </c>
+      <c r="H295" t="n">
+        <v>3434.47</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>46298.125</v>
+      </c>
+      <c r="B296" t="n">
+        <v>2179.38</v>
+      </c>
+      <c r="C296" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1140.52</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>3329.69</v>
+      </c>
+      <c r="H296" t="n">
+        <v>3329.69</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>46298.14583333334</v>
+      </c>
+      <c r="B297" t="n">
+        <v>2174</v>
+      </c>
+      <c r="C297" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1141.55</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
+        <v>3329</v>
+      </c>
+      <c r="H297" t="n">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>46298.16666666666</v>
+      </c>
+      <c r="B298" t="n">
+        <v>2111.13</v>
+      </c>
+      <c r="C298" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1146.52</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>3289.82</v>
+      </c>
+      <c r="H298" t="n">
+        <v>3289.82</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>46298.1875</v>
+      </c>
+      <c r="B299" t="n">
+        <v>2066.04</v>
+      </c>
+      <c r="C299" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="D299" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1158.53</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>3265</v>
+      </c>
+      <c r="H299" t="n">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>46298.20833333334</v>
+      </c>
+      <c r="B300" t="n">
+        <v>2042.28</v>
+      </c>
+      <c r="C300" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1160.55</v>
+      </c>
+      <c r="F300" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G300" t="n">
+        <v>3227.99</v>
+      </c>
+      <c r="H300" t="n">
+        <v>3224.71</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>46298.22916666666</v>
+      </c>
+      <c r="B301" t="n">
+        <v>2065.63</v>
+      </c>
+      <c r="C301" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1168.13</v>
+      </c>
+      <c r="F301" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="G301" t="n">
+        <v>3260.22</v>
+      </c>
+      <c r="H301" t="n">
+        <v>3246.39</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>46298.25</v>
+      </c>
+      <c r="B302" t="n">
+        <v>2043.37</v>
+      </c>
+      <c r="C302" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1166.36</v>
+      </c>
+      <c r="F302" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="G302" t="n">
+        <v>3230.62</v>
+      </c>
+      <c r="H302" t="n">
+        <v>3220.7</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>46298.27083333334</v>
+      </c>
+      <c r="B303" t="n">
+        <v>1794.19</v>
+      </c>
+      <c r="C303" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1170.25</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>2974.99</v>
+      </c>
+      <c r="H303" t="n">
+        <v>2974.99</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>46298.29166666666</v>
+      </c>
+      <c r="B304" t="n">
+        <v>1875.43</v>
+      </c>
+      <c r="C304" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1149.81</v>
+      </c>
+      <c r="F304" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G304" t="n">
+        <v>3040</v>
+      </c>
+      <c r="H304" t="n">
+        <v>3037.26</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>46298.3125</v>
+      </c>
+      <c r="B305" t="n">
+        <v>2022.03</v>
+      </c>
+      <c r="C305" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D305" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1137.94</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>3179.07</v>
+      </c>
+      <c r="H305" t="n">
+        <v>3179.07</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>46298.33333333334</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2169.4</v>
+      </c>
+      <c r="C306" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1158.77</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>3343.71</v>
+      </c>
+      <c r="H306" t="n">
+        <v>3343.71</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>46298.35416666666</v>
+      </c>
+      <c r="B307" t="n">
+        <v>2320.73</v>
+      </c>
+      <c r="C307" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="D307" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1145.17</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>3491.15</v>
+      </c>
+      <c r="H307" t="n">
+        <v>3491.15</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>46298.375</v>
+      </c>
+      <c r="B308" t="n">
+        <v>2454.5</v>
+      </c>
+      <c r="C308" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1126.53</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>3598.52</v>
+      </c>
+      <c r="H308" t="n">
+        <v>3598.52</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>46298.39583333334</v>
+      </c>
+      <c r="B309" t="n">
+        <v>2600.37</v>
+      </c>
+      <c r="C309" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="D309" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1150.86</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" t="n">
+        <v>3777.8</v>
+      </c>
+      <c r="H309" t="n">
+        <v>3777.8</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>46298.41666666666</v>
+      </c>
+      <c r="B310" t="n">
+        <v>2711.28</v>
+      </c>
+      <c r="C310" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="D310" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1149.83</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" t="n">
+        <v>3882.35</v>
+      </c>
+      <c r="H310" t="n">
+        <v>3882.35</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>46298.4375</v>
+      </c>
+      <c r="B311" t="n">
+        <v>2819.68</v>
+      </c>
+      <c r="C311" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1149.56</v>
+      </c>
+      <c r="F311" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="G311" t="n">
+        <v>4000.26</v>
+      </c>
+      <c r="H311" t="n">
+        <v>3987.58</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>46298.45833333334</v>
+      </c>
+      <c r="B312" t="n">
+        <v>2890.15</v>
+      </c>
+      <c r="C312" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="D312" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1156.08</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="n">
+        <v>4092.39</v>
+      </c>
+      <c r="H312" t="n">
+        <v>4092.39</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>46298.47916666666</v>
+      </c>
+      <c r="B313" t="n">
+        <v>2920.9</v>
+      </c>
+      <c r="C313" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="D313" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1153.95</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
+        <v>4137.81</v>
+      </c>
+      <c r="H313" t="n">
+        <v>4137.81</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>46298.5</v>
+      </c>
+      <c r="B314" t="n">
+        <v>3029.54</v>
+      </c>
+      <c r="C314" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1134.3</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="n">
+        <v>4224.7</v>
+      </c>
+      <c r="H314" t="n">
+        <v>4224.7</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>46298.52083333334</v>
+      </c>
+      <c r="B315" t="n">
+        <v>3058.65</v>
+      </c>
+      <c r="C315" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1132.16</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
+        <v>4258.16</v>
+      </c>
+      <c r="H315" t="n">
+        <v>4258.16</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>46298.54166666666</v>
+      </c>
+      <c r="B316" t="n">
+        <v>3074.19</v>
+      </c>
+      <c r="C316" t="n">
+        <v>72.44</v>
+      </c>
+      <c r="D316" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1125.91</v>
+      </c>
+      <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="n">
+        <v>4286.22</v>
+      </c>
+      <c r="H316" t="n">
+        <v>4286.22</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>46298.5625</v>
+      </c>
+      <c r="B317" t="n">
+        <v>3124.07</v>
+      </c>
+      <c r="C317" t="n">
+        <v>66.01000000000001</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1137.04</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0</v>
+      </c>
+      <c r="G317" t="n">
+        <v>4327.120000000001</v>
+      </c>
+      <c r="H317" t="n">
+        <v>4327.120000000001</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>46298.58333333334</v>
+      </c>
+      <c r="B318" t="n">
+        <v>3134.92</v>
+      </c>
+      <c r="C318" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1142.43</v>
+      </c>
+      <c r="F318" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" t="n">
+        <v>4339.48</v>
+      </c>
+      <c r="H318" t="n">
+        <v>4339.48</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>46298.60416666666</v>
+      </c>
+      <c r="B319" t="n">
+        <v>3145</v>
+      </c>
+      <c r="C319" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1149.14</v>
+      </c>
+      <c r="F319" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="G319" t="n">
+        <v>4371.35</v>
+      </c>
+      <c r="H319" t="n">
+        <v>4352.59</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>46298.625</v>
+      </c>
+      <c r="B320" t="n">
+        <v>3159.11</v>
+      </c>
+      <c r="C320" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1155.44</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>4362.77</v>
+      </c>
+      <c r="H320" t="n">
+        <v>4362.77</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>46298.64583333334</v>
+      </c>
+      <c r="B321" t="n">
+        <v>3159.32</v>
+      </c>
+      <c r="C321" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1135.14</v>
+      </c>
+      <c r="F321" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G321" t="n">
+        <v>4342.23</v>
+      </c>
+      <c r="H321" t="n">
+        <v>4338.27</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>46298.66666666666</v>
+      </c>
+      <c r="B322" t="n">
+        <v>3155.25</v>
+      </c>
+      <c r="C322" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1143.42</v>
+      </c>
+      <c r="F322" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="G322" t="n">
+        <v>4348.150000000001</v>
+      </c>
+      <c r="H322" t="n">
+        <v>4328.1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>46298.6875</v>
+      </c>
+      <c r="B323" t="n">
+        <v>3145.69</v>
+      </c>
+      <c r="C323" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1131.02</v>
+      </c>
+      <c r="F323" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G323" t="n">
+        <v>4310.96</v>
+      </c>
+      <c r="H323" t="n">
+        <v>4301.67</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>46298.70833333334</v>
+      </c>
+      <c r="B324" t="n">
+        <v>3094.67</v>
+      </c>
+      <c r="C324" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="D324" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1129.91</v>
+      </c>
+      <c r="F324" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" t="n">
+        <v>4255.59</v>
+      </c>
+      <c r="H324" t="n">
+        <v>4255.59</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>46298.72916666666</v>
+      </c>
+      <c r="B325" t="n">
+        <v>3131.45</v>
+      </c>
+      <c r="C325" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1129.79</v>
+      </c>
+      <c r="F325" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" t="n">
+        <v>4278.65</v>
+      </c>
+      <c r="H325" t="n">
+        <v>4278.65</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>46298.75</v>
+      </c>
+      <c r="B326" t="n">
+        <v>3231.54</v>
+      </c>
+      <c r="C326" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="D326" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E326" t="n">
+        <v>1128.62</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
+        <v>4380.09</v>
+      </c>
+      <c r="H326" t="n">
+        <v>4380.09</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>46298.77083333334</v>
+      </c>
+      <c r="B327" t="n">
+        <v>3521.8</v>
+      </c>
+      <c r="C327" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>1139.96</v>
+      </c>
+      <c r="F327" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G327" t="n">
+        <v>4682.48</v>
+      </c>
+      <c r="H327" t="n">
+        <v>4678.13</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>46298.79166666666</v>
+      </c>
+      <c r="B328" t="n">
+        <v>3645.13</v>
+      </c>
+      <c r="C328" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>1093.36</v>
+      </c>
+      <c r="F328" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" t="n">
+        <v>4750.94</v>
+      </c>
+      <c r="H328" t="n">
+        <v>4750.94</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>46298.8125</v>
+      </c>
+      <c r="B329" t="n">
+        <v>3604.93</v>
+      </c>
+      <c r="C329" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D329" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E329" t="n">
+        <v>1119.75</v>
+      </c>
+      <c r="F329" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" t="n">
+        <v>4738.09</v>
+      </c>
+      <c r="H329" t="n">
+        <v>4738.09</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>46298.83333333334</v>
+      </c>
+      <c r="B330" t="n">
+        <v>3553.07</v>
+      </c>
+      <c r="C330" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="D330" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1124.23</v>
+      </c>
+      <c r="F330" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" t="n">
+        <v>4699.780000000001</v>
+      </c>
+      <c r="H330" t="n">
+        <v>4699.780000000001</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n">
+        <v>46298.85416666666</v>
+      </c>
+      <c r="B331" t="n">
+        <v>3514.26</v>
+      </c>
+      <c r="C331" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D331" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1130.14</v>
+      </c>
+      <c r="F331" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" t="n">
+        <v>4658.84</v>
+      </c>
+      <c r="H331" t="n">
+        <v>4658.84</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n">
+        <v>46298.875</v>
+      </c>
+      <c r="B332" t="n">
+        <v>3447.11</v>
+      </c>
+      <c r="C332" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1146.65</v>
+      </c>
+      <c r="F332" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="G332" t="n">
+        <v>4617.74</v>
+      </c>
+      <c r="H332" t="n">
+        <v>4602.15</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n">
+        <v>46298.89583333334</v>
+      </c>
+      <c r="B333" t="n">
+        <v>3395.26</v>
+      </c>
+      <c r="C333" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1159.37</v>
+      </c>
+      <c r="F333" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G333" t="n">
+        <v>4563.06</v>
+      </c>
+      <c r="H333" t="n">
+        <v>4561.09</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n">
+        <v>46298.91666666666</v>
+      </c>
+      <c r="B334" t="n">
+        <v>3293.98</v>
+      </c>
+      <c r="C334" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1150.2</v>
+      </c>
+      <c r="F334" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="G334" t="n">
+        <v>4470.06</v>
+      </c>
+      <c r="H334" t="n">
+        <v>4449.65</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n">
+        <v>46298.9375</v>
+      </c>
+      <c r="B335" t="n">
+        <v>3241.06</v>
+      </c>
+      <c r="C335" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1150.74</v>
+      </c>
+      <c r="F335" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G335" t="n">
+        <v>4407.9</v>
+      </c>
+      <c r="H335" t="n">
+        <v>4397.62</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="n">
+        <v>46298.95833333334</v>
+      </c>
+      <c r="B336" t="n">
+        <v>3099.61</v>
+      </c>
+      <c r="C336" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="D336" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E336" t="n">
+        <v>1154.6</v>
+      </c>
+      <c r="F336" t="n">
+        <v>0</v>
+      </c>
+      <c r="G336" t="n">
+        <v>4262.200000000001</v>
+      </c>
+      <c r="H336" t="n">
+        <v>4262.200000000001</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="n">
+        <v>46298.97916666666</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2971.68</v>
+      </c>
+      <c r="C337" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1149.29</v>
+      </c>
+      <c r="F337" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="G337" t="n">
+        <v>4145.469999999999</v>
+      </c>
+      <c r="H337" t="n">
+        <v>4126.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,59 @@
       </c>
       <c r="Q8" t="n">
         <v>0.004</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102636</v>
+      </c>
+      <c r="C9" t="n">
+        <v>75717</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26193</v>
+      </c>
+      <c r="E9" t="n">
+        <v>23371</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2822</v>
+      </c>
+      <c r="G9" t="n">
+        <v>643</v>
+      </c>
+      <c r="H9" t="n">
+        <v>83</v>
+      </c>
+      <c r="I9" t="n">
+        <v>72</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.276</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.155</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.003</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,17 +1071,17 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Sopladora</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Delsitanisagua</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sopladora</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1061,13 +1114,13 @@
         <v>13964</v>
       </c>
       <c r="E2" t="n">
+        <v>8114</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="G2" t="n">
         <v>3724</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8114</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2768</v>
       </c>
       <c r="H2" t="n">
         <v>2003</v>
@@ -1093,13 +1146,13 @@
         <v>16681</v>
       </c>
       <c r="E3" t="n">
+        <v>8424</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2477</v>
+      </c>
+      <c r="G3" t="n">
         <v>3644</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8424</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2477</v>
       </c>
       <c r="H3" t="n">
         <v>1820</v>
@@ -1125,13 +1178,13 @@
         <v>17645</v>
       </c>
       <c r="E4" t="n">
+        <v>9735</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2491</v>
+      </c>
+      <c r="G4" t="n">
         <v>3194</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9735</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2491</v>
       </c>
       <c r="H4" t="n">
         <v>1820</v>
@@ -1157,13 +1210,13 @@
         <v>14882</v>
       </c>
       <c r="E5" t="n">
+        <v>8469</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2773</v>
+      </c>
+      <c r="G5" t="n">
         <v>3026</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8469</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2773</v>
       </c>
       <c r="H5" t="n">
         <v>2009</v>
@@ -1189,13 +1242,13 @@
         <v>14644</v>
       </c>
       <c r="E6" t="n">
+        <v>8416</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2472</v>
+      </c>
+      <c r="G6" t="n">
         <v>3345</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8416</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2472</v>
       </c>
       <c r="H6" t="n">
         <v>1847</v>
@@ -1221,13 +1274,13 @@
         <v>10078</v>
       </c>
       <c r="E7" t="n">
+        <v>5868</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2512</v>
+      </c>
+      <c r="G7" t="n">
         <v>2963</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5868</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2512</v>
       </c>
       <c r="H7" t="n">
         <v>1853</v>
@@ -1253,13 +1306,13 @@
         <v>5014</v>
       </c>
       <c r="E8" t="n">
+        <v>2907</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2854</v>
+      </c>
+      <c r="G8" t="n">
         <v>3431</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2907</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2854</v>
       </c>
       <c r="H8" t="n">
         <v>2034</v>
@@ -1268,6 +1321,38 @@
         <v>1105</v>
       </c>
       <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B9" t="n">
+        <v>23346</v>
+      </c>
+      <c r="C9" t="n">
+        <v>19704</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14358</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8041</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2801</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2788</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1488</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1164</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1280,7 +1365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,17 +1622,21 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1556,7 +1645,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>16882</v>
+        <v>23346</v>
       </c>
     </row>
     <row r="10">
@@ -1564,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,7 +1672,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>20069</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="11">
@@ -1591,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,7 +1699,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>19095</v>
+        <v>20069</v>
       </c>
     </row>
     <row r="12">
@@ -1618,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1637,7 +1726,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>19098</v>
+        <v>19095</v>
       </c>
     </row>
     <row r="13">
@@ -1645,7 +1734,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1664,7 +1753,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>20810</v>
+        <v>19098</v>
       </c>
     </row>
     <row r="14">
@@ -1672,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1691,7 +1780,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>19280</v>
+        <v>20810</v>
       </c>
     </row>
     <row r="15">
@@ -1699,7 +1788,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1718,7 +1807,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>21755</v>
+        <v>19280</v>
       </c>
     </row>
     <row r="16">
@@ -1726,21 +1815,17 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1749,7 +1834,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>13964</v>
+        <v>21755</v>
       </c>
     </row>
     <row r="17">
@@ -1757,21 +1842,17 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1780,7 +1861,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>16681</v>
+        <v>19704</v>
       </c>
     </row>
     <row r="18">
@@ -1788,7 +1869,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1811,7 +1892,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>17645</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="19">
@@ -1819,7 +1900,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1842,7 +1923,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>14882</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="20">
@@ -1850,7 +1931,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1873,7 +1954,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>14644</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="21">
@@ -1881,7 +1962,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1904,7 +1985,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>10078</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="22">
@@ -1912,7 +1993,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1935,7 +2016,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5014</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="23">
@@ -1943,21 +2024,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1966,7 +2047,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3724</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="24">
@@ -1974,21 +2055,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1997,7 +2078,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3644</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="25">
@@ -2005,21 +2086,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2028,7 +2109,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3194</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="26">
@@ -2036,21 +2117,21 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2059,7 +2140,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3026</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="27">
@@ -2067,21 +2148,21 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2090,7 +2171,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3345</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="28">
@@ -2098,21 +2179,21 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2121,7 +2202,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2963</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="29">
@@ -2129,21 +2210,21 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2152,7 +2233,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3431</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="30">
@@ -2160,7 +2241,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2183,7 +2264,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>8114</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="31">
@@ -2191,7 +2272,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2214,7 +2295,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8424</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="32">
@@ -2222,7 +2303,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2245,7 +2326,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9735</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="33">
@@ -2253,7 +2334,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2276,7 +2357,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8469</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="34">
@@ -2284,16 +2365,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2307,7 +2388,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>8416</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="35">
@@ -2315,16 +2396,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2338,7 +2419,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>5868</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="36">
@@ -2346,16 +2427,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2369,7 +2450,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2907</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="37">
@@ -2377,7 +2458,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2400,7 +2481,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2768</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="38">
@@ -2408,7 +2489,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2431,7 +2512,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2477</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="39">
@@ -2439,7 +2520,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2462,7 +2543,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2491</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="40">
@@ -2470,7 +2551,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2493,7 +2574,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2773</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="41">
@@ -2501,7 +2582,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2524,7 +2605,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2472</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="42">
@@ -2532,21 +2613,21 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2555,7 +2636,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2512</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="43">
@@ -2563,21 +2644,21 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46298</v>
+        <v>46293</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2586,7 +2667,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2854</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="44">
@@ -2594,21 +2675,21 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2617,7 +2698,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2003</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="45">
@@ -2625,21 +2706,21 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2648,7 +2729,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1820</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="46">
@@ -2656,21 +2737,21 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2679,7 +2760,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1820</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="47">
@@ -2687,21 +2768,21 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2710,7 +2791,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2009</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="48">
@@ -2718,21 +2799,21 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2741,7 +2822,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1847</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="49">
@@ -2749,21 +2830,21 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2772,7 +2853,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1853</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="50">
@@ -2780,7 +2861,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2803,7 +2884,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2034</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="51">
@@ -2811,16 +2892,16 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2834,7 +2915,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>239</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="52">
@@ -2842,16 +2923,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2865,7 +2946,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1531</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="53">
@@ -2873,16 +2954,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2896,7 +2977,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>306</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="54">
@@ -2904,16 +2985,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2927,7 +3008,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>721</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="55">
@@ -2935,16 +3016,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2958,7 +3039,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>750</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="56">
@@ -2966,16 +3047,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2989,7 +3070,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>461</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="57">
@@ -2997,16 +3078,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3020,7 +3101,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1105</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="58">
@@ -3032,7 +3113,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3051,7 +3132,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2301</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59">
@@ -3063,7 +3144,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3082,7 +3163,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2554</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="60">
@@ -3094,7 +3175,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3113,7 +3194,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2604</v>
+        <v>306</v>
       </c>
     </row>
     <row r="61">
@@ -3125,7 +3206,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3144,7 +3225,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2307</v>
+        <v>721</v>
       </c>
     </row>
     <row r="62">
@@ -3156,7 +3237,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3175,7 +3256,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3102</v>
+        <v>750</v>
       </c>
     </row>
     <row r="63">
@@ -3187,26 +3268,305 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>Mazar</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="G66" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
         <v>2187</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -3220,7 +3580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12001,6 +12361,1254 @@
         <v>4126.44</v>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B338" t="n">
+        <v>2843.21</v>
+      </c>
+      <c r="C338" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>1151.31</v>
+      </c>
+      <c r="F338" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G338" t="n">
+        <v>4011.94</v>
+      </c>
+      <c r="H338" t="n">
+        <v>4009.85</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B339" t="n">
+        <v>2737.79</v>
+      </c>
+      <c r="C339" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1112.43</v>
+      </c>
+      <c r="F339" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G339" t="n">
+        <v>3873.33</v>
+      </c>
+      <c r="H339" t="n">
+        <v>3864.01</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B340" t="n">
+        <v>2619.44</v>
+      </c>
+      <c r="C340" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1131.4</v>
+      </c>
+      <c r="F340" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="G340" t="n">
+        <v>3783.09</v>
+      </c>
+      <c r="H340" t="n">
+        <v>3766.25</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="n">
+        <v>46300.0625</v>
+      </c>
+      <c r="B341" t="n">
+        <v>2582.42</v>
+      </c>
+      <c r="C341" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1124.47</v>
+      </c>
+      <c r="F341" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G341" t="n">
+        <v>3725.01</v>
+      </c>
+      <c r="H341" t="n">
+        <v>3723.45</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B342" t="n">
+        <v>2502.34</v>
+      </c>
+      <c r="C342" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="D342" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1119.39</v>
+      </c>
+      <c r="F342" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
+        <v>3640.76</v>
+      </c>
+      <c r="H342" t="n">
+        <v>3640.76</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="n">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B343" t="n">
+        <v>2420.73</v>
+      </c>
+      <c r="C343" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="D343" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1133.13</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>3579.09</v>
+      </c>
+      <c r="H343" t="n">
+        <v>3579.09</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="n">
+        <v>46300.125</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2343.74</v>
+      </c>
+      <c r="C344" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>1140.76</v>
+      </c>
+      <c r="F344" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" t="n">
+        <v>3495.61</v>
+      </c>
+      <c r="H344" t="n">
+        <v>3495.61</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="n">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B345" t="n">
+        <v>2277.11</v>
+      </c>
+      <c r="C345" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1141.56</v>
+      </c>
+      <c r="F345" t="n">
+        <v>0</v>
+      </c>
+      <c r="G345" t="n">
+        <v>3426.75</v>
+      </c>
+      <c r="H345" t="n">
+        <v>3426.75</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="n">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2287.12</v>
+      </c>
+      <c r="C346" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1118.22</v>
+      </c>
+      <c r="F346" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="G346" t="n">
+        <v>3423.15</v>
+      </c>
+      <c r="H346" t="n">
+        <v>3414.13</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="n">
+        <v>46300.1875</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2270.12</v>
+      </c>
+      <c r="C347" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D347" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1144.91</v>
+      </c>
+      <c r="F347" t="n">
+        <v>0</v>
+      </c>
+      <c r="G347" t="n">
+        <v>3435.84</v>
+      </c>
+      <c r="H347" t="n">
+        <v>3435.84</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="n">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2283.31</v>
+      </c>
+      <c r="C348" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="D348" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1154.38</v>
+      </c>
+      <c r="F348" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" t="n">
+        <v>3451.04</v>
+      </c>
+      <c r="H348" t="n">
+        <v>3451.04</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="n">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B349" t="n">
+        <v>2407.99</v>
+      </c>
+      <c r="C349" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>1147.94</v>
+      </c>
+      <c r="F349" t="n">
+        <v>0</v>
+      </c>
+      <c r="G349" t="n">
+        <v>3569.09</v>
+      </c>
+      <c r="H349" t="n">
+        <v>3569.09</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="n">
+        <v>46300.25</v>
+      </c>
+      <c r="B350" t="n">
+        <v>2290.49</v>
+      </c>
+      <c r="C350" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D350" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1151.96</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>3457.44</v>
+      </c>
+      <c r="H350" t="n">
+        <v>3457.44</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="n">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B351" t="n">
+        <v>2186.9</v>
+      </c>
+      <c r="C351" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="D351" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1146.84</v>
+      </c>
+      <c r="F351" t="n">
+        <v>0</v>
+      </c>
+      <c r="G351" t="n">
+        <v>3365.32</v>
+      </c>
+      <c r="H351" t="n">
+        <v>3365.32</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="n">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B352" t="n">
+        <v>2175.21</v>
+      </c>
+      <c r="C352" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1147.97</v>
+      </c>
+      <c r="F352" t="n">
+        <v>11</v>
+      </c>
+      <c r="G352" t="n">
+        <v>3345.3</v>
+      </c>
+      <c r="H352" t="n">
+        <v>3334.3</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="n">
+        <v>46300.3125</v>
+      </c>
+      <c r="B353" t="n">
+        <v>2404.92</v>
+      </c>
+      <c r="C353" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1137.25</v>
+      </c>
+      <c r="F353" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G353" t="n">
+        <v>3556.67</v>
+      </c>
+      <c r="H353" t="n">
+        <v>3553.36</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="n">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B354" t="n">
+        <v>2613.24</v>
+      </c>
+      <c r="C354" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1139.33</v>
+      </c>
+      <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
+        <v>3764.42</v>
+      </c>
+      <c r="H354" t="n">
+        <v>3764.42</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="n">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B355" t="n">
+        <v>2808.34</v>
+      </c>
+      <c r="C355" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1135.4</v>
+      </c>
+      <c r="F355" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="G355" t="n">
+        <v>3980.15</v>
+      </c>
+      <c r="H355" t="n">
+        <v>3957.82</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="n">
+        <v>46300.375</v>
+      </c>
+      <c r="B356" t="n">
+        <v>2983.46</v>
+      </c>
+      <c r="C356" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="D356" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1129.4</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>4138</v>
+      </c>
+      <c r="H356" t="n">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="n">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B357" t="n">
+        <v>3110.4</v>
+      </c>
+      <c r="C357" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="D357" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1122.91</v>
+      </c>
+      <c r="F357" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" t="n">
+        <v>4259.25</v>
+      </c>
+      <c r="H357" t="n">
+        <v>4259.25</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="n">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B358" t="n">
+        <v>3284.64</v>
+      </c>
+      <c r="C358" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="D358" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="E358" t="n">
+        <v>1104.21</v>
+      </c>
+      <c r="F358" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" t="n">
+        <v>4414.52</v>
+      </c>
+      <c r="H358" t="n">
+        <v>4414.52</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="n">
+        <v>46300.4375</v>
+      </c>
+      <c r="B359" t="n">
+        <v>3371.06</v>
+      </c>
+      <c r="C359" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1104.61</v>
+      </c>
+      <c r="F359" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" t="n">
+        <v>4500.17</v>
+      </c>
+      <c r="H359" t="n">
+        <v>4500.17</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="n">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B360" t="n">
+        <v>3450.3</v>
+      </c>
+      <c r="C360" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1094.89</v>
+      </c>
+      <c r="F360" t="n">
+        <v>0</v>
+      </c>
+      <c r="G360" t="n">
+        <v>4590.42</v>
+      </c>
+      <c r="H360" t="n">
+        <v>4590.42</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="n">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B361" t="n">
+        <v>3541.25</v>
+      </c>
+      <c r="C361" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1090.53</v>
+      </c>
+      <c r="F361" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" t="n">
+        <v>4686.76</v>
+      </c>
+      <c r="H361" t="n">
+        <v>4686.76</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>46300.5</v>
+      </c>
+      <c r="B362" t="n">
+        <v>3550.45</v>
+      </c>
+      <c r="C362" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="D362" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1085.26</v>
+      </c>
+      <c r="F362" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" t="n">
+        <v>4719.86</v>
+      </c>
+      <c r="H362" t="n">
+        <v>4719.86</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B363" t="n">
+        <v>3589</v>
+      </c>
+      <c r="C363" t="n">
+        <v>70.68000000000001</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1089.1</v>
+      </c>
+      <c r="F363" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G363" t="n">
+        <v>4750.84</v>
+      </c>
+      <c r="H363" t="n">
+        <v>4748.78</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B364" t="n">
+        <v>3638.6</v>
+      </c>
+      <c r="C364" t="n">
+        <v>68.31</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0</v>
+      </c>
+      <c r="E364" t="n">
+        <v>1085.43</v>
+      </c>
+      <c r="F364" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" t="n">
+        <v>4792.34</v>
+      </c>
+      <c r="H364" t="n">
+        <v>4792.34</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B365" t="n">
+        <v>3714.46</v>
+      </c>
+      <c r="C365" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>1093.49</v>
+      </c>
+      <c r="F365" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="G365" t="n">
+        <v>4880.84</v>
+      </c>
+      <c r="H365" t="n">
+        <v>4875.27</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="n">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B366" t="n">
+        <v>3751.34</v>
+      </c>
+      <c r="C366" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>1085.1</v>
+      </c>
+      <c r="F366" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="G366" t="n">
+        <v>4909.96</v>
+      </c>
+      <c r="H366" t="n">
+        <v>4907.07</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="n">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B367" t="n">
+        <v>3807.08</v>
+      </c>
+      <c r="C367" t="n">
+        <v>68.81999999999999</v>
+      </c>
+      <c r="D367" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1091.44</v>
+      </c>
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>4969.49</v>
+      </c>
+      <c r="H367" t="n">
+        <v>4969.49</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n">
+        <v>46300.625</v>
+      </c>
+      <c r="B368" t="n">
+        <v>3839.78</v>
+      </c>
+      <c r="C368" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" t="n">
+        <v>1091.31</v>
+      </c>
+      <c r="F368" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G368" t="n">
+        <v>5002.820000000001</v>
+      </c>
+      <c r="H368" t="n">
+        <v>4999.120000000001</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B369" t="n">
+        <v>3865.18</v>
+      </c>
+      <c r="C369" t="n">
+        <v>67.45</v>
+      </c>
+      <c r="D369" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="E369" t="n">
+        <v>1086.67</v>
+      </c>
+      <c r="F369" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" t="n">
+        <v>5023.76</v>
+      </c>
+      <c r="H369" t="n">
+        <v>5023.76</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B370" t="n">
+        <v>3838.32</v>
+      </c>
+      <c r="C370" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="D370" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E370" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="n">
+        <v>4987.91</v>
+      </c>
+      <c r="H370" t="n">
+        <v>4987.91</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n">
+        <v>46300.6875</v>
+      </c>
+      <c r="B371" t="n">
+        <v>3767.95</v>
+      </c>
+      <c r="C371" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="D371" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E371" t="n">
+        <v>1103.7</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="n">
+        <v>4929.17</v>
+      </c>
+      <c r="H371" t="n">
+        <v>4929.17</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B372" t="n">
+        <v>3655.26</v>
+      </c>
+      <c r="C372" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="n">
+        <v>1114.72</v>
+      </c>
+      <c r="F372" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="G372" t="n">
+        <v>4821.36</v>
+      </c>
+      <c r="H372" t="n">
+        <v>4814.88</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B373" t="n">
+        <v>3546.46</v>
+      </c>
+      <c r="C373" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="D373" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E373" t="n">
+        <v>1120.64</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="n">
+        <v>4729.3</v>
+      </c>
+      <c r="H373" t="n">
+        <v>4729.3</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>46300.75</v>
+      </c>
+      <c r="B374" t="n">
+        <v>3531.15</v>
+      </c>
+      <c r="C374" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="D374" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="E374" t="n">
+        <v>1118.37</v>
+      </c>
+      <c r="F374" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" t="n">
+        <v>4686.01</v>
+      </c>
+      <c r="H374" t="n">
+        <v>4686.01</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B375" t="n">
+        <v>3968.74</v>
+      </c>
+      <c r="C375" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E375" t="n">
+        <v>1125.52</v>
+      </c>
+      <c r="F375" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" t="n">
+        <v>5129.92</v>
+      </c>
+      <c r="H375" t="n">
+        <v>5129.92</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="n">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B376" t="n">
+        <v>4057.71</v>
+      </c>
+      <c r="C376" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="D376" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="E376" t="n">
+        <v>1127.4</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>5213.889999999999</v>
+      </c>
+      <c r="H376" t="n">
+        <v>5213.889999999999</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="n">
+        <v>46300.8125</v>
+      </c>
+      <c r="B377" t="n">
+        <v>4067.94</v>
+      </c>
+      <c r="C377" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="D377" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E377" t="n">
+        <v>1133.8</v>
+      </c>
+      <c r="F377" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" t="n">
+        <v>5221.97</v>
+      </c>
+      <c r="H377" t="n">
+        <v>5221.97</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B378" t="n">
+        <v>4076.59</v>
+      </c>
+      <c r="C378" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0</v>
+      </c>
+      <c r="E378" t="n">
+        <v>1130.43</v>
+      </c>
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" t="n">
+        <v>5217.820000000001</v>
+      </c>
+      <c r="H378" t="n">
+        <v>5217.820000000001</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="n">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B379" t="n">
+        <v>4073.47</v>
+      </c>
+      <c r="C379" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>1105.38</v>
+      </c>
+      <c r="F379" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G379" t="n">
+        <v>5190.74</v>
+      </c>
+      <c r="H379" t="n">
+        <v>5188.21</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>46300.875</v>
+      </c>
+      <c r="B380" t="n">
+        <v>4032.72</v>
+      </c>
+      <c r="C380" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="n">
+        <v>1092.23</v>
+      </c>
+      <c r="F380" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="G380" t="n">
+        <v>5154.299999999999</v>
+      </c>
+      <c r="H380" t="n">
+        <v>5131.94</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B381" t="n">
+        <v>3939.66</v>
+      </c>
+      <c r="C381" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" t="n">
+        <v>1082.88</v>
+      </c>
+      <c r="F381" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G381" t="n">
+        <v>5034.990000000001</v>
+      </c>
+      <c r="H381" t="n">
+        <v>5029.190000000001</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B382" t="n">
+        <v>3820.14</v>
+      </c>
+      <c r="C382" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0</v>
+      </c>
+      <c r="E382" t="n">
+        <v>1077.73</v>
+      </c>
+      <c r="F382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" t="n">
+        <v>4904.219999999999</v>
+      </c>
+      <c r="H382" t="n">
+        <v>4904.219999999999</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>46300.9375</v>
+      </c>
+      <c r="B383" t="n">
+        <v>3640.04</v>
+      </c>
+      <c r="C383" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D383" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E383" t="n">
+        <v>1087.49</v>
+      </c>
+      <c r="F383" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" t="n">
+        <v>4736.03</v>
+      </c>
+      <c r="H383" t="n">
+        <v>4736.03</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B384" t="n">
+        <v>3485.94</v>
+      </c>
+      <c r="C384" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0</v>
+      </c>
+      <c r="E384" t="n">
+        <v>1086.96</v>
+      </c>
+      <c r="F384" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="G384" t="n">
+        <v>4597.87</v>
+      </c>
+      <c r="H384" t="n">
+        <v>4579.24</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B385" t="n">
+        <v>3315.66</v>
+      </c>
+      <c r="C385" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="D385" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E385" t="n">
+        <v>1074.95</v>
+      </c>
+      <c r="F385" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" t="n">
+        <v>4399.18</v>
+      </c>
+      <c r="H385" t="n">
+        <v>4399.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,6 +1031,59 @@
         <v>0.003</v>
       </c>
       <c r="Q9" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103966</v>
+      </c>
+      <c r="C10" t="n">
+        <v>77991</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25358</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22541</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2816</v>
+      </c>
+      <c r="G10" t="n">
+        <v>567</v>
+      </c>
+      <c r="H10" t="n">
+        <v>51</v>
+      </c>
+      <c r="I10" t="n">
+        <v>79</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.332</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -1045,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,14 +1114,14 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Otras Hidro</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Paute</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
           <t>Sopladora</t>
@@ -1076,27 +1129,27 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Delsitanisagua</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Delsitanisagua</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Agoyán</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Minas San Francisco</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Mazar</t>
         </is>
       </c>
     </row>
@@ -1108,28 +1161,28 @@
         <v>24721</v>
       </c>
       <c r="C2" t="n">
+        <v>13964</v>
+      </c>
+      <c r="D2" t="n">
         <v>16882</v>
-      </c>
-      <c r="D2" t="n">
-        <v>13964</v>
       </c>
       <c r="E2" t="n">
         <v>8114</v>
       </c>
       <c r="F2" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G2" t="n">
         <v>2768</v>
       </c>
-      <c r="G2" t="n">
-        <v>3724</v>
-      </c>
       <c r="H2" t="n">
+        <v>2301</v>
+      </c>
+      <c r="I2" t="n">
         <v>2003</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>239</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2301</v>
       </c>
     </row>
     <row r="3">
@@ -1140,28 +1193,28 @@
         <v>23420</v>
       </c>
       <c r="C3" t="n">
+        <v>16681</v>
+      </c>
+      <c r="D3" t="n">
         <v>20069</v>
-      </c>
-      <c r="D3" t="n">
-        <v>16681</v>
       </c>
       <c r="E3" t="n">
         <v>8424</v>
       </c>
       <c r="F3" t="n">
+        <v>3644</v>
+      </c>
+      <c r="G3" t="n">
         <v>2477</v>
       </c>
-      <c r="G3" t="n">
-        <v>3644</v>
-      </c>
       <c r="H3" t="n">
+        <v>2554</v>
+      </c>
+      <c r="I3" t="n">
         <v>1820</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1531</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2554</v>
       </c>
     </row>
     <row r="4">
@@ -1172,28 +1225,28 @@
         <v>19992</v>
       </c>
       <c r="C4" t="n">
+        <v>17645</v>
+      </c>
+      <c r="D4" t="n">
         <v>19095</v>
-      </c>
-      <c r="D4" t="n">
-        <v>17645</v>
       </c>
       <c r="E4" t="n">
         <v>9735</v>
       </c>
       <c r="F4" t="n">
+        <v>3194</v>
+      </c>
+      <c r="G4" t="n">
         <v>2491</v>
       </c>
-      <c r="G4" t="n">
-        <v>3194</v>
-      </c>
       <c r="H4" t="n">
+        <v>2604</v>
+      </c>
+      <c r="I4" t="n">
         <v>1820</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>306</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2604</v>
       </c>
     </row>
     <row r="5">
@@ -1204,28 +1257,28 @@
         <v>17987</v>
       </c>
       <c r="C5" t="n">
+        <v>14882</v>
+      </c>
+      <c r="D5" t="n">
         <v>19098</v>
-      </c>
-      <c r="D5" t="n">
-        <v>14882</v>
       </c>
       <c r="E5" t="n">
         <v>8469</v>
       </c>
       <c r="F5" t="n">
+        <v>3026</v>
+      </c>
+      <c r="G5" t="n">
         <v>2773</v>
       </c>
-      <c r="G5" t="n">
-        <v>3026</v>
-      </c>
       <c r="H5" t="n">
+        <v>2307</v>
+      </c>
+      <c r="I5" t="n">
         <v>2009</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>721</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2307</v>
       </c>
     </row>
     <row r="6">
@@ -1236,28 +1289,28 @@
         <v>17990</v>
       </c>
       <c r="C6" t="n">
+        <v>14644</v>
+      </c>
+      <c r="D6" t="n">
         <v>20810</v>
-      </c>
-      <c r="D6" t="n">
-        <v>14644</v>
       </c>
       <c r="E6" t="n">
         <v>8416</v>
       </c>
       <c r="F6" t="n">
+        <v>3345</v>
+      </c>
+      <c r="G6" t="n">
         <v>2472</v>
       </c>
-      <c r="G6" t="n">
-        <v>3345</v>
-      </c>
       <c r="H6" t="n">
+        <v>3102</v>
+      </c>
+      <c r="I6" t="n">
         <v>1847</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>750</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3102</v>
       </c>
     </row>
     <row r="7">
@@ -1268,28 +1321,28 @@
         <v>22254</v>
       </c>
       <c r="C7" t="n">
+        <v>10078</v>
+      </c>
+      <c r="D7" t="n">
         <v>19280</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10078</v>
       </c>
       <c r="E7" t="n">
         <v>5868</v>
       </c>
       <c r="F7" t="n">
+        <v>2963</v>
+      </c>
+      <c r="G7" t="n">
         <v>2512</v>
       </c>
-      <c r="G7" t="n">
-        <v>2963</v>
-      </c>
       <c r="H7" t="n">
+        <v>2187</v>
+      </c>
+      <c r="I7" t="n">
         <v>1853</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>461</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2187</v>
       </c>
     </row>
     <row r="8">
@@ -1300,27 +1353,27 @@
         <v>26473</v>
       </c>
       <c r="C8" t="n">
+        <v>5014</v>
+      </c>
+      <c r="D8" t="n">
         <v>21755</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5014</v>
       </c>
       <c r="E8" t="n">
         <v>2907</v>
       </c>
       <c r="F8" t="n">
+        <v>3431</v>
+      </c>
+      <c r="G8" t="n">
         <v>2854</v>
       </c>
-      <c r="G8" t="n">
-        <v>3431</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
         <v>2034</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1105</v>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1330,28 +1383,60 @@
         <v>23346</v>
       </c>
       <c r="C9" t="n">
+        <v>14358</v>
+      </c>
+      <c r="D9" t="n">
         <v>19704</v>
-      </c>
-      <c r="D9" t="n">
-        <v>14358</v>
       </c>
       <c r="E9" t="n">
         <v>8041</v>
       </c>
       <c r="F9" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G9" t="n">
         <v>2801</v>
       </c>
-      <c r="G9" t="n">
-        <v>2788</v>
-      </c>
       <c r="H9" t="n">
+        <v>1164</v>
+      </c>
+      <c r="I9" t="n">
         <v>2027</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1488</v>
       </c>
-      <c r="J9" t="n">
-        <v>1164</v>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B10" t="n">
+        <v>19157</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18959</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18740</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9960</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2675</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2566</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2157</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1907</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1870</v>
       </c>
     </row>
   </sheetData>
@@ -1365,7 +1450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,17 +1738,21 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46291</v>
+        <v>46301</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1672,7 +1761,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>16882</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="11">
@@ -1680,17 +1769,21 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1699,7 +1792,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>20069</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="12">
@@ -1707,17 +1800,21 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1726,7 +1823,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>19095</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="13">
@@ -1734,17 +1831,21 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1753,7 +1854,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>19098</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="14">
@@ -1761,17 +1862,21 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1780,7 +1885,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>20810</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="15">
@@ -1788,17 +1893,21 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1807,7 +1916,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19280</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="16">
@@ -1815,17 +1924,21 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1834,7 +1947,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>21755</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="17">
@@ -1842,17 +1955,21 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1861,7 +1978,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>19704</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="18">
@@ -1869,7 +1986,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1892,7 +2009,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>13964</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="19">
@@ -1900,7 +2017,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1923,7 +2040,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>16681</v>
+        <v>18959</v>
       </c>
     </row>
     <row r="20">
@@ -1931,21 +2048,17 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1954,7 +2067,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>17645</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="21">
@@ -1962,21 +2075,17 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1985,7 +2094,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>14882</v>
+        <v>20069</v>
       </c>
     </row>
     <row r="22">
@@ -1993,21 +2102,17 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2016,7 +2121,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>14644</v>
+        <v>19095</v>
       </c>
     </row>
     <row r="23">
@@ -2024,21 +2129,17 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2047,7 +2148,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>10078</v>
+        <v>19098</v>
       </c>
     </row>
     <row r="24">
@@ -2055,21 +2156,17 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2078,7 +2175,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5014</v>
+        <v>20810</v>
       </c>
     </row>
     <row r="25">
@@ -2086,21 +2183,17 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2109,7 +2202,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>14358</v>
+        <v>19280</v>
       </c>
     </row>
     <row r="26">
@@ -2117,21 +2210,17 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sopladora</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2140,7 +2229,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>8114</v>
+        <v>21755</v>
       </c>
     </row>
     <row r="27">
@@ -2148,21 +2237,17 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sopladora</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2171,7 +2256,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>8424</v>
+        <v>19704</v>
       </c>
     </row>
     <row r="28">
@@ -2179,21 +2264,17 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sopladora</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2202,7 +2283,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9735</v>
+        <v>18740</v>
       </c>
     </row>
     <row r="29">
@@ -2210,7 +2291,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2233,7 +2314,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8469</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="30">
@@ -2241,7 +2322,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2264,7 +2345,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>8416</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="31">
@@ -2272,7 +2353,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2295,7 +2376,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5868</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="32">
@@ -2303,7 +2384,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2326,7 +2407,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2907</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="33">
@@ -2334,7 +2415,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2357,7 +2438,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8041</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="34">
@@ -2365,16 +2446,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2388,7 +2469,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2768</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="35">
@@ -2396,16 +2477,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2419,7 +2500,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2477</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="36">
@@ -2427,16 +2508,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2450,7 +2531,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2491</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="37">
@@ -2458,16 +2539,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2481,7 +2562,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2773</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="38">
@@ -2489,21 +2570,21 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2512,7 +2593,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2472</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="39">
@@ -2520,21 +2601,21 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2543,7 +2624,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2512</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="40">
@@ -2551,21 +2632,21 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2574,7 +2655,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2854</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="41">
@@ -2582,21 +2663,21 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2605,7 +2686,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2801</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="42">
@@ -2613,7 +2694,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2636,7 +2717,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3724</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="43">
@@ -2644,7 +2725,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2667,7 +2748,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3644</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="44">
@@ -2675,7 +2756,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2698,7 +2779,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3194</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="45">
@@ -2706,7 +2787,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2729,7 +2810,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3026</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="46">
@@ -2737,7 +2818,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2760,7 +2841,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3345</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="47">
@@ -2768,21 +2849,21 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2791,7 +2872,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2963</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="48">
@@ -2799,21 +2880,21 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46298</v>
+        <v>46293</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2822,7 +2903,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3431</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="49">
@@ -2830,21 +2911,21 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46300</v>
+        <v>46294</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2853,7 +2934,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2788</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="50">
@@ -2861,11 +2942,11 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2884,7 +2965,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2003</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="51">
@@ -2892,11 +2973,11 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2915,7 +2996,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1820</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="52">
@@ -2923,11 +3004,11 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2946,7 +3027,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1820</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="53">
@@ -2954,11 +3035,11 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2977,7 +3058,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2009</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="54">
@@ -2985,11 +3066,11 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3008,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1847</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="55">
@@ -3016,11 +3097,11 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3039,7 +3120,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1853</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="56">
@@ -3047,16 +3128,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3070,7 +3151,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2034</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="57">
@@ -3078,16 +3159,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3101,7 +3182,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2027</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="58">
@@ -3109,11 +3190,11 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3132,7 +3213,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>239</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="59">
@@ -3140,11 +3221,11 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3163,7 +3244,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1531</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="60">
@@ -3171,11 +3252,11 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3194,7 +3275,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>306</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="61">
@@ -3202,11 +3283,11 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3225,7 +3306,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>721</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="62">
@@ -3233,11 +3314,11 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3256,7 +3337,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>750</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="63">
@@ -3264,11 +3345,11 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3287,7 +3368,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>461</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="64">
@@ -3295,16 +3376,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3318,7 +3399,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1105</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="65">
@@ -3326,16 +3407,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3349,7 +3430,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1488</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="66">
@@ -3357,16 +3438,16 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3380,7 +3461,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2301</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="67">
@@ -3388,16 +3469,16 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3411,7 +3492,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2554</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="68">
@@ -3419,16 +3500,16 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3442,7 +3523,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2604</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="69">
@@ -3450,16 +3531,16 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3473,7 +3554,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2307</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="70">
@@ -3481,16 +3562,16 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3504,7 +3585,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>3102</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="71">
@@ -3512,16 +3593,16 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3535,7 +3616,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2187</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="72">
@@ -3543,30 +3624,309 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Tungurahua</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="2" t="n">
         <v>46300</v>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Mazar</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>1164</v>
+      <c r="G80" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1870</v>
       </c>
     </row>
   </sheetData>
@@ -3580,7 +3940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13609,6 +13969,1254 @@
         <v>4399.18</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B386" t="n">
+        <v>3123.18</v>
+      </c>
+      <c r="C386" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" t="n">
+        <v>1087.16</v>
+      </c>
+      <c r="F386" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="G386" t="n">
+        <v>4234.330000000001</v>
+      </c>
+      <c r="H386" t="n">
+        <v>4216.690000000001</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B387" t="n">
+        <v>3023.61</v>
+      </c>
+      <c r="C387" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="n">
+        <v>1063.49</v>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>4093.45</v>
+      </c>
+      <c r="H387" t="n">
+        <v>4093.45</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B388" t="n">
+        <v>2909.49</v>
+      </c>
+      <c r="C388" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" t="n">
+        <v>1057.74</v>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>3977.82</v>
+      </c>
+      <c r="H388" t="n">
+        <v>3977.82</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>46301.0625</v>
+      </c>
+      <c r="B389" t="n">
+        <v>2842.21</v>
+      </c>
+      <c r="C389" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="n">
+        <v>1040.56</v>
+      </c>
+      <c r="F389" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" t="n">
+        <v>3893.68</v>
+      </c>
+      <c r="H389" t="n">
+        <v>3893.68</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B390" t="n">
+        <v>2748.38</v>
+      </c>
+      <c r="C390" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" t="n">
+        <v>1053.2</v>
+      </c>
+      <c r="F390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" t="n">
+        <v>3811.51</v>
+      </c>
+      <c r="H390" t="n">
+        <v>3811.51</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B391" t="n">
+        <v>2671.51</v>
+      </c>
+      <c r="C391" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="D391" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E391" t="n">
+        <v>1057.8</v>
+      </c>
+      <c r="F391" t="n">
+        <v>0</v>
+      </c>
+      <c r="G391" t="n">
+        <v>3740.320000000001</v>
+      </c>
+      <c r="H391" t="n">
+        <v>3740.320000000001</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>46301.125</v>
+      </c>
+      <c r="B392" t="n">
+        <v>2594.12</v>
+      </c>
+      <c r="C392" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0</v>
+      </c>
+      <c r="E392" t="n">
+        <v>1081.28</v>
+      </c>
+      <c r="F392" t="n">
+        <v>0</v>
+      </c>
+      <c r="G392" t="n">
+        <v>3683.18</v>
+      </c>
+      <c r="H392" t="n">
+        <v>3683.18</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B393" t="n">
+        <v>2536</v>
+      </c>
+      <c r="C393" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" t="n">
+        <v>1077.8</v>
+      </c>
+      <c r="F393" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="G393" t="n">
+        <v>3638.26</v>
+      </c>
+      <c r="H393" t="n">
+        <v>3621.53</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B394" t="n">
+        <v>2507.56</v>
+      </c>
+      <c r="C394" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="D394" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E394" t="n">
+        <v>1070.31</v>
+      </c>
+      <c r="F394" t="n">
+        <v>0</v>
+      </c>
+      <c r="G394" t="n">
+        <v>3586.96</v>
+      </c>
+      <c r="H394" t="n">
+        <v>3586.96</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>46301.1875</v>
+      </c>
+      <c r="B395" t="n">
+        <v>2497.15</v>
+      </c>
+      <c r="C395" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0</v>
+      </c>
+      <c r="E395" t="n">
+        <v>1072.37</v>
+      </c>
+      <c r="F395" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="G395" t="n">
+        <v>3582.51</v>
+      </c>
+      <c r="H395" t="n">
+        <v>3576.93</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B396" t="n">
+        <v>2513.21</v>
+      </c>
+      <c r="C396" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0</v>
+      </c>
+      <c r="E396" t="n">
+        <v>1079.96</v>
+      </c>
+      <c r="F396" t="n">
+        <v>0</v>
+      </c>
+      <c r="G396" t="n">
+        <v>3600.03</v>
+      </c>
+      <c r="H396" t="n">
+        <v>3600.03</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B397" t="n">
+        <v>2601.46</v>
+      </c>
+      <c r="C397" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="D397" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E397" t="n">
+        <v>1078</v>
+      </c>
+      <c r="F397" t="n">
+        <v>0</v>
+      </c>
+      <c r="G397" t="n">
+        <v>3688.7</v>
+      </c>
+      <c r="H397" t="n">
+        <v>3688.7</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>46301.25</v>
+      </c>
+      <c r="B398" t="n">
+        <v>2505.83</v>
+      </c>
+      <c r="C398" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D398" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="E398" t="n">
+        <v>1061.4</v>
+      </c>
+      <c r="F398" t="n">
+        <v>0</v>
+      </c>
+      <c r="G398" t="n">
+        <v>3587.24</v>
+      </c>
+      <c r="H398" t="n">
+        <v>3587.24</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B399" t="n">
+        <v>2410.79</v>
+      </c>
+      <c r="C399" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0</v>
+      </c>
+      <c r="E399" t="n">
+        <v>1060.54</v>
+      </c>
+      <c r="F399" t="n">
+        <v>0</v>
+      </c>
+      <c r="G399" t="n">
+        <v>3477.79</v>
+      </c>
+      <c r="H399" t="n">
+        <v>3477.79</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B400" t="n">
+        <v>2353.86</v>
+      </c>
+      <c r="C400" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="D400" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="E400" t="n">
+        <v>1088.88</v>
+      </c>
+      <c r="F400" t="n">
+        <v>0</v>
+      </c>
+      <c r="G400" t="n">
+        <v>3465.26</v>
+      </c>
+      <c r="H400" t="n">
+        <v>3465.26</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>46301.3125</v>
+      </c>
+      <c r="B401" t="n">
+        <v>2515.41</v>
+      </c>
+      <c r="C401" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" t="n">
+        <v>1087.98</v>
+      </c>
+      <c r="F401" t="n">
+        <v>0</v>
+      </c>
+      <c r="G401" t="n">
+        <v>3607.51</v>
+      </c>
+      <c r="H401" t="n">
+        <v>3607.51</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B402" t="n">
+        <v>2694.04</v>
+      </c>
+      <c r="C402" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0</v>
+      </c>
+      <c r="E402" t="n">
+        <v>1091.57</v>
+      </c>
+      <c r="F402" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G402" t="n">
+        <v>3794.41</v>
+      </c>
+      <c r="H402" t="n">
+        <v>3792.5</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B403" t="n">
+        <v>2934.7</v>
+      </c>
+      <c r="C403" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" t="n">
+        <v>1078.91</v>
+      </c>
+      <c r="F403" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G403" t="n">
+        <v>4023.55</v>
+      </c>
+      <c r="H403" t="n">
+        <v>4020.59</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>46301.375</v>
+      </c>
+      <c r="B404" t="n">
+        <v>3060.98</v>
+      </c>
+      <c r="C404" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="D404" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="E404" t="n">
+        <v>1074.03</v>
+      </c>
+      <c r="F404" t="n">
+        <v>0</v>
+      </c>
+      <c r="G404" t="n">
+        <v>4153.33</v>
+      </c>
+      <c r="H404" t="n">
+        <v>4153.33</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B405" t="n">
+        <v>3172.2</v>
+      </c>
+      <c r="C405" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="D405" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E405" t="n">
+        <v>1063.23</v>
+      </c>
+      <c r="F405" t="n">
+        <v>0</v>
+      </c>
+      <c r="G405" t="n">
+        <v>4248.33</v>
+      </c>
+      <c r="H405" t="n">
+        <v>4248.33</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B406" t="n">
+        <v>3298.65</v>
+      </c>
+      <c r="C406" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" t="n">
+        <v>1077.46</v>
+      </c>
+      <c r="F406" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="G406" t="n">
+        <v>4394.07</v>
+      </c>
+      <c r="H406" t="n">
+        <v>4389.48</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>46301.4375</v>
+      </c>
+      <c r="B407" t="n">
+        <v>3374.35</v>
+      </c>
+      <c r="C407" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>1068.67</v>
+      </c>
+      <c r="F407" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="G407" t="n">
+        <v>4509.6</v>
+      </c>
+      <c r="H407" t="n">
+        <v>4495.18</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B408" t="n">
+        <v>3483.73</v>
+      </c>
+      <c r="C408" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="D408" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E408" t="n">
+        <v>1064.54</v>
+      </c>
+      <c r="F408" t="n">
+        <v>0</v>
+      </c>
+      <c r="G408" t="n">
+        <v>4609.52</v>
+      </c>
+      <c r="H408" t="n">
+        <v>4609.52</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B409" t="n">
+        <v>3544.89</v>
+      </c>
+      <c r="C409" t="n">
+        <v>64.47</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="n">
+        <v>1070.63</v>
+      </c>
+      <c r="F409" t="n">
+        <v>0</v>
+      </c>
+      <c r="G409" t="n">
+        <v>4679.99</v>
+      </c>
+      <c r="H409" t="n">
+        <v>4679.99</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>46301.5</v>
+      </c>
+      <c r="B410" t="n">
+        <v>3575.27</v>
+      </c>
+      <c r="C410" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="n">
+        <v>1063.52</v>
+      </c>
+      <c r="F410" t="n">
+        <v>0</v>
+      </c>
+      <c r="G410" t="n">
+        <v>4705.9</v>
+      </c>
+      <c r="H410" t="n">
+        <v>4705.9</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B411" t="n">
+        <v>3584.59</v>
+      </c>
+      <c r="C411" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="n">
+        <v>1066.64</v>
+      </c>
+      <c r="F411" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G411" t="n">
+        <v>4724.72</v>
+      </c>
+      <c r="H411" t="n">
+        <v>4718.22</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B412" t="n">
+        <v>3609.36</v>
+      </c>
+      <c r="C412" t="n">
+        <v>69.97</v>
+      </c>
+      <c r="D412" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E412" t="n">
+        <v>1063.23</v>
+      </c>
+      <c r="F412" t="n">
+        <v>0</v>
+      </c>
+      <c r="G412" t="n">
+        <v>4747.95</v>
+      </c>
+      <c r="H412" t="n">
+        <v>4747.95</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B413" t="n">
+        <v>3701.19</v>
+      </c>
+      <c r="C413" t="n">
+        <v>71.91</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>1064.32</v>
+      </c>
+      <c r="F413" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4839.49</v>
+      </c>
+      <c r="H413" t="n">
+        <v>4837.42</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B414" t="n">
+        <v>3811.1</v>
+      </c>
+      <c r="C414" t="n">
+        <v>67.59</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>1061.37</v>
+      </c>
+      <c r="F414" t="n">
+        <v>0</v>
+      </c>
+      <c r="G414" t="n">
+        <v>4940.06</v>
+      </c>
+      <c r="H414" t="n">
+        <v>4940.06</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B415" t="n">
+        <v>3874.5</v>
+      </c>
+      <c r="C415" t="n">
+        <v>69.48999999999999</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0</v>
+      </c>
+      <c r="E415" t="n">
+        <v>1065.57</v>
+      </c>
+      <c r="F415" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="G415" t="n">
+        <v>5019.23</v>
+      </c>
+      <c r="H415" t="n">
+        <v>5009.56</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>46301.625</v>
+      </c>
+      <c r="B416" t="n">
+        <v>3877.95</v>
+      </c>
+      <c r="C416" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>1075.39</v>
+      </c>
+      <c r="F416" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G416" t="n">
+        <v>5032.53</v>
+      </c>
+      <c r="H416" t="n">
+        <v>5016.13</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B417" t="n">
+        <v>3861.57</v>
+      </c>
+      <c r="C417" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>1071.54</v>
+      </c>
+      <c r="F417" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G417" t="n">
+        <v>4997.53</v>
+      </c>
+      <c r="H417" t="n">
+        <v>4988.24</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B418" t="n">
+        <v>3854.11</v>
+      </c>
+      <c r="C418" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>1071.59</v>
+      </c>
+      <c r="F418" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G418" t="n">
+        <v>4974.57</v>
+      </c>
+      <c r="H418" t="n">
+        <v>4968.17</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>46301.6875</v>
+      </c>
+      <c r="B419" t="n">
+        <v>3818.21</v>
+      </c>
+      <c r="C419" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>1072.89</v>
+      </c>
+      <c r="F419" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="G419" t="n">
+        <v>4945.23</v>
+      </c>
+      <c r="H419" t="n">
+        <v>4926.75</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B420" t="n">
+        <v>3741.02</v>
+      </c>
+      <c r="C420" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0</v>
+      </c>
+      <c r="E420" t="n">
+        <v>1072.72</v>
+      </c>
+      <c r="F420" t="n">
+        <v>0</v>
+      </c>
+      <c r="G420" t="n">
+        <v>4849.06</v>
+      </c>
+      <c r="H420" t="n">
+        <v>4849.06</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B421" t="n">
+        <v>3645.06</v>
+      </c>
+      <c r="C421" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>1078.57</v>
+      </c>
+      <c r="F421" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="G421" t="n">
+        <v>4763.73</v>
+      </c>
+      <c r="H421" t="n">
+        <v>4748.09</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>46301.75</v>
+      </c>
+      <c r="B422" t="n">
+        <v>3660.34</v>
+      </c>
+      <c r="C422" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="D422" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="E422" t="n">
+        <v>1077.22</v>
+      </c>
+      <c r="F422" t="n">
+        <v>0</v>
+      </c>
+      <c r="G422" t="n">
+        <v>4778.81</v>
+      </c>
+      <c r="H422" t="n">
+        <v>4778.81</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B423" t="n">
+        <v>4001.66</v>
+      </c>
+      <c r="C423" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="D423" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="E423" t="n">
+        <v>1070.46</v>
+      </c>
+      <c r="F423" t="n">
+        <v>0</v>
+      </c>
+      <c r="G423" t="n">
+        <v>5097.76</v>
+      </c>
+      <c r="H423" t="n">
+        <v>5097.76</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B424" t="n">
+        <v>4137.78</v>
+      </c>
+      <c r="C424" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="D424" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" t="n">
+        <v>1095.73</v>
+      </c>
+      <c r="F424" t="n">
+        <v>0</v>
+      </c>
+      <c r="G424" t="n">
+        <v>5243.719999999999</v>
+      </c>
+      <c r="H424" t="n">
+        <v>5243.719999999999</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>46301.8125</v>
+      </c>
+      <c r="B425" t="n">
+        <v>4141.03</v>
+      </c>
+      <c r="C425" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="D425" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1112.37</v>
+      </c>
+      <c r="F425" t="n">
+        <v>0</v>
+      </c>
+      <c r="G425" t="n">
+        <v>5268.38</v>
+      </c>
+      <c r="H425" t="n">
+        <v>5268.38</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B426" t="n">
+        <v>4117.01</v>
+      </c>
+      <c r="C426" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>1124.82</v>
+      </c>
+      <c r="F426" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G426" t="n">
+        <v>5254.679999999999</v>
+      </c>
+      <c r="H426" t="n">
+        <v>5252.57</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B427" t="n">
+        <v>4067.87</v>
+      </c>
+      <c r="C427" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="n">
+        <v>1126.26</v>
+      </c>
+      <c r="F427" t="n">
+        <v>0</v>
+      </c>
+      <c r="G427" t="n">
+        <v>5205.98</v>
+      </c>
+      <c r="H427" t="n">
+        <v>5205.98</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>46301.875</v>
+      </c>
+      <c r="B428" t="n">
+        <v>3970.65</v>
+      </c>
+      <c r="C428" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="n">
+        <v>1130.04</v>
+      </c>
+      <c r="F428" t="n">
+        <v>0</v>
+      </c>
+      <c r="G428" t="n">
+        <v>5112.23</v>
+      </c>
+      <c r="H428" t="n">
+        <v>5112.23</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B429" t="n">
+        <v>3899.37</v>
+      </c>
+      <c r="C429" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="n">
+        <v>1121.51</v>
+      </c>
+      <c r="F429" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="G429" t="n">
+        <v>5043.389999999999</v>
+      </c>
+      <c r="H429" t="n">
+        <v>5033.66</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B430" t="n">
+        <v>3799.23</v>
+      </c>
+      <c r="C430" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="n">
+        <v>1110.24</v>
+      </c>
+      <c r="F430" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="G430" t="n">
+        <v>4923.650000000001</v>
+      </c>
+      <c r="H430" t="n">
+        <v>4919.13</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>46301.9375</v>
+      </c>
+      <c r="B431" t="n">
+        <v>3626.44</v>
+      </c>
+      <c r="C431" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="D431" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1101.29</v>
+      </c>
+      <c r="F431" t="n">
+        <v>0</v>
+      </c>
+      <c r="G431" t="n">
+        <v>4741.93</v>
+      </c>
+      <c r="H431" t="n">
+        <v>4741.93</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B432" t="n">
+        <v>3459.39</v>
+      </c>
+      <c r="C432" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="D432" t="n">
+        <v>0</v>
+      </c>
+      <c r="E432" t="n">
+        <v>1102.86</v>
+      </c>
+      <c r="F432" t="n">
+        <v>0</v>
+      </c>
+      <c r="G432" t="n">
+        <v>4569.02</v>
+      </c>
+      <c r="H432" t="n">
+        <v>4569.02</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B433" t="n">
+        <v>3263.99</v>
+      </c>
+      <c r="C433" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="D433" t="n">
+        <v>0</v>
+      </c>
+      <c r="E433" t="n">
+        <v>1101.85</v>
+      </c>
+      <c r="F433" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="G433" t="n">
+        <v>4378.4</v>
+      </c>
+      <c r="H433" t="n">
+        <v>4372.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1085,6 +1085,59 @@
       </c>
       <c r="Q10" t="n">
         <v>0.003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103708</v>
+      </c>
+      <c r="C11" t="n">
+        <v>78817</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24110</v>
+      </c>
+      <c r="E11" t="n">
+        <v>21329</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2781</v>
+      </c>
+      <c r="G11" t="n">
+        <v>632</v>
+      </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>101</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.321</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.004</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,19 +1162,19 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Coca Codo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Paute</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
           <t>Sopladora</t>
@@ -1129,17 +1182,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Delsitanisagua</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Mazar</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -1158,25 +1211,25 @@
         <v>46291</v>
       </c>
       <c r="B2" t="n">
+        <v>16882</v>
+      </c>
+      <c r="C2" t="n">
         <v>24721</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>13964</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16882</v>
       </c>
       <c r="E2" t="n">
         <v>8114</v>
       </c>
       <c r="F2" t="n">
-        <v>3724</v>
+        <v>2301</v>
       </c>
       <c r="G2" t="n">
         <v>2768</v>
       </c>
       <c r="H2" t="n">
-        <v>2301</v>
+        <v>3724</v>
       </c>
       <c r="I2" t="n">
         <v>2003</v>
@@ -1190,25 +1243,25 @@
         <v>46293</v>
       </c>
       <c r="B3" t="n">
+        <v>20069</v>
+      </c>
+      <c r="C3" t="n">
         <v>23420</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>16681</v>
-      </c>
-      <c r="D3" t="n">
-        <v>20069</v>
       </c>
       <c r="E3" t="n">
         <v>8424</v>
       </c>
       <c r="F3" t="n">
-        <v>3644</v>
+        <v>2554</v>
       </c>
       <c r="G3" t="n">
         <v>2477</v>
       </c>
       <c r="H3" t="n">
-        <v>2554</v>
+        <v>3644</v>
       </c>
       <c r="I3" t="n">
         <v>1820</v>
@@ -1222,25 +1275,25 @@
         <v>46294</v>
       </c>
       <c r="B4" t="n">
+        <v>19095</v>
+      </c>
+      <c r="C4" t="n">
         <v>19992</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>17645</v>
-      </c>
-      <c r="D4" t="n">
-        <v>19095</v>
       </c>
       <c r="E4" t="n">
         <v>9735</v>
       </c>
       <c r="F4" t="n">
-        <v>3194</v>
+        <v>2604</v>
       </c>
       <c r="G4" t="n">
         <v>2491</v>
       </c>
       <c r="H4" t="n">
-        <v>2604</v>
+        <v>3194</v>
       </c>
       <c r="I4" t="n">
         <v>1820</v>
@@ -1254,25 +1307,25 @@
         <v>46295</v>
       </c>
       <c r="B5" t="n">
+        <v>19098</v>
+      </c>
+      <c r="C5" t="n">
         <v>17987</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>14882</v>
-      </c>
-      <c r="D5" t="n">
-        <v>19098</v>
       </c>
       <c r="E5" t="n">
         <v>8469</v>
       </c>
       <c r="F5" t="n">
-        <v>3026</v>
+        <v>2307</v>
       </c>
       <c r="G5" t="n">
         <v>2773</v>
       </c>
       <c r="H5" t="n">
-        <v>2307</v>
+        <v>3026</v>
       </c>
       <c r="I5" t="n">
         <v>2009</v>
@@ -1286,25 +1339,25 @@
         <v>46296</v>
       </c>
       <c r="B6" t="n">
+        <v>20810</v>
+      </c>
+      <c r="C6" t="n">
         <v>17990</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>14644</v>
-      </c>
-      <c r="D6" t="n">
-        <v>20810</v>
       </c>
       <c r="E6" t="n">
         <v>8416</v>
       </c>
       <c r="F6" t="n">
-        <v>3345</v>
+        <v>3102</v>
       </c>
       <c r="G6" t="n">
         <v>2472</v>
       </c>
       <c r="H6" t="n">
-        <v>3102</v>
+        <v>3345</v>
       </c>
       <c r="I6" t="n">
         <v>1847</v>
@@ -1318,25 +1371,25 @@
         <v>46297</v>
       </c>
       <c r="B7" t="n">
+        <v>19280</v>
+      </c>
+      <c r="C7" t="n">
         <v>22254</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>10078</v>
-      </c>
-      <c r="D7" t="n">
-        <v>19280</v>
       </c>
       <c r="E7" t="n">
         <v>5868</v>
       </c>
       <c r="F7" t="n">
-        <v>2963</v>
+        <v>2187</v>
       </c>
       <c r="G7" t="n">
         <v>2512</v>
       </c>
       <c r="H7" t="n">
-        <v>2187</v>
+        <v>2963</v>
       </c>
       <c r="I7" t="n">
         <v>1853</v>
@@ -1350,24 +1403,24 @@
         <v>46298</v>
       </c>
       <c r="B8" t="n">
+        <v>21755</v>
+      </c>
+      <c r="C8" t="n">
         <v>26473</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>5014</v>
-      </c>
-      <c r="D8" t="n">
-        <v>21755</v>
       </c>
       <c r="E8" t="n">
         <v>2907</v>
       </c>
-      <c r="F8" t="n">
-        <v>3431</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>2854</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>3431</v>
+      </c>
       <c r="I8" t="n">
         <v>2034</v>
       </c>
@@ -1380,25 +1433,25 @@
         <v>46300</v>
       </c>
       <c r="B9" t="n">
+        <v>19704</v>
+      </c>
+      <c r="C9" t="n">
         <v>23346</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>14358</v>
-      </c>
-      <c r="D9" t="n">
-        <v>19704</v>
       </c>
       <c r="E9" t="n">
         <v>8041</v>
       </c>
       <c r="F9" t="n">
-        <v>2788</v>
+        <v>1164</v>
       </c>
       <c r="G9" t="n">
         <v>2801</v>
       </c>
       <c r="H9" t="n">
-        <v>1164</v>
+        <v>2788</v>
       </c>
       <c r="I9" t="n">
         <v>2027</v>
@@ -1412,31 +1465,63 @@
         <v>46301</v>
       </c>
       <c r="B10" t="n">
+        <v>18740</v>
+      </c>
+      <c r="C10" t="n">
         <v>19157</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>18959</v>
-      </c>
-      <c r="D10" t="n">
-        <v>18740</v>
       </c>
       <c r="E10" t="n">
         <v>9960</v>
       </c>
       <c r="F10" t="n">
-        <v>2675</v>
+        <v>2157</v>
       </c>
       <c r="G10" t="n">
         <v>2566</v>
       </c>
       <c r="H10" t="n">
-        <v>2157</v>
+        <v>2675</v>
       </c>
       <c r="I10" t="n">
         <v>1907</v>
       </c>
       <c r="J10" t="n">
         <v>1870</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B11" t="n">
+        <v>19903</v>
+      </c>
+      <c r="C11" t="n">
+        <v>19048</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18347</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9798</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2831</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2706</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2526</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1966</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1693</v>
       </c>
     </row>
   </sheetData>
@@ -1450,7 +1535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,17 +1579,13 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1513,7 +1594,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>24721</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="3">
@@ -1525,17 +1606,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1544,7 +1621,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23420</v>
+        <v>20069</v>
       </c>
     </row>
     <row r="4">
@@ -1556,17 +1633,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1575,7 +1648,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19992</v>
+        <v>19095</v>
       </c>
     </row>
     <row r="5">
@@ -1587,17 +1660,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1606,7 +1675,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>17987</v>
+        <v>19098</v>
       </c>
     </row>
     <row r="6">
@@ -1618,17 +1687,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1637,7 +1702,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>17990</v>
+        <v>20810</v>
       </c>
     </row>
     <row r="7">
@@ -1649,17 +1714,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1668,7 +1729,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22254</v>
+        <v>19280</v>
       </c>
     </row>
     <row r="8">
@@ -1680,17 +1741,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1699,7 +1756,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>26473</v>
+        <v>21755</v>
       </c>
     </row>
     <row r="9">
@@ -1711,17 +1768,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1730,7 +1783,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>23346</v>
+        <v>19704</v>
       </c>
     </row>
     <row r="10">
@@ -1742,17 +1795,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1761,7 +1810,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>19157</v>
+        <v>18740</v>
       </c>
     </row>
     <row r="11">
@@ -1769,21 +1818,17 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46291</v>
+        <v>46302</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1792,7 +1837,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>13964</v>
+        <v>19903</v>
       </c>
     </row>
     <row r="12">
@@ -1800,21 +1845,21 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1823,7 +1868,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>16681</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="13">
@@ -1831,21 +1876,21 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1854,7 +1899,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>17645</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="14">
@@ -1862,21 +1907,21 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1885,7 +1930,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>14882</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="15">
@@ -1893,21 +1938,21 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1916,7 +1961,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>14644</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="16">
@@ -1924,21 +1969,21 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1947,7 +1992,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>10078</v>
+        <v>17990</v>
       </c>
     </row>
     <row r="17">
@@ -1955,21 +2000,21 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1978,7 +2023,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5014</v>
+        <v>22254</v>
       </c>
     </row>
     <row r="18">
@@ -1986,21 +2031,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2009,7 +2054,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>14358</v>
+        <v>26473</v>
       </c>
     </row>
     <row r="19">
@@ -2017,21 +2062,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2040,7 +2085,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>18959</v>
+        <v>23346</v>
       </c>
     </row>
     <row r="20">
@@ -2048,17 +2093,21 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46291</v>
+        <v>46301</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2067,7 +2116,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>16882</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="21">
@@ -2075,17 +2124,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Napo</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2094,7 +2147,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>20069</v>
+        <v>19048</v>
       </c>
     </row>
     <row r="22">
@@ -2102,17 +2155,21 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2121,7 +2178,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>19095</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="23">
@@ -2129,17 +2186,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2148,7 +2209,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>19098</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="24">
@@ -2156,17 +2217,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2175,7 +2240,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>20810</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="25">
@@ -2183,17 +2248,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2202,7 +2271,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>19280</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="26">
@@ -2210,17 +2279,21 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2229,7 +2302,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>21755</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="27">
@@ -2237,17 +2310,21 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2256,7 +2333,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>19704</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="28">
@@ -2264,17 +2341,21 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Otras Hidro</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nacional (agregado)</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2283,7 +2364,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>18740</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="29">
@@ -2291,11 +2372,11 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2314,7 +2395,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8114</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="30">
@@ -2322,11 +2403,11 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2345,7 +2426,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>8424</v>
+        <v>18959</v>
       </c>
     </row>
     <row r="31">
@@ -2353,11 +2434,11 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2376,7 +2457,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9735</v>
+        <v>18347</v>
       </c>
     </row>
     <row r="32">
@@ -2384,7 +2465,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2407,7 +2488,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8469</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="33">
@@ -2415,7 +2496,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2438,7 +2519,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8416</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="34">
@@ -2446,7 +2527,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2469,7 +2550,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5868</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="35">
@@ -2477,7 +2558,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2500,7 +2581,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2907</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="36">
@@ -2508,7 +2589,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2531,7 +2612,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>8041</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="37">
@@ -2539,7 +2620,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2562,7 +2643,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>9960</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="38">
@@ -2570,21 +2651,21 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2593,7 +2674,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3724</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="39">
@@ -2601,21 +2682,21 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2624,7 +2705,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3644</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="40">
@@ -2632,21 +2713,21 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2655,7 +2736,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>3194</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="41">
@@ -2663,21 +2744,21 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2686,7 +2767,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3026</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="42">
@@ -2694,21 +2775,21 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2717,7 +2798,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3345</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="43">
@@ -2725,21 +2806,21 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2748,7 +2829,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2963</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="44">
@@ -2756,21 +2837,21 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2779,7 +2860,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3431</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="45">
@@ -2787,21 +2868,21 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2810,7 +2891,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2788</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="46">
@@ -2818,21 +2899,21 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2841,7 +2922,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2675</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="47">
@@ -2849,16 +2930,16 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2872,7 +2953,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2768</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="48">
@@ -2880,16 +2961,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2903,7 +2984,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2477</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="49">
@@ -2911,16 +2992,16 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2934,7 +3015,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2491</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="50">
@@ -2942,16 +3023,16 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2965,7 +3046,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2773</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="51">
@@ -2973,7 +3054,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2996,7 +3077,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2472</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="52">
@@ -3004,7 +3085,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3027,7 +3108,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2512</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="53">
@@ -3035,7 +3116,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3058,7 +3139,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2854</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="54">
@@ -3066,7 +3147,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3089,7 +3170,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2801</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="55">
@@ -3097,7 +3178,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3120,7 +3201,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2566</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="56">
@@ -3128,16 +3209,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3151,7 +3232,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2301</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="57">
@@ -3159,16 +3240,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3182,7 +3263,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2554</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="58">
@@ -3190,16 +3271,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3213,7 +3294,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2604</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="59">
@@ -3221,16 +3302,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3244,7 +3325,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2307</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="60">
@@ -3252,16 +3333,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3275,7 +3356,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3102</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="61">
@@ -3283,21 +3364,21 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3306,7 +3387,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2187</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="62">
@@ -3314,21 +3395,21 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3337,7 +3418,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1164</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="63">
@@ -3345,21 +3426,21 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3368,7 +3449,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2157</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="64">
@@ -3376,21 +3457,21 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3399,7 +3480,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2003</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="65">
@@ -3407,21 +3488,21 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3430,7 +3511,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1820</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="66">
@@ -3438,21 +3519,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3461,7 +3542,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1820</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="67">
@@ -3469,21 +3550,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3492,7 +3573,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2009</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="68">
@@ -3500,21 +3581,21 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3523,7 +3604,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1847</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="69">
@@ -3531,21 +3612,21 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3554,7 +3635,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1853</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="70">
@@ -3562,21 +3643,21 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3585,7 +3666,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2034</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="71">
@@ -3593,7 +3674,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46300</v>
+        <v>46291</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3616,7 +3697,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2027</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="72">
@@ -3624,7 +3705,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3647,7 +3728,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1907</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="73">
@@ -3655,16 +3736,16 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3678,7 +3759,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>239</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="74">
@@ -3686,16 +3767,16 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3709,7 +3790,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1531</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="75">
@@ -3717,16 +3798,16 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3740,7 +3821,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>306</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="76">
@@ -3748,16 +3829,16 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3771,7 +3852,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>721</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="77">
@@ -3779,16 +3860,16 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3802,7 +3883,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>750</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="78">
@@ -3810,16 +3891,16 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3833,7 +3914,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>461</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="79">
@@ -3841,16 +3922,16 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46298</v>
+        <v>46301</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3864,7 +3945,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1105</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="80">
@@ -3872,16 +3953,16 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3895,7 +3976,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1488</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="81">
@@ -3903,30 +3984,309 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="2" t="n">
         <v>46301</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Minas San Francisco</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G81" t="n">
+      <c r="G89" t="n">
         <v>1870</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1693</v>
       </c>
     </row>
   </sheetData>
@@ -3940,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15217,6 +15577,1254 @@
         <v>4372.77</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B434" t="n">
+        <v>3049.96</v>
+      </c>
+      <c r="C434" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="D434" t="n">
+        <v>0</v>
+      </c>
+      <c r="E434" t="n">
+        <v>1088.76</v>
+      </c>
+      <c r="F434" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="G434" t="n">
+        <v>4181.89</v>
+      </c>
+      <c r="H434" t="n">
+        <v>4149.56</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B435" t="n">
+        <v>3038.12</v>
+      </c>
+      <c r="C435" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="n">
+        <v>1052.51</v>
+      </c>
+      <c r="F435" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="G435" t="n">
+        <v>4107.339999999999</v>
+      </c>
+      <c r="H435" t="n">
+        <v>4104.69</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B436" t="n">
+        <v>2933.49</v>
+      </c>
+      <c r="C436" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0</v>
+      </c>
+      <c r="E436" t="n">
+        <v>1037.43</v>
+      </c>
+      <c r="F436" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="G436" t="n">
+        <v>3994.67</v>
+      </c>
+      <c r="H436" t="n">
+        <v>3982.06</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>46302.0625</v>
+      </c>
+      <c r="B437" t="n">
+        <v>2806.2</v>
+      </c>
+      <c r="C437" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="D437" t="n">
+        <v>0</v>
+      </c>
+      <c r="E437" t="n">
+        <v>1064.11</v>
+      </c>
+      <c r="F437" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="G437" t="n">
+        <v>3907.03</v>
+      </c>
+      <c r="H437" t="n">
+        <v>3881.07</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B438" t="n">
+        <v>2727.77</v>
+      </c>
+      <c r="C438" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="D438" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1071.16</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" t="n">
+        <v>3818.36</v>
+      </c>
+      <c r="H438" t="n">
+        <v>3818.36</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B439" t="n">
+        <v>2726.05</v>
+      </c>
+      <c r="C439" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D439" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E439" t="n">
+        <v>993.25</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0</v>
+      </c>
+      <c r="G439" t="n">
+        <v>3733.31</v>
+      </c>
+      <c r="H439" t="n">
+        <v>3733.31</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>46302.125</v>
+      </c>
+      <c r="B440" t="n">
+        <v>2693.58</v>
+      </c>
+      <c r="C440" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="D440" t="n">
+        <v>0</v>
+      </c>
+      <c r="E440" t="n">
+        <v>999.6</v>
+      </c>
+      <c r="F440" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="G440" t="n">
+        <v>3716.5</v>
+      </c>
+      <c r="H440" t="n">
+        <v>3704.14</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B441" t="n">
+        <v>2649.55</v>
+      </c>
+      <c r="C441" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="D441" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E441" t="n">
+        <v>999.3200000000001</v>
+      </c>
+      <c r="F441" t="n">
+        <v>0</v>
+      </c>
+      <c r="G441" t="n">
+        <v>3667.64</v>
+      </c>
+      <c r="H441" t="n">
+        <v>3667.64</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B442" t="n">
+        <v>2617.74</v>
+      </c>
+      <c r="C442" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="D442" t="n">
+        <v>0</v>
+      </c>
+      <c r="E442" t="n">
+        <v>993.5</v>
+      </c>
+      <c r="F442" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G442" t="n">
+        <v>3632.26</v>
+      </c>
+      <c r="H442" t="n">
+        <v>3622.67</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>46302.1875</v>
+      </c>
+      <c r="B443" t="n">
+        <v>2598.38</v>
+      </c>
+      <c r="C443" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="D443" t="n">
+        <v>0</v>
+      </c>
+      <c r="E443" t="n">
+        <v>1007.23</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0</v>
+      </c>
+      <c r="G443" t="n">
+        <v>3616.15</v>
+      </c>
+      <c r="H443" t="n">
+        <v>3616.15</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B444" t="n">
+        <v>2582.79</v>
+      </c>
+      <c r="C444" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="D444" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="E444" t="n">
+        <v>996.76</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0</v>
+      </c>
+      <c r="G444" t="n">
+        <v>3624.89</v>
+      </c>
+      <c r="H444" t="n">
+        <v>3624.89</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B445" t="n">
+        <v>2682.25</v>
+      </c>
+      <c r="C445" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="D445" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E445" t="n">
+        <v>1010.76</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0</v>
+      </c>
+      <c r="G445" t="n">
+        <v>3710.85</v>
+      </c>
+      <c r="H445" t="n">
+        <v>3710.85</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>46302.25</v>
+      </c>
+      <c r="B446" t="n">
+        <v>2634.97</v>
+      </c>
+      <c r="C446" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="D446" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E446" t="n">
+        <v>1019.91</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" t="n">
+        <v>3665.75</v>
+      </c>
+      <c r="H446" t="n">
+        <v>3665.75</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B447" t="n">
+        <v>2493.57</v>
+      </c>
+      <c r="C447" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="D447" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E447" t="n">
+        <v>1012.14</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0</v>
+      </c>
+      <c r="G447" t="n">
+        <v>3523.27</v>
+      </c>
+      <c r="H447" t="n">
+        <v>3523.27</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B448" t="n">
+        <v>2451.59</v>
+      </c>
+      <c r="C448" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="D448" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="E448" t="n">
+        <v>1013.66</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G448" t="n">
+        <v>3491.13</v>
+      </c>
+      <c r="H448" t="n">
+        <v>3491.13</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>46302.3125</v>
+      </c>
+      <c r="B449" t="n">
+        <v>2622.49</v>
+      </c>
+      <c r="C449" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D449" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="E449" t="n">
+        <v>1005.28</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0</v>
+      </c>
+      <c r="G449" t="n">
+        <v>3643.8</v>
+      </c>
+      <c r="H449" t="n">
+        <v>3643.8</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B450" t="n">
+        <v>2780.84</v>
+      </c>
+      <c r="C450" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D450" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E450" t="n">
+        <v>1008.25</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0</v>
+      </c>
+      <c r="G450" t="n">
+        <v>3804.83</v>
+      </c>
+      <c r="H450" t="n">
+        <v>3804.83</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B451" t="n">
+        <v>2995.01</v>
+      </c>
+      <c r="C451" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="D451" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="E451" t="n">
+        <v>1005.71</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0</v>
+      </c>
+      <c r="G451" t="n">
+        <v>4030.960000000001</v>
+      </c>
+      <c r="H451" t="n">
+        <v>4030.960000000001</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>46302.375</v>
+      </c>
+      <c r="B452" t="n">
+        <v>3130.02</v>
+      </c>
+      <c r="C452" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="D452" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="E452" t="n">
+        <v>1007.2</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0</v>
+      </c>
+      <c r="G452" t="n">
+        <v>4176.24</v>
+      </c>
+      <c r="H452" t="n">
+        <v>4176.24</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B453" t="n">
+        <v>3287.99</v>
+      </c>
+      <c r="C453" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="D453" t="n">
+        <v>0</v>
+      </c>
+      <c r="E453" t="n">
+        <v>994.98</v>
+      </c>
+      <c r="F453" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="G453" t="n">
+        <v>4315.630000000001</v>
+      </c>
+      <c r="H453" t="n">
+        <v>4310.950000000001</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B454" t="n">
+        <v>3396.94</v>
+      </c>
+      <c r="C454" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="D454" t="n">
+        <v>0</v>
+      </c>
+      <c r="E454" t="n">
+        <v>983.76</v>
+      </c>
+      <c r="F454" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G454" t="n">
+        <v>4438.06</v>
+      </c>
+      <c r="H454" t="n">
+        <v>4433.21</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>46302.4375</v>
+      </c>
+      <c r="B455" t="n">
+        <v>3481.29</v>
+      </c>
+      <c r="C455" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="D455" t="n">
+        <v>0</v>
+      </c>
+      <c r="E455" t="n">
+        <v>986.08</v>
+      </c>
+      <c r="F455" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="G455" t="n">
+        <v>4545.360000000001</v>
+      </c>
+      <c r="H455" t="n">
+        <v>4528.81</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="B456" t="n">
+        <v>3589.6</v>
+      </c>
+      <c r="C456" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="D456" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E456" t="n">
+        <v>985.6799999999999</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G456" t="n">
+        <v>4645.07</v>
+      </c>
+      <c r="H456" t="n">
+        <v>4645.07</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n">
+        <v>46302.47916666666</v>
+      </c>
+      <c r="B457" t="n">
+        <v>3689.44</v>
+      </c>
+      <c r="C457" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="D457" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="E457" t="n">
+        <v>990.8200000000001</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" t="n">
+        <v>4755.92</v>
+      </c>
+      <c r="H457" t="n">
+        <v>4755.92</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n">
+        <v>46302.5</v>
+      </c>
+      <c r="B458" t="n">
+        <v>3659.15</v>
+      </c>
+      <c r="C458" t="n">
+        <v>68.41</v>
+      </c>
+      <c r="D458" t="n">
+        <v>0</v>
+      </c>
+      <c r="E458" t="n">
+        <v>989.83</v>
+      </c>
+      <c r="F458" t="n">
+        <v>0</v>
+      </c>
+      <c r="G458" t="n">
+        <v>4717.39</v>
+      </c>
+      <c r="H458" t="n">
+        <v>4717.39</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n">
+        <v>46302.52083333334</v>
+      </c>
+      <c r="B459" t="n">
+        <v>3694.74</v>
+      </c>
+      <c r="C459" t="n">
+        <v>67.79000000000001</v>
+      </c>
+      <c r="D459" t="n">
+        <v>0</v>
+      </c>
+      <c r="E459" t="n">
+        <v>1010.82</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0</v>
+      </c>
+      <c r="G459" t="n">
+        <v>4773.349999999999</v>
+      </c>
+      <c r="H459" t="n">
+        <v>4773.349999999999</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="B460" t="n">
+        <v>3705.97</v>
+      </c>
+      <c r="C460" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="D460" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="E460" t="n">
+        <v>1008.11</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0</v>
+      </c>
+      <c r="G460" t="n">
+        <v>4800.24</v>
+      </c>
+      <c r="H460" t="n">
+        <v>4800.24</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B461" t="n">
+        <v>3763.64</v>
+      </c>
+      <c r="C461" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="D461" t="n">
+        <v>0</v>
+      </c>
+      <c r="E461" t="n">
+        <v>1013.06</v>
+      </c>
+      <c r="F461" t="n">
+        <v>0</v>
+      </c>
+      <c r="G461" t="n">
+        <v>4838.29</v>
+      </c>
+      <c r="H461" t="n">
+        <v>4838.29</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="B462" t="n">
+        <v>3816.37</v>
+      </c>
+      <c r="C462" t="n">
+        <v>61.47</v>
+      </c>
+      <c r="D462" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="E462" t="n">
+        <v>1040.7</v>
+      </c>
+      <c r="F462" t="n">
+        <v>0</v>
+      </c>
+      <c r="G462" t="n">
+        <v>4934.179999999999</v>
+      </c>
+      <c r="H462" t="n">
+        <v>4934.179999999999</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n">
+        <v>46302.60416666666</v>
+      </c>
+      <c r="B463" t="n">
+        <v>3905.69</v>
+      </c>
+      <c r="C463" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="D463" t="n">
+        <v>0</v>
+      </c>
+      <c r="E463" t="n">
+        <v>1043.98</v>
+      </c>
+      <c r="F463" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="G463" t="n">
+        <v>5031.76</v>
+      </c>
+      <c r="H463" t="n">
+        <v>5015.58</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n">
+        <v>46302.625</v>
+      </c>
+      <c r="B464" t="n">
+        <v>3912.77</v>
+      </c>
+      <c r="C464" t="n">
+        <v>65.38</v>
+      </c>
+      <c r="D464" t="n">
+        <v>0</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1043.75</v>
+      </c>
+      <c r="F464" t="n">
+        <v>0</v>
+      </c>
+      <c r="G464" t="n">
+        <v>5021.9</v>
+      </c>
+      <c r="H464" t="n">
+        <v>5021.9</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="B465" t="n">
+        <v>3951.66</v>
+      </c>
+      <c r="C465" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="D465" t="n">
+        <v>0</v>
+      </c>
+      <c r="E465" t="n">
+        <v>1023.81</v>
+      </c>
+      <c r="F465" t="n">
+        <v>0</v>
+      </c>
+      <c r="G465" t="n">
+        <v>5028.33</v>
+      </c>
+      <c r="H465" t="n">
+        <v>5028.33</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="B466" t="n">
+        <v>3876.83</v>
+      </c>
+      <c r="C466" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="D466" t="n">
+        <v>0</v>
+      </c>
+      <c r="E466" t="n">
+        <v>1016.78</v>
+      </c>
+      <c r="F466" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G466" t="n">
+        <v>4941.35</v>
+      </c>
+      <c r="H466" t="n">
+        <v>4939.25</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n">
+        <v>46302.6875</v>
+      </c>
+      <c r="B467" t="n">
+        <v>3802.15</v>
+      </c>
+      <c r="C467" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="D467" t="n">
+        <v>0</v>
+      </c>
+      <c r="E467" t="n">
+        <v>1035.47</v>
+      </c>
+      <c r="F467" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G467" t="n">
+        <v>4875.240000000001</v>
+      </c>
+      <c r="H467" t="n">
+        <v>4873.43</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="B468" t="n">
+        <v>3684.19</v>
+      </c>
+      <c r="C468" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D468" t="n">
+        <v>0</v>
+      </c>
+      <c r="E468" t="n">
+        <v>1042.46</v>
+      </c>
+      <c r="F468" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G468" t="n">
+        <v>4780.25</v>
+      </c>
+      <c r="H468" t="n">
+        <v>4760.75</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n">
+        <v>46302.72916666666</v>
+      </c>
+      <c r="B469" t="n">
+        <v>3601.53</v>
+      </c>
+      <c r="C469" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="D469" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E469" t="n">
+        <v>1041.91</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0</v>
+      </c>
+      <c r="G469" t="n">
+        <v>4685.54</v>
+      </c>
+      <c r="H469" t="n">
+        <v>4685.54</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="n">
+        <v>46302.75</v>
+      </c>
+      <c r="B470" t="n">
+        <v>3599.34</v>
+      </c>
+      <c r="C470" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="D470" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="E470" t="n">
+        <v>1039.22</v>
+      </c>
+      <c r="F470" t="n">
+        <v>0</v>
+      </c>
+      <c r="G470" t="n">
+        <v>4681.21</v>
+      </c>
+      <c r="H470" t="n">
+        <v>4681.21</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="n">
+        <v>46302.77083333334</v>
+      </c>
+      <c r="B471" t="n">
+        <v>3989.1</v>
+      </c>
+      <c r="C471" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="D471" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="E471" t="n">
+        <v>1045.14</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0</v>
+      </c>
+      <c r="G471" t="n">
+        <v>5055.97</v>
+      </c>
+      <c r="H471" t="n">
+        <v>5055.97</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="n">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="B472" t="n">
+        <v>4024.09</v>
+      </c>
+      <c r="C472" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D472" t="n">
+        <v>0</v>
+      </c>
+      <c r="E472" t="n">
+        <v>1061.3</v>
+      </c>
+      <c r="F472" t="n">
+        <v>0</v>
+      </c>
+      <c r="G472" t="n">
+        <v>5098.04</v>
+      </c>
+      <c r="H472" t="n">
+        <v>5098.04</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="n">
+        <v>46302.8125</v>
+      </c>
+      <c r="B473" t="n">
+        <v>4063.31</v>
+      </c>
+      <c r="C473" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D473" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="E473" t="n">
+        <v>1053.51</v>
+      </c>
+      <c r="F473" t="n">
+        <v>0</v>
+      </c>
+      <c r="G473" t="n">
+        <v>5134.04</v>
+      </c>
+      <c r="H473" t="n">
+        <v>5134.04</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="n">
+        <v>46302.83333333334</v>
+      </c>
+      <c r="B474" t="n">
+        <v>4023.08</v>
+      </c>
+      <c r="C474" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="D474" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="E474" t="n">
+        <v>1054.57</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0</v>
+      </c>
+      <c r="G474" t="n">
+        <v>5101.7</v>
+      </c>
+      <c r="H474" t="n">
+        <v>5101.7</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="n">
+        <v>46302.85416666666</v>
+      </c>
+      <c r="B475" t="n">
+        <v>3998.06</v>
+      </c>
+      <c r="C475" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="D475" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="E475" t="n">
+        <v>1060.78</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0</v>
+      </c>
+      <c r="G475" t="n">
+        <v>5083.48</v>
+      </c>
+      <c r="H475" t="n">
+        <v>5083.48</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="n">
+        <v>46302.875</v>
+      </c>
+      <c r="B476" t="n">
+        <v>3910.88</v>
+      </c>
+      <c r="C476" t="n">
+        <v>8</v>
+      </c>
+      <c r="D476" t="n">
+        <v>0</v>
+      </c>
+      <c r="E476" t="n">
+        <v>1066.73</v>
+      </c>
+      <c r="F476" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="G476" t="n">
+        <v>5002.66</v>
+      </c>
+      <c r="H476" t="n">
+        <v>4985.61</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="n">
+        <v>46302.89583333334</v>
+      </c>
+      <c r="B477" t="n">
+        <v>3812.4</v>
+      </c>
+      <c r="C477" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="D477" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E477" t="n">
+        <v>1068.01</v>
+      </c>
+      <c r="F477" t="n">
+        <v>0</v>
+      </c>
+      <c r="G477" t="n">
+        <v>4912.14</v>
+      </c>
+      <c r="H477" t="n">
+        <v>4912.14</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="n">
+        <v>46302.91666666666</v>
+      </c>
+      <c r="B478" t="n">
+        <v>3706.96</v>
+      </c>
+      <c r="C478" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="D478" t="n">
+        <v>0</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1063.42</v>
+      </c>
+      <c r="F478" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="G478" t="n">
+        <v>4798.13</v>
+      </c>
+      <c r="H478" t="n">
+        <v>4778.41</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="n">
+        <v>46302.9375</v>
+      </c>
+      <c r="B479" t="n">
+        <v>3616.91</v>
+      </c>
+      <c r="C479" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="D479" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1066.84</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0</v>
+      </c>
+      <c r="G479" t="n">
+        <v>4703.2</v>
+      </c>
+      <c r="H479" t="n">
+        <v>4703.2</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="n">
+        <v>46302.95833333334</v>
+      </c>
+      <c r="B480" t="n">
+        <v>3504.32</v>
+      </c>
+      <c r="C480" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="D480" t="n">
+        <v>0</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1025.34</v>
+      </c>
+      <c r="F480" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="G480" t="n">
+        <v>4557.96</v>
+      </c>
+      <c r="H480" t="n">
+        <v>4537.49</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="n">
+        <v>46302.97916666666</v>
+      </c>
+      <c r="B481" t="n">
+        <v>3348.84</v>
+      </c>
+      <c r="C481" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D481" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1042.15</v>
+      </c>
+      <c r="F481" t="n">
+        <v>0</v>
+      </c>
+      <c r="G481" t="n">
+        <v>4405.55</v>
+      </c>
+      <c r="H481" t="n">
+        <v>4405.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1138,59 @@
       </c>
       <c r="Q11" t="n">
         <v>0.004</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92681</v>
+      </c>
+      <c r="C12" t="n">
+        <v>72231</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19644</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18023</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1621</v>
+      </c>
+      <c r="G12" t="n">
+        <v>697</v>
+      </c>
+      <c r="H12" t="n">
+        <v>109</v>
+      </c>
+      <c r="I12" t="n">
+        <v>79</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.862</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.003</v>
       </c>
     </row>
   </sheetData>
@@ -1151,7 +1204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1182,17 +1235,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Delsitanisagua</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Mazar</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -1223,13 +1276,13 @@
         <v>8114</v>
       </c>
       <c r="F2" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G2" t="n">
         <v>2301</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>2768</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3724</v>
       </c>
       <c r="I2" t="n">
         <v>2003</v>
@@ -1255,13 +1308,13 @@
         <v>8424</v>
       </c>
       <c r="F3" t="n">
+        <v>3644</v>
+      </c>
+      <c r="G3" t="n">
         <v>2554</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2477</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3644</v>
       </c>
       <c r="I3" t="n">
         <v>1820</v>
@@ -1287,13 +1340,13 @@
         <v>9735</v>
       </c>
       <c r="F4" t="n">
+        <v>3194</v>
+      </c>
+      <c r="G4" t="n">
         <v>2604</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2491</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3194</v>
       </c>
       <c r="I4" t="n">
         <v>1820</v>
@@ -1319,13 +1372,13 @@
         <v>8469</v>
       </c>
       <c r="F5" t="n">
+        <v>3026</v>
+      </c>
+      <c r="G5" t="n">
         <v>2307</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>2773</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3026</v>
       </c>
       <c r="I5" t="n">
         <v>2009</v>
@@ -1351,13 +1404,13 @@
         <v>8416</v>
       </c>
       <c r="F6" t="n">
+        <v>3345</v>
+      </c>
+      <c r="G6" t="n">
         <v>3102</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>2472</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3345</v>
       </c>
       <c r="I6" t="n">
         <v>1847</v>
@@ -1383,13 +1436,13 @@
         <v>5868</v>
       </c>
       <c r="F7" t="n">
+        <v>2963</v>
+      </c>
+      <c r="G7" t="n">
         <v>2187</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>2512</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2963</v>
       </c>
       <c r="I7" t="n">
         <v>1853</v>
@@ -1414,12 +1467,12 @@
       <c r="E8" t="n">
         <v>2907</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="F8" t="n">
+        <v>3431</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>2854</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3431</v>
       </c>
       <c r="I8" t="n">
         <v>2034</v>
@@ -1445,13 +1498,13 @@
         <v>8041</v>
       </c>
       <c r="F9" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G9" t="n">
         <v>1164</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2801</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2788</v>
       </c>
       <c r="I9" t="n">
         <v>2027</v>
@@ -1477,13 +1530,13 @@
         <v>9960</v>
       </c>
       <c r="F10" t="n">
+        <v>2675</v>
+      </c>
+      <c r="G10" t="n">
         <v>2157</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>2566</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2675</v>
       </c>
       <c r="I10" t="n">
         <v>1907</v>
@@ -1509,19 +1562,51 @@
         <v>9798</v>
       </c>
       <c r="F11" t="n">
+        <v>2526</v>
+      </c>
+      <c r="G11" t="n">
         <v>2831</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>2706</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2526</v>
       </c>
       <c r="I11" t="n">
         <v>1966</v>
       </c>
       <c r="J11" t="n">
         <v>1693</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>20083</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16518</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16208</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9495</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2565</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2551</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2525</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1838</v>
+      </c>
+      <c r="J12" t="n">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -1535,7 +1620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1845,21 +1930,17 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1868,7 +1949,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>24721</v>
+        <v>20083</v>
       </c>
     </row>
     <row r="13">
@@ -1876,7 +1957,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,7 +1980,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>23420</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="14">
@@ -1907,7 +1988,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,7 +2011,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>19992</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="15">
@@ -1938,7 +2019,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1961,7 +2042,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>17987</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="16">
@@ -1969,7 +2050,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1992,7 +2073,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>17990</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="17">
@@ -2000,7 +2081,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2023,7 +2104,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>22254</v>
+        <v>17990</v>
       </c>
     </row>
     <row r="18">
@@ -2031,7 +2112,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2054,7 +2135,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>26473</v>
+        <v>22254</v>
       </c>
     </row>
     <row r="19">
@@ -2062,7 +2143,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2085,7 +2166,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>23346</v>
+        <v>26473</v>
       </c>
     </row>
     <row r="20">
@@ -2093,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2116,7 +2197,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>19157</v>
+        <v>23346</v>
       </c>
     </row>
     <row r="21">
@@ -2124,7 +2205,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2147,7 +2228,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>19048</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="22">
@@ -2155,21 +2236,21 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46291</v>
+        <v>46302</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2178,7 +2259,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>13964</v>
+        <v>19048</v>
       </c>
     </row>
     <row r="23">
@@ -2186,21 +2267,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46293</v>
+        <v>46305</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2209,7 +2290,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>16681</v>
+        <v>16518</v>
       </c>
     </row>
     <row r="24">
@@ -2217,7 +2298,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2240,7 +2321,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>17645</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="25">
@@ -2248,7 +2329,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2271,7 +2352,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>14882</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="26">
@@ -2279,7 +2360,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2302,7 +2383,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>14644</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="27">
@@ -2310,7 +2391,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2333,7 +2414,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>10078</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="28">
@@ -2341,7 +2422,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2364,7 +2445,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5014</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="29">
@@ -2372,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2395,7 +2476,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>14358</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="30">
@@ -2403,7 +2484,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2426,7 +2507,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>18959</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="31">
@@ -2434,7 +2515,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2457,7 +2538,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>18347</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="32">
@@ -2465,11 +2546,11 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46291</v>
+        <v>46301</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2488,7 +2569,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8114</v>
+        <v>18959</v>
       </c>
     </row>
     <row r="33">
@@ -2496,11 +2577,11 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2519,7 +2600,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8424</v>
+        <v>18347</v>
       </c>
     </row>
     <row r="34">
@@ -2527,11 +2608,11 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46294</v>
+        <v>46305</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2550,7 +2631,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>9735</v>
+        <v>16208</v>
       </c>
     </row>
     <row r="35">
@@ -2558,7 +2639,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2581,7 +2662,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>8469</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="36">
@@ -2589,7 +2670,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2612,7 +2693,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>8416</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="37">
@@ -2620,7 +2701,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2643,7 +2724,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5868</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="38">
@@ -2651,7 +2732,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2674,7 +2755,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2907</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="39">
@@ -2682,7 +2763,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2705,7 +2786,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>8041</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="40">
@@ -2713,7 +2794,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2736,7 +2817,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>9960</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="41">
@@ -2744,7 +2825,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46302</v>
+        <v>46298</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2767,7 +2848,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>9798</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="42">
@@ -2775,11 +2856,11 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2798,7 +2879,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2301</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="43">
@@ -2806,11 +2887,11 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2829,7 +2910,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2554</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="44">
@@ -2837,11 +2918,11 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2860,7 +2941,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2604</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="45">
@@ -2868,11 +2949,11 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2891,7 +2972,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2307</v>
+        <v>9495</v>
       </c>
     </row>
     <row r="46">
@@ -2899,21 +2980,21 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2922,7 +3003,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3102</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="47">
@@ -2930,21 +3011,21 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2953,7 +3034,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2187</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="48">
@@ -2961,21 +3042,21 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46300</v>
+        <v>46294</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2984,7 +3065,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1164</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="49">
@@ -2992,21 +3073,21 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46301</v>
+        <v>46295</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3015,7 +3096,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2157</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="50">
@@ -3023,21 +3104,21 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3046,7 +3127,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2831</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="51">
@@ -3054,21 +3135,21 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3077,7 +3158,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2768</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="52">
@@ -3085,21 +3166,21 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3108,7 +3189,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2477</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="53">
@@ -3116,21 +3197,21 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3139,7 +3220,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2491</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="54">
@@ -3147,21 +3228,21 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3170,7 +3251,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2773</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="55">
@@ -3178,21 +3259,21 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3201,7 +3282,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2472</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="56">
@@ -3209,21 +3290,21 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46297</v>
+        <v>46305</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3232,7 +3313,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2512</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="57">
@@ -3240,16 +3321,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3263,7 +3344,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2854</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="58">
@@ -3271,16 +3352,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3294,7 +3375,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2801</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="59">
@@ -3302,16 +3383,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3325,7 +3406,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2566</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="60">
@@ -3333,16 +3414,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3356,7 +3437,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2706</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="61">
@@ -3364,21 +3445,21 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3387,7 +3468,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>3724</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="62">
@@ -3395,21 +3476,21 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3418,7 +3499,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3644</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="63">
@@ -3426,21 +3507,21 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3449,7 +3530,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3194</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="64">
@@ -3457,21 +3538,21 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3480,7 +3561,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>3026</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="65">
@@ -3488,21 +3569,21 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3511,7 +3592,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3345</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="66">
@@ -3519,21 +3600,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46297</v>
+        <v>46305</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3542,7 +3623,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2963</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="67">
@@ -3550,21 +3631,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3573,7 +3654,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>3431</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="68">
@@ -3581,21 +3662,21 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3604,7 +3685,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2788</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="69">
@@ -3612,21 +3693,21 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3635,7 +3716,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2675</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="70">
@@ -3643,21 +3724,21 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3666,7 +3747,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2526</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="71">
@@ -3674,11 +3755,11 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3697,7 +3778,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2003</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="72">
@@ -3705,11 +3786,11 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3728,7 +3809,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1820</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="73">
@@ -3736,11 +3817,11 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3759,7 +3840,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1820</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="74">
@@ -3767,11 +3848,11 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3790,7 +3871,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2009</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="75">
@@ -3798,11 +3879,11 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3821,7 +3902,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1847</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="76">
@@ -3829,11 +3910,11 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3852,7 +3933,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1853</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="77">
@@ -3860,11 +3941,11 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3883,7 +3964,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2034</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="78">
@@ -3891,7 +3972,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46300</v>
+        <v>46291</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3914,7 +3995,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2027</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="79">
@@ -3922,7 +4003,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3945,7 +4026,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1907</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="80">
@@ -3953,7 +4034,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46302</v>
+        <v>46294</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3976,7 +4057,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1966</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="81">
@@ -3984,16 +4065,16 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4007,7 +4088,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>239</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="82">
@@ -4015,16 +4096,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4038,7 +4119,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1531</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="83">
@@ -4046,16 +4127,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4069,7 +4150,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>306</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="84">
@@ -4077,16 +4158,16 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4100,7 +4181,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>721</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="85">
@@ -4108,16 +4189,16 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4131,7 +4212,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>750</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="86">
@@ -4139,16 +4220,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4162,7 +4243,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>461</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="87">
@@ -4170,16 +4251,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4193,7 +4274,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1105</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="88">
@@ -4201,16 +4282,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4224,7 +4305,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1488</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="89">
@@ -4232,7 +4313,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46301</v>
+        <v>46291</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4255,7 +4336,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1870</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90">
@@ -4263,30 +4344,309 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="2" t="n">
         <v>46302</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Minas San Francisco</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G90" t="n">
+      <c r="G98" t="n">
         <v>1693</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -4300,7 +4660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H481"/>
+  <dimension ref="A1:H529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16825,6 +17185,1254 @@
         <v>4405.55</v>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B482" t="n">
+        <v>3139.46</v>
+      </c>
+      <c r="C482" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="D482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E482" t="n">
+        <v>818.77</v>
+      </c>
+      <c r="F482" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="G482" t="n">
+        <v>3993.13</v>
+      </c>
+      <c r="H482" t="n">
+        <v>3977.72</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="n">
+        <v>46305.02083333334</v>
+      </c>
+      <c r="B483" t="n">
+        <v>3040.69</v>
+      </c>
+      <c r="C483" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D483" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E483" t="n">
+        <v>804.16</v>
+      </c>
+      <c r="F483" t="n">
+        <v>0</v>
+      </c>
+      <c r="G483" t="n">
+        <v>3867.16</v>
+      </c>
+      <c r="H483" t="n">
+        <v>3867.16</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="n">
+        <v>46305.04166666666</v>
+      </c>
+      <c r="B484" t="n">
+        <v>2959.61</v>
+      </c>
+      <c r="C484" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="D484" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E484" t="n">
+        <v>793.6799999999999</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0</v>
+      </c>
+      <c r="G484" t="n">
+        <v>3770.27</v>
+      </c>
+      <c r="H484" t="n">
+        <v>3770.27</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="n">
+        <v>46305.0625</v>
+      </c>
+      <c r="B485" t="n">
+        <v>2849.51</v>
+      </c>
+      <c r="C485" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="D485" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E485" t="n">
+        <v>801.79</v>
+      </c>
+      <c r="F485" t="n">
+        <v>0</v>
+      </c>
+      <c r="G485" t="n">
+        <v>3676.85</v>
+      </c>
+      <c r="H485" t="n">
+        <v>3676.85</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="n">
+        <v>46305.08333333334</v>
+      </c>
+      <c r="B486" t="n">
+        <v>2773.97</v>
+      </c>
+      <c r="C486" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="n">
+        <v>806.14</v>
+      </c>
+      <c r="F486" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G486" t="n">
+        <v>3598.17</v>
+      </c>
+      <c r="H486" t="n">
+        <v>3594.75</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="n">
+        <v>46305.10416666666</v>
+      </c>
+      <c r="B487" t="n">
+        <v>2698.76</v>
+      </c>
+      <c r="C487" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="D487" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="E487" t="n">
+        <v>817.76</v>
+      </c>
+      <c r="F487" t="n">
+        <v>0</v>
+      </c>
+      <c r="G487" t="n">
+        <v>3542.97</v>
+      </c>
+      <c r="H487" t="n">
+        <v>3542.97</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="n">
+        <v>46305.125</v>
+      </c>
+      <c r="B488" t="n">
+        <v>2621.57</v>
+      </c>
+      <c r="C488" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="D488" t="n">
+        <v>20</v>
+      </c>
+      <c r="E488" t="n">
+        <v>814.0599999999999</v>
+      </c>
+      <c r="F488" t="n">
+        <v>0</v>
+      </c>
+      <c r="G488" t="n">
+        <v>3469.29</v>
+      </c>
+      <c r="H488" t="n">
+        <v>3469.29</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="n">
+        <v>46305.14583333334</v>
+      </c>
+      <c r="B489" t="n">
+        <v>2584.54</v>
+      </c>
+      <c r="C489" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="D489" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="E489" t="n">
+        <v>814.25</v>
+      </c>
+      <c r="F489" t="n">
+        <v>0</v>
+      </c>
+      <c r="G489" t="n">
+        <v>3414.89</v>
+      </c>
+      <c r="H489" t="n">
+        <v>3414.89</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="n">
+        <v>46305.16666666666</v>
+      </c>
+      <c r="B490" t="n">
+        <v>2542.87</v>
+      </c>
+      <c r="C490" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="D490" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="E490" t="n">
+        <v>805.92</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0</v>
+      </c>
+      <c r="G490" t="n">
+        <v>3368.99</v>
+      </c>
+      <c r="H490" t="n">
+        <v>3368.99</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="n">
+        <v>46305.1875</v>
+      </c>
+      <c r="B491" t="n">
+        <v>2500.91</v>
+      </c>
+      <c r="C491" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="D491" t="n">
+        <v>0</v>
+      </c>
+      <c r="E491" t="n">
+        <v>820.85</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0</v>
+      </c>
+      <c r="G491" t="n">
+        <v>3333.79</v>
+      </c>
+      <c r="H491" t="n">
+        <v>3333.79</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="n">
+        <v>46305.20833333334</v>
+      </c>
+      <c r="B492" t="n">
+        <v>2465.04</v>
+      </c>
+      <c r="C492" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="D492" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E492" t="n">
+        <v>831.61</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0</v>
+      </c>
+      <c r="G492" t="n">
+        <v>3309.12</v>
+      </c>
+      <c r="H492" t="n">
+        <v>3309.12</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="n">
+        <v>46305.22916666666</v>
+      </c>
+      <c r="B493" t="n">
+        <v>2455.08</v>
+      </c>
+      <c r="C493" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="D493" t="n">
+        <v>0</v>
+      </c>
+      <c r="E493" t="n">
+        <v>835.42</v>
+      </c>
+      <c r="F493" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G493" t="n">
+        <v>3315.47</v>
+      </c>
+      <c r="H493" t="n">
+        <v>3303.77</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="n">
+        <v>46305.25</v>
+      </c>
+      <c r="B494" t="n">
+        <v>2361.92</v>
+      </c>
+      <c r="C494" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="D494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E494" t="n">
+        <v>836.14</v>
+      </c>
+      <c r="F494" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="G494" t="n">
+        <v>3225.79</v>
+      </c>
+      <c r="H494" t="n">
+        <v>3209.55</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="n">
+        <v>46305.27083333334</v>
+      </c>
+      <c r="B495" t="n">
+        <v>2138.58</v>
+      </c>
+      <c r="C495" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="D495" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="E495" t="n">
+        <v>835.66</v>
+      </c>
+      <c r="F495" t="n">
+        <v>0</v>
+      </c>
+      <c r="G495" t="n">
+        <v>3001.36</v>
+      </c>
+      <c r="H495" t="n">
+        <v>3001.36</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="n">
+        <v>46305.29166666666</v>
+      </c>
+      <c r="B496" t="n">
+        <v>2182.02</v>
+      </c>
+      <c r="C496" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="D496" t="n">
+        <v>0</v>
+      </c>
+      <c r="E496" t="n">
+        <v>833.47</v>
+      </c>
+      <c r="F496" t="n">
+        <v>0</v>
+      </c>
+      <c r="G496" t="n">
+        <v>3030.7</v>
+      </c>
+      <c r="H496" t="n">
+        <v>3030.7</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="n">
+        <v>46305.3125</v>
+      </c>
+      <c r="B497" t="n">
+        <v>2284.49</v>
+      </c>
+      <c r="C497" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D497" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="E497" t="n">
+        <v>835.23</v>
+      </c>
+      <c r="F497" t="n">
+        <v>0</v>
+      </c>
+      <c r="G497" t="n">
+        <v>3149.17</v>
+      </c>
+      <c r="H497" t="n">
+        <v>3149.17</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="n">
+        <v>46305.33333333334</v>
+      </c>
+      <c r="B498" t="n">
+        <v>2442.88</v>
+      </c>
+      <c r="C498" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="D498" t="n">
+        <v>0</v>
+      </c>
+      <c r="E498" t="n">
+        <v>832.49</v>
+      </c>
+      <c r="F498" t="n">
+        <v>0</v>
+      </c>
+      <c r="G498" t="n">
+        <v>3290.85</v>
+      </c>
+      <c r="H498" t="n">
+        <v>3290.85</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="n">
+        <v>46305.35416666666</v>
+      </c>
+      <c r="B499" t="n">
+        <v>2615.62</v>
+      </c>
+      <c r="C499" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="D499" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E499" t="n">
+        <v>822.4299999999999</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0</v>
+      </c>
+      <c r="G499" t="n">
+        <v>3457.62</v>
+      </c>
+      <c r="H499" t="n">
+        <v>3457.62</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="n">
+        <v>46305.375</v>
+      </c>
+      <c r="B500" t="n">
+        <v>2760.01</v>
+      </c>
+      <c r="C500" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="D500" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E500" t="n">
+        <v>820.15</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0</v>
+      </c>
+      <c r="G500" t="n">
+        <v>3598.26</v>
+      </c>
+      <c r="H500" t="n">
+        <v>3598.26</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="n">
+        <v>46305.39583333334</v>
+      </c>
+      <c r="B501" t="n">
+        <v>2919.84</v>
+      </c>
+      <c r="C501" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="D501" t="n">
+        <v>0</v>
+      </c>
+      <c r="E501" t="n">
+        <v>819.3</v>
+      </c>
+      <c r="F501" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="G501" t="n">
+        <v>3765.03</v>
+      </c>
+      <c r="H501" t="n">
+        <v>3756.46</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46305.41666666666</v>
+      </c>
+      <c r="B502" t="n">
+        <v>3028.3</v>
+      </c>
+      <c r="C502" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="D502" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E502" t="n">
+        <v>814.33</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0</v>
+      </c>
+      <c r="G502" t="n">
+        <v>3866.43</v>
+      </c>
+      <c r="H502" t="n">
+        <v>3866.43</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>46305.4375</v>
+      </c>
+      <c r="B503" t="n">
+        <v>3126.6</v>
+      </c>
+      <c r="C503" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="D503" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="E503" t="n">
+        <v>812.38</v>
+      </c>
+      <c r="F503" t="n">
+        <v>0</v>
+      </c>
+      <c r="G503" t="n">
+        <v>3965.69</v>
+      </c>
+      <c r="H503" t="n">
+        <v>3965.69</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="n">
+        <v>46305.45833333334</v>
+      </c>
+      <c r="B504" t="n">
+        <v>3190.06</v>
+      </c>
+      <c r="C504" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="D504" t="n">
+        <v>0</v>
+      </c>
+      <c r="E504" t="n">
+        <v>816.17</v>
+      </c>
+      <c r="F504" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G504" t="n">
+        <v>4042.64</v>
+      </c>
+      <c r="H504" t="n">
+        <v>4036.78</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="n">
+        <v>46305.47916666666</v>
+      </c>
+      <c r="B505" t="n">
+        <v>3205.24</v>
+      </c>
+      <c r="C505" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="D505" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="E505" t="n">
+        <v>811.01</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0</v>
+      </c>
+      <c r="G505" t="n">
+        <v>4086.05</v>
+      </c>
+      <c r="H505" t="n">
+        <v>4086.05</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="n">
+        <v>46305.5</v>
+      </c>
+      <c r="B506" t="n">
+        <v>3247.77</v>
+      </c>
+      <c r="C506" t="n">
+        <v>75</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+      <c r="E506" t="n">
+        <v>817.88</v>
+      </c>
+      <c r="F506" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G506" t="n">
+        <v>4143.21</v>
+      </c>
+      <c r="H506" t="n">
+        <v>4140.65</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="n">
+        <v>46305.52083333334</v>
+      </c>
+      <c r="B507" t="n">
+        <v>3283.23</v>
+      </c>
+      <c r="C507" t="n">
+        <v>73.83</v>
+      </c>
+      <c r="D507" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E507" t="n">
+        <v>804.35</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0</v>
+      </c>
+      <c r="G507" t="n">
+        <v>4165.43</v>
+      </c>
+      <c r="H507" t="n">
+        <v>4165.43</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="n">
+        <v>46305.54166666666</v>
+      </c>
+      <c r="B508" t="n">
+        <v>3306.72</v>
+      </c>
+      <c r="C508" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="D508" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="E508" t="n">
+        <v>808.39</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" t="n">
+        <v>4203.67</v>
+      </c>
+      <c r="H508" t="n">
+        <v>4203.67</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="n">
+        <v>46305.5625</v>
+      </c>
+      <c r="B509" t="n">
+        <v>3335.47</v>
+      </c>
+      <c r="C509" t="n">
+        <v>71.73999999999999</v>
+      </c>
+      <c r="D509" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="E509" t="n">
+        <v>826.65</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0</v>
+      </c>
+      <c r="G509" t="n">
+        <v>4252.419999999999</v>
+      </c>
+      <c r="H509" t="n">
+        <v>4252.419999999999</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="n">
+        <v>46305.58333333334</v>
+      </c>
+      <c r="B510" t="n">
+        <v>3367.37</v>
+      </c>
+      <c r="C510" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0</v>
+      </c>
+      <c r="E510" t="n">
+        <v>819.04</v>
+      </c>
+      <c r="F510" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="G510" t="n">
+        <v>4266.009999999999</v>
+      </c>
+      <c r="H510" t="n">
+        <v>4257.28</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
+        <v>46305.60416666666</v>
+      </c>
+      <c r="B511" t="n">
+        <v>3349.15</v>
+      </c>
+      <c r="C511" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="D511" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E511" t="n">
+        <v>829.1900000000001</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0</v>
+      </c>
+      <c r="G511" t="n">
+        <v>4256.15</v>
+      </c>
+      <c r="H511" t="n">
+        <v>4256.15</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>46305.625</v>
+      </c>
+      <c r="B512" t="n">
+        <v>3373.81</v>
+      </c>
+      <c r="C512" t="n">
+        <v>66.98</v>
+      </c>
+      <c r="D512" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="E512" t="n">
+        <v>823.54</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0</v>
+      </c>
+      <c r="G512" t="n">
+        <v>4270.549999999999</v>
+      </c>
+      <c r="H512" t="n">
+        <v>4270.549999999999</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="n">
+        <v>46305.64583333334</v>
+      </c>
+      <c r="B513" t="n">
+        <v>3369.56</v>
+      </c>
+      <c r="C513" t="n">
+        <v>65.26000000000001</v>
+      </c>
+      <c r="D513" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E513" t="n">
+        <v>821.01</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0</v>
+      </c>
+      <c r="G513" t="n">
+        <v>4258.87</v>
+      </c>
+      <c r="H513" t="n">
+        <v>4258.87</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>46305.66666666666</v>
+      </c>
+      <c r="B514" t="n">
+        <v>3360.46</v>
+      </c>
+      <c r="C514" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="D514" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="E514" t="n">
+        <v>808.2</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0</v>
+      </c>
+      <c r="G514" t="n">
+        <v>4239.36</v>
+      </c>
+      <c r="H514" t="n">
+        <v>4239.36</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>46305.6875</v>
+      </c>
+      <c r="B515" t="n">
+        <v>3331.47</v>
+      </c>
+      <c r="C515" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="D515" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="E515" t="n">
+        <v>833.3200000000001</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0</v>
+      </c>
+      <c r="G515" t="n">
+        <v>4231.39</v>
+      </c>
+      <c r="H515" t="n">
+        <v>4231.39</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="n">
+        <v>46305.70833333334</v>
+      </c>
+      <c r="B516" t="n">
+        <v>3309.71</v>
+      </c>
+      <c r="C516" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="D516" t="n">
+        <v>0</v>
+      </c>
+      <c r="E516" t="n">
+        <v>850.62</v>
+      </c>
+      <c r="F516" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="G516" t="n">
+        <v>4200.14</v>
+      </c>
+      <c r="H516" t="n">
+        <v>4197.650000000001</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="n">
+        <v>46305.72916666666</v>
+      </c>
+      <c r="B517" t="n">
+        <v>3266.15</v>
+      </c>
+      <c r="C517" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="D517" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E517" t="n">
+        <v>862.58</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" t="n">
+        <v>4161.91</v>
+      </c>
+      <c r="H517" t="n">
+        <v>4161.91</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="n">
+        <v>46305.75</v>
+      </c>
+      <c r="B518" t="n">
+        <v>3298.03</v>
+      </c>
+      <c r="C518" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="D518" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E518" t="n">
+        <v>863.63</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0</v>
+      </c>
+      <c r="G518" t="n">
+        <v>4216.11</v>
+      </c>
+      <c r="H518" t="n">
+        <v>4216.11</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="n">
+        <v>46305.77083333334</v>
+      </c>
+      <c r="B519" t="n">
+        <v>3754.99</v>
+      </c>
+      <c r="C519" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="D519" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="E519" t="n">
+        <v>860.08</v>
+      </c>
+      <c r="F519" t="n">
+        <v>0</v>
+      </c>
+      <c r="G519" t="n">
+        <v>4647.46</v>
+      </c>
+      <c r="H519" t="n">
+        <v>4647.46</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="n">
+        <v>46305.79166666666</v>
+      </c>
+      <c r="B520" t="n">
+        <v>3833.44</v>
+      </c>
+      <c r="C520" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="D520" t="n">
+        <v>0</v>
+      </c>
+      <c r="E520" t="n">
+        <v>862.21</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0</v>
+      </c>
+      <c r="G520" t="n">
+        <v>4710.62</v>
+      </c>
+      <c r="H520" t="n">
+        <v>4710.62</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="n">
+        <v>46305.8125</v>
+      </c>
+      <c r="B521" t="n">
+        <v>3824.34</v>
+      </c>
+      <c r="C521" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="D521" t="n">
+        <v>0</v>
+      </c>
+      <c r="E521" t="n">
+        <v>865.38</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0</v>
+      </c>
+      <c r="G521" t="n">
+        <v>4707.13</v>
+      </c>
+      <c r="H521" t="n">
+        <v>4707.13</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="n">
+        <v>46305.83333333334</v>
+      </c>
+      <c r="B522" t="n">
+        <v>3790.13</v>
+      </c>
+      <c r="C522" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="D522" t="n">
+        <v>0</v>
+      </c>
+      <c r="E522" t="n">
+        <v>864.84</v>
+      </c>
+      <c r="F522" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G522" t="n">
+        <v>4674.08</v>
+      </c>
+      <c r="H522" t="n">
+        <v>4671.92</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="n">
+        <v>46305.85416666666</v>
+      </c>
+      <c r="B523" t="n">
+        <v>3741.5</v>
+      </c>
+      <c r="C523" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="D523" t="n">
+        <v>0</v>
+      </c>
+      <c r="E523" t="n">
+        <v>867.85</v>
+      </c>
+      <c r="F523" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="G523" t="n">
+        <v>4633.820000000001</v>
+      </c>
+      <c r="H523" t="n">
+        <v>4625.97</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="n">
+        <v>46305.875</v>
+      </c>
+      <c r="B524" t="n">
+        <v>3666.46</v>
+      </c>
+      <c r="C524" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="D524" t="n">
+        <v>0</v>
+      </c>
+      <c r="E524" t="n">
+        <v>872.24</v>
+      </c>
+      <c r="F524" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="G524" t="n">
+        <v>4587.759999999999</v>
+      </c>
+      <c r="H524" t="n">
+        <v>4553.69</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="n">
+        <v>46305.89583333334</v>
+      </c>
+      <c r="B525" t="n">
+        <v>3605.95</v>
+      </c>
+      <c r="C525" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="D525" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E525" t="n">
+        <v>873.17</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0</v>
+      </c>
+      <c r="G525" t="n">
+        <v>4497.75</v>
+      </c>
+      <c r="H525" t="n">
+        <v>4497.75</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="n">
+        <v>46305.91666666666</v>
+      </c>
+      <c r="B526" t="n">
+        <v>3488.18</v>
+      </c>
+      <c r="C526" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="D526" t="n">
+        <v>0</v>
+      </c>
+      <c r="E526" t="n">
+        <v>876.58</v>
+      </c>
+      <c r="F526" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G526" t="n">
+        <v>4394.59</v>
+      </c>
+      <c r="H526" t="n">
+        <v>4384.31</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="n">
+        <v>46305.9375</v>
+      </c>
+      <c r="B527" t="n">
+        <v>3331.15</v>
+      </c>
+      <c r="C527" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="D527" t="n">
+        <v>0</v>
+      </c>
+      <c r="E527" t="n">
+        <v>932.42</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0</v>
+      </c>
+      <c r="G527" t="n">
+        <v>4283.4</v>
+      </c>
+      <c r="H527" t="n">
+        <v>4283.4</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="n">
+        <v>46305.95833333334</v>
+      </c>
+      <c r="B528" t="n">
+        <v>3208.05</v>
+      </c>
+      <c r="C528" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="D528" t="n">
+        <v>0</v>
+      </c>
+      <c r="E528" t="n">
+        <v>935.16</v>
+      </c>
+      <c r="F528" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="G528" t="n">
+        <v>4188.89</v>
+      </c>
+      <c r="H528" t="n">
+        <v>4162.43</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="n">
+        <v>46305.97916666666</v>
+      </c>
+      <c r="B529" t="n">
+        <v>3082.38</v>
+      </c>
+      <c r="C529" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="D529" t="n">
+        <v>0</v>
+      </c>
+      <c r="E529" t="n">
+        <v>931.64</v>
+      </c>
+      <c r="F529" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="G529" t="n">
+        <v>4055.05</v>
+      </c>
+      <c r="H529" t="n">
+        <v>4033.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1191,6 +1191,59 @@
       </c>
       <c r="Q12" t="n">
         <v>0.003</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95032</v>
+      </c>
+      <c r="C13" t="n">
+        <v>67536</v>
+      </c>
+      <c r="D13" t="n">
+        <v>26933</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25419</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1514</v>
+      </c>
+      <c r="G13" t="n">
+        <v>522</v>
+      </c>
+      <c r="H13" t="n">
+        <v>41</v>
+      </c>
+      <c r="I13" t="n">
+        <v>118</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.814</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.005</v>
       </c>
     </row>
   </sheetData>
@@ -1204,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,22 +1288,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Delsitanisagua</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Agoyán</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>Mazar</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Agoyán</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1276,16 +1329,16 @@
         <v>8114</v>
       </c>
       <c r="F2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="G2" t="n">
         <v>3724</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="I2" t="n">
         <v>2301</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2768</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2003</v>
       </c>
       <c r="J2" t="n">
         <v>239</v>
@@ -1308,16 +1361,16 @@
         <v>8424</v>
       </c>
       <c r="F3" t="n">
+        <v>2477</v>
+      </c>
+      <c r="G3" t="n">
         <v>3644</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I3" t="n">
         <v>2554</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2477</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1820</v>
       </c>
       <c r="J3" t="n">
         <v>1531</v>
@@ -1340,16 +1393,16 @@
         <v>9735</v>
       </c>
       <c r="F4" t="n">
+        <v>2491</v>
+      </c>
+      <c r="G4" t="n">
         <v>3194</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I4" t="n">
         <v>2604</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2491</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1820</v>
       </c>
       <c r="J4" t="n">
         <v>306</v>
@@ -1372,16 +1425,16 @@
         <v>8469</v>
       </c>
       <c r="F5" t="n">
+        <v>2773</v>
+      </c>
+      <c r="G5" t="n">
         <v>3026</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="I5" t="n">
         <v>2307</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2773</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2009</v>
       </c>
       <c r="J5" t="n">
         <v>721</v>
@@ -1404,16 +1457,16 @@
         <v>8416</v>
       </c>
       <c r="F6" t="n">
+        <v>2472</v>
+      </c>
+      <c r="G6" t="n">
         <v>3345</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1847</v>
+      </c>
+      <c r="I6" t="n">
         <v>3102</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2472</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1847</v>
       </c>
       <c r="J6" t="n">
         <v>750</v>
@@ -1436,16 +1489,16 @@
         <v>5868</v>
       </c>
       <c r="F7" t="n">
+        <v>2512</v>
+      </c>
+      <c r="G7" t="n">
         <v>2963</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1853</v>
+      </c>
+      <c r="I7" t="n">
         <v>2187</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2512</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1853</v>
       </c>
       <c r="J7" t="n">
         <v>461</v>
@@ -1468,15 +1521,15 @@
         <v>2907</v>
       </c>
       <c r="F8" t="n">
+        <v>2854</v>
+      </c>
+      <c r="G8" t="n">
         <v>3431</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>2854</v>
-      </c>
-      <c r="I8" t="n">
         <v>2034</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>1105</v>
       </c>
@@ -1498,16 +1551,16 @@
         <v>8041</v>
       </c>
       <c r="F9" t="n">
+        <v>2801</v>
+      </c>
+      <c r="G9" t="n">
         <v>2788</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I9" t="n">
         <v>1164</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2801</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2027</v>
       </c>
       <c r="J9" t="n">
         <v>1488</v>
@@ -1530,16 +1583,16 @@
         <v>9960</v>
       </c>
       <c r="F10" t="n">
+        <v>2566</v>
+      </c>
+      <c r="G10" t="n">
         <v>2675</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>1907</v>
+      </c>
+      <c r="I10" t="n">
         <v>2157</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2566</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1907</v>
       </c>
       <c r="J10" t="n">
         <v>1870</v>
@@ -1562,16 +1615,16 @@
         <v>9798</v>
       </c>
       <c r="F11" t="n">
+        <v>2706</v>
+      </c>
+      <c r="G11" t="n">
         <v>2526</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
+        <v>1966</v>
+      </c>
+      <c r="I11" t="n">
         <v>2831</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2706</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1966</v>
       </c>
       <c r="J11" t="n">
         <v>1693</v>
@@ -1594,19 +1647,51 @@
         <v>9495</v>
       </c>
       <c r="F12" t="n">
+        <v>2525</v>
+      </c>
+      <c r="G12" t="n">
         <v>2565</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
+        <v>1838</v>
+      </c>
+      <c r="I12" t="n">
         <v>2551</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2525</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1838</v>
       </c>
       <c r="J12" t="n">
         <v>447</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B13" t="n">
+        <v>24903</v>
+      </c>
+      <c r="C13" t="n">
+        <v>21674</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6934</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4088</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2823</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2495</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1997</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1358</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1957,21 +2042,17 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1980,7 +2061,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>24721</v>
+        <v>24903</v>
       </c>
     </row>
     <row r="14">
@@ -1988,7 +2069,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,7 +2092,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>23420</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="15">
@@ -2019,7 +2100,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,7 +2123,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19992</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="16">
@@ -2050,7 +2131,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2073,7 +2154,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>17987</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="17">
@@ -2081,7 +2162,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2104,7 +2185,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>17990</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="18">
@@ -2112,7 +2193,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2135,7 +2216,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>22254</v>
+        <v>17990</v>
       </c>
     </row>
     <row r="19">
@@ -2143,7 +2224,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2166,7 +2247,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>26473</v>
+        <v>22254</v>
       </c>
     </row>
     <row r="20">
@@ -2174,7 +2255,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2197,7 +2278,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>23346</v>
+        <v>26473</v>
       </c>
     </row>
     <row r="21">
@@ -2205,7 +2286,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2228,7 +2309,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>19157</v>
+        <v>23346</v>
       </c>
     </row>
     <row r="22">
@@ -2236,7 +2317,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2259,7 +2340,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>19048</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="23">
@@ -2267,7 +2348,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46305</v>
+        <v>46302</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2290,7 +2371,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>16518</v>
+        <v>19048</v>
       </c>
     </row>
     <row r="24">
@@ -2298,21 +2379,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2321,7 +2402,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>13964</v>
+        <v>16518</v>
       </c>
     </row>
     <row r="25">
@@ -2329,21 +2410,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46293</v>
+        <v>46321</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2352,7 +2433,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>16681</v>
+        <v>21674</v>
       </c>
     </row>
     <row r="26">
@@ -2360,7 +2441,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2383,7 +2464,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>17645</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="27">
@@ -2391,7 +2472,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2414,7 +2495,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>14882</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="28">
@@ -2422,7 +2503,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2445,7 +2526,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>14644</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="29">
@@ -2453,7 +2534,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2476,7 +2557,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>10078</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="30">
@@ -2484,7 +2565,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2507,7 +2588,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5014</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="31">
@@ -2515,7 +2596,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2538,7 +2619,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>14358</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="32">
@@ -2546,7 +2627,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2569,7 +2650,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>18959</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="33">
@@ -2577,7 +2658,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2600,7 +2681,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>18347</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="34">
@@ -2608,7 +2689,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46305</v>
+        <v>46301</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2631,7 +2712,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>16208</v>
+        <v>18959</v>
       </c>
     </row>
     <row r="35">
@@ -2639,11 +2720,11 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46291</v>
+        <v>46302</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2662,7 +2743,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>8114</v>
+        <v>18347</v>
       </c>
     </row>
     <row r="36">
@@ -2670,11 +2751,11 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46293</v>
+        <v>46305</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2693,7 +2774,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>8424</v>
+        <v>16208</v>
       </c>
     </row>
     <row r="37">
@@ -2701,11 +2782,11 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46294</v>
+        <v>46321</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2724,7 +2805,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>9735</v>
+        <v>6934</v>
       </c>
     </row>
     <row r="38">
@@ -2732,7 +2813,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2755,7 +2836,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>8469</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="39">
@@ -2763,7 +2844,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2786,7 +2867,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>8416</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="40">
@@ -2794,7 +2875,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2817,7 +2898,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5868</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="41">
@@ -2825,7 +2906,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2848,7 +2929,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2907</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="42">
@@ -2856,7 +2937,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2879,7 +2960,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>8041</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="43">
@@ -2887,7 +2968,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2910,7 +2991,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>9960</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="44">
@@ -2918,7 +2999,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46302</v>
+        <v>46298</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2941,7 +3022,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>9798</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="45">
@@ -2949,7 +3030,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2972,7 +3053,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>9495</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="46">
@@ -2980,21 +3061,21 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46291</v>
+        <v>46301</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3003,7 +3084,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3724</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="47">
@@ -3011,21 +3092,21 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3034,7 +3115,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3644</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="48">
@@ -3042,21 +3123,21 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46294</v>
+        <v>46305</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3065,7 +3146,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3194</v>
+        <v>9495</v>
       </c>
     </row>
     <row r="49">
@@ -3073,21 +3154,21 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46295</v>
+        <v>46321</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3096,7 +3177,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3026</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="50">
@@ -3104,21 +3185,21 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3127,7 +3208,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3345</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="51">
@@ -3135,21 +3216,21 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3158,7 +3239,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2963</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="52">
@@ -3166,21 +3247,21 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3189,7 +3270,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3431</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="53">
@@ -3197,21 +3278,21 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3220,7 +3301,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2788</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="54">
@@ -3228,21 +3309,21 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3251,7 +3332,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2675</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="55">
@@ -3259,21 +3340,21 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3282,7 +3363,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2526</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="56">
@@ -3290,21 +3371,21 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3313,7 +3394,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2565</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="57">
@@ -3321,16 +3402,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3344,7 +3425,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2301</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="58">
@@ -3352,16 +3433,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3375,7 +3456,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2554</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="59">
@@ -3383,16 +3464,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3406,7 +3487,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2604</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="60">
@@ -3414,16 +3495,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3437,7 +3518,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2307</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="61">
@@ -3445,16 +3526,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46296</v>
+        <v>46321</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3468,7 +3549,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>3102</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="62">
@@ -3476,21 +3557,21 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3499,7 +3580,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2187</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="63">
@@ -3507,21 +3588,21 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3530,7 +3611,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1164</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="64">
@@ -3538,21 +3619,21 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3561,7 +3642,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2157</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="65">
@@ -3569,21 +3650,21 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3592,7 +3673,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2831</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="66">
@@ -3600,21 +3681,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46305</v>
+        <v>46296</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3623,7 +3704,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2551</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="67">
@@ -3631,21 +3712,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3654,7 +3735,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2768</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="68">
@@ -3662,21 +3743,21 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3685,7 +3766,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2477</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="69">
@@ -3693,21 +3774,21 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3716,7 +3797,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2491</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="70">
@@ -3724,21 +3805,21 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3747,7 +3828,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2773</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="71">
@@ -3755,21 +3836,21 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3778,7 +3859,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2472</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="72">
@@ -3786,21 +3867,21 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46297</v>
+        <v>46305</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3809,7 +3890,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2512</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="73">
@@ -3817,21 +3898,21 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46298</v>
+        <v>46321</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3840,7 +3921,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2854</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="74">
@@ -3848,11 +3929,11 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46300</v>
+        <v>46291</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3871,7 +3952,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2801</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="75">
@@ -3879,11 +3960,11 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3902,7 +3983,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2566</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="76">
@@ -3910,11 +3991,11 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46302</v>
+        <v>46294</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3933,7 +4014,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2706</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="77">
@@ -3941,11 +4022,11 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46305</v>
+        <v>46295</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3964,7 +4045,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2525</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="78">
@@ -3972,7 +4053,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3995,7 +4076,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2003</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="79">
@@ -4003,7 +4084,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4026,7 +4107,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1820</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="80">
@@ -4034,7 +4115,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4057,7 +4138,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1820</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="81">
@@ -4065,7 +4146,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4088,7 +4169,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2009</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="82">
@@ -4096,7 +4177,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4119,7 +4200,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1847</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="83">
@@ -4127,7 +4208,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4150,7 +4231,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1853</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="84">
@@ -4158,7 +4239,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4181,7 +4262,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>2034</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="85">
@@ -4189,7 +4270,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4212,7 +4293,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2027</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="86">
@@ -4220,16 +4301,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46301</v>
+        <v>46291</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4243,7 +4324,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1907</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="87">
@@ -4251,16 +4332,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46302</v>
+        <v>46293</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4274,7 +4355,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1966</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="88">
@@ -4282,16 +4363,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46305</v>
+        <v>46294</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4305,7 +4386,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1838</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="89">
@@ -4313,11 +4394,11 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4336,7 +4417,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>239</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="90">
@@ -4344,11 +4425,11 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4367,7 +4448,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1531</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="91">
@@ -4375,11 +4456,11 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4398,7 +4479,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>306</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="92">
@@ -4406,11 +4487,11 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4429,7 +4510,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>721</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="93">
@@ -4437,11 +4518,11 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4460,7 +4541,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>750</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="94">
@@ -4468,11 +4549,11 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4491,7 +4572,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>461</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="95">
@@ -4499,11 +4580,11 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4522,7 +4603,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1105</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="96">
@@ -4530,11 +4611,11 @@
         <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4553,7 +4634,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1488</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="97">
@@ -4561,7 +4642,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46301</v>
+        <v>46291</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4584,7 +4665,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1870</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98">
@@ -4592,7 +4673,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46302</v>
+        <v>46293</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4615,7 +4696,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1693</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="99">
@@ -4623,30 +4704,309 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Minas San Francisco</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G99" t="n">
+      <c r="G107" t="n">
         <v>447</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
@@ -4660,7 +5020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H529"/>
+  <dimension ref="A1:H577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18433,6 +18793,1254 @@
         <v>4033.31</v>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B530" t="n">
+        <v>2230.38</v>
+      </c>
+      <c r="C530" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="D530" t="n">
+        <v>0</v>
+      </c>
+      <c r="E530" t="n">
+        <v>1232.01</v>
+      </c>
+      <c r="F530" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="G530" t="n">
+        <v>3489.21</v>
+      </c>
+      <c r="H530" t="n">
+        <v>3472.53</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="n">
+        <v>46321.02083333334</v>
+      </c>
+      <c r="B531" t="n">
+        <v>2314.98</v>
+      </c>
+      <c r="C531" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D531" t="n">
+        <v>0</v>
+      </c>
+      <c r="E531" t="n">
+        <v>1222.62</v>
+      </c>
+      <c r="F531" t="n">
+        <v>0</v>
+      </c>
+      <c r="G531" t="n">
+        <v>3548.1</v>
+      </c>
+      <c r="H531" t="n">
+        <v>3548.1</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="n">
+        <v>46321.04166666666</v>
+      </c>
+      <c r="B532" t="n">
+        <v>2383.59</v>
+      </c>
+      <c r="C532" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D532" t="n">
+        <v>0</v>
+      </c>
+      <c r="E532" t="n">
+        <v>1174.51</v>
+      </c>
+      <c r="F532" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="G532" t="n">
+        <v>3584.51</v>
+      </c>
+      <c r="H532" t="n">
+        <v>3569.4</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="n">
+        <v>46321.0625</v>
+      </c>
+      <c r="B533" t="n">
+        <v>2324.29</v>
+      </c>
+      <c r="C533" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="D533" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="E533" t="n">
+        <v>1169.31</v>
+      </c>
+      <c r="F533" t="n">
+        <v>0</v>
+      </c>
+      <c r="G533" t="n">
+        <v>3517.26</v>
+      </c>
+      <c r="H533" t="n">
+        <v>3517.26</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="n">
+        <v>46321.08333333334</v>
+      </c>
+      <c r="B534" t="n">
+        <v>2287.79</v>
+      </c>
+      <c r="C534" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="D534" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="E534" t="n">
+        <v>1122.41</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0</v>
+      </c>
+      <c r="G534" t="n">
+        <v>3430.21</v>
+      </c>
+      <c r="H534" t="n">
+        <v>3430.21</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="n">
+        <v>46321.10416666666</v>
+      </c>
+      <c r="B535" t="n">
+        <v>2213.09</v>
+      </c>
+      <c r="C535" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="D535" t="n">
+        <v>0</v>
+      </c>
+      <c r="E535" t="n">
+        <v>1112.53</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0</v>
+      </c>
+      <c r="G535" t="n">
+        <v>3336.21</v>
+      </c>
+      <c r="H535" t="n">
+        <v>3336.21</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="n">
+        <v>46321.125</v>
+      </c>
+      <c r="B536" t="n">
+        <v>2198.84</v>
+      </c>
+      <c r="C536" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="D536" t="n">
+        <v>0</v>
+      </c>
+      <c r="E536" t="n">
+        <v>1130.66</v>
+      </c>
+      <c r="F536" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="G536" t="n">
+        <v>3345.84</v>
+      </c>
+      <c r="H536" t="n">
+        <v>3340.01</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>46321.14583333334</v>
+      </c>
+      <c r="B537" t="n">
+        <v>2131.86</v>
+      </c>
+      <c r="C537" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="D537" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E537" t="n">
+        <v>1133.96</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" t="n">
+        <v>3278.41</v>
+      </c>
+      <c r="H537" t="n">
+        <v>3278.41</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>46321.16666666666</v>
+      </c>
+      <c r="B538" t="n">
+        <v>2071.54</v>
+      </c>
+      <c r="C538" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="D538" t="n">
+        <v>0</v>
+      </c>
+      <c r="E538" t="n">
+        <v>1145.81</v>
+      </c>
+      <c r="F538" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G538" t="n">
+        <v>3239.68</v>
+      </c>
+      <c r="H538" t="n">
+        <v>3230.39</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="n">
+        <v>46321.1875</v>
+      </c>
+      <c r="B539" t="n">
+        <v>2089.91</v>
+      </c>
+      <c r="C539" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="D539" t="n">
+        <v>0</v>
+      </c>
+      <c r="E539" t="n">
+        <v>1134.06</v>
+      </c>
+      <c r="F539" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G539" t="n">
+        <v>3243.53</v>
+      </c>
+      <c r="H539" t="n">
+        <v>3234.83</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="n">
+        <v>46321.20833333334</v>
+      </c>
+      <c r="B540" t="n">
+        <v>2092.05</v>
+      </c>
+      <c r="C540" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="D540" t="n">
+        <v>0</v>
+      </c>
+      <c r="E540" t="n">
+        <v>1151.37</v>
+      </c>
+      <c r="F540" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="G540" t="n">
+        <v>3276.71</v>
+      </c>
+      <c r="H540" t="n">
+        <v>3254.889999999999</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="n">
+        <v>46321.22916666666</v>
+      </c>
+      <c r="B541" t="n">
+        <v>2181.31</v>
+      </c>
+      <c r="C541" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="D541" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="E541" t="n">
+        <v>1145.84</v>
+      </c>
+      <c r="F541" t="n">
+        <v>0</v>
+      </c>
+      <c r="G541" t="n">
+        <v>3345.52</v>
+      </c>
+      <c r="H541" t="n">
+        <v>3345.52</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="n">
+        <v>46321.25</v>
+      </c>
+      <c r="B542" t="n">
+        <v>2083.41</v>
+      </c>
+      <c r="C542" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="D542" t="n">
+        <v>0</v>
+      </c>
+      <c r="E542" t="n">
+        <v>1155.91</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0</v>
+      </c>
+      <c r="G542" t="n">
+        <v>3248.49</v>
+      </c>
+      <c r="H542" t="n">
+        <v>3248.49</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="n">
+        <v>46321.27083333334</v>
+      </c>
+      <c r="B543" t="n">
+        <v>2032.76</v>
+      </c>
+      <c r="C543" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="D543" t="n">
+        <v>0</v>
+      </c>
+      <c r="E543" t="n">
+        <v>1149.69</v>
+      </c>
+      <c r="F543" t="n">
+        <v>0</v>
+      </c>
+      <c r="G543" t="n">
+        <v>3191.39</v>
+      </c>
+      <c r="H543" t="n">
+        <v>3191.39</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="n">
+        <v>46321.29166666666</v>
+      </c>
+      <c r="B544" t="n">
+        <v>2021.01</v>
+      </c>
+      <c r="C544" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="D544" t="n">
+        <v>0</v>
+      </c>
+      <c r="E544" t="n">
+        <v>1155.07</v>
+      </c>
+      <c r="F544" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G544" t="n">
+        <v>3186.02</v>
+      </c>
+      <c r="H544" t="n">
+        <v>3183.93</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="n">
+        <v>46321.3125</v>
+      </c>
+      <c r="B545" t="n">
+        <v>2202.6</v>
+      </c>
+      <c r="C545" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="D545" t="n">
+        <v>0</v>
+      </c>
+      <c r="E545" t="n">
+        <v>1155.26</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0</v>
+      </c>
+      <c r="G545" t="n">
+        <v>3365.88</v>
+      </c>
+      <c r="H545" t="n">
+        <v>3365.88</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="n">
+        <v>46321.33333333334</v>
+      </c>
+      <c r="B546" t="n">
+        <v>2400.82</v>
+      </c>
+      <c r="C546" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="D546" t="n">
+        <v>0</v>
+      </c>
+      <c r="E546" t="n">
+        <v>1141.87</v>
+      </c>
+      <c r="F546" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="G546" t="n">
+        <v>3564.58</v>
+      </c>
+      <c r="H546" t="n">
+        <v>3550.62</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="n">
+        <v>46321.35416666666</v>
+      </c>
+      <c r="B547" t="n">
+        <v>2640.38</v>
+      </c>
+      <c r="C547" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D547" t="n">
+        <v>0</v>
+      </c>
+      <c r="E547" t="n">
+        <v>1142.71</v>
+      </c>
+      <c r="F547" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="G547" t="n">
+        <v>3808.44</v>
+      </c>
+      <c r="H547" t="n">
+        <v>3790.72</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="n">
+        <v>46321.375</v>
+      </c>
+      <c r="B548" t="n">
+        <v>2823.78</v>
+      </c>
+      <c r="C548" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="D548" t="n">
+        <v>0</v>
+      </c>
+      <c r="E548" t="n">
+        <v>1148.44</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0</v>
+      </c>
+      <c r="G548" t="n">
+        <v>3980.15</v>
+      </c>
+      <c r="H548" t="n">
+        <v>3980.15</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="n">
+        <v>46321.39583333334</v>
+      </c>
+      <c r="B549" t="n">
+        <v>2986.98</v>
+      </c>
+      <c r="C549" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="D549" t="n">
+        <v>0</v>
+      </c>
+      <c r="E549" t="n">
+        <v>1150.78</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0</v>
+      </c>
+      <c r="G549" t="n">
+        <v>4144.55</v>
+      </c>
+      <c r="H549" t="n">
+        <v>4144.55</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="n">
+        <v>46321.41666666666</v>
+      </c>
+      <c r="B550" t="n">
+        <v>3126.66</v>
+      </c>
+      <c r="C550" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="D550" t="n">
+        <v>0</v>
+      </c>
+      <c r="E550" t="n">
+        <v>1140.62</v>
+      </c>
+      <c r="F550" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="G550" t="n">
+        <v>4299.92</v>
+      </c>
+      <c r="H550" t="n">
+        <v>4275.33</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="n">
+        <v>46321.4375</v>
+      </c>
+      <c r="B551" t="n">
+        <v>3225.98</v>
+      </c>
+      <c r="C551" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="D551" t="n">
+        <v>0</v>
+      </c>
+      <c r="E551" t="n">
+        <v>1134.97</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" t="n">
+        <v>4374.28</v>
+      </c>
+      <c r="H551" t="n">
+        <v>4374.28</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="n">
+        <v>46321.45833333334</v>
+      </c>
+      <c r="B552" t="n">
+        <v>3322.33</v>
+      </c>
+      <c r="C552" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D552" t="n">
+        <v>0</v>
+      </c>
+      <c r="E552" t="n">
+        <v>1138.69</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" t="n">
+        <v>4491.82</v>
+      </c>
+      <c r="H552" t="n">
+        <v>4491.82</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="n">
+        <v>46321.47916666666</v>
+      </c>
+      <c r="B553" t="n">
+        <v>3358.02</v>
+      </c>
+      <c r="C553" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="D553" t="n">
+        <v>0</v>
+      </c>
+      <c r="E553" t="n">
+        <v>1134.84</v>
+      </c>
+      <c r="F553" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G553" t="n">
+        <v>4567.19</v>
+      </c>
+      <c r="H553" t="n">
+        <v>4564.58</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="n">
+        <v>46321.5</v>
+      </c>
+      <c r="B554" t="n">
+        <v>3412.99</v>
+      </c>
+      <c r="C554" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0</v>
+      </c>
+      <c r="E554" t="n">
+        <v>1121.32</v>
+      </c>
+      <c r="F554" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G554" t="n">
+        <v>4607.12</v>
+      </c>
+      <c r="H554" t="n">
+        <v>4603.41</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="n">
+        <v>46321.52083333334</v>
+      </c>
+      <c r="B555" t="n">
+        <v>3438.97</v>
+      </c>
+      <c r="C555" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D555" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="E555" t="n">
+        <v>1115.01</v>
+      </c>
+      <c r="F555" t="n">
+        <v>0</v>
+      </c>
+      <c r="G555" t="n">
+        <v>4626.83</v>
+      </c>
+      <c r="H555" t="n">
+        <v>4626.83</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="n">
+        <v>46321.54166666666</v>
+      </c>
+      <c r="B556" t="n">
+        <v>3451.28</v>
+      </c>
+      <c r="C556" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0</v>
+      </c>
+      <c r="E556" t="n">
+        <v>1130.26</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0</v>
+      </c>
+      <c r="G556" t="n">
+        <v>4646.34</v>
+      </c>
+      <c r="H556" t="n">
+        <v>4646.34</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="B557" t="n">
+        <v>3547.5</v>
+      </c>
+      <c r="C557" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="D557" t="n">
+        <v>0</v>
+      </c>
+      <c r="E557" t="n">
+        <v>1126.56</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0</v>
+      </c>
+      <c r="G557" t="n">
+        <v>4739.9</v>
+      </c>
+      <c r="H557" t="n">
+        <v>4739.9</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="n">
+        <v>46321.58333333334</v>
+      </c>
+      <c r="B558" t="n">
+        <v>3570.94</v>
+      </c>
+      <c r="C558" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0</v>
+      </c>
+      <c r="E558" t="n">
+        <v>1125.08</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0</v>
+      </c>
+      <c r="G558" t="n">
+        <v>4760.969999999999</v>
+      </c>
+      <c r="H558" t="n">
+        <v>4760.969999999999</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="n">
+        <v>46321.60416666666</v>
+      </c>
+      <c r="B559" t="n">
+        <v>3398.24</v>
+      </c>
+      <c r="C559" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="D559" t="n">
+        <v>0</v>
+      </c>
+      <c r="E559" t="n">
+        <v>1131.17</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0</v>
+      </c>
+      <c r="G559" t="n">
+        <v>4590.96</v>
+      </c>
+      <c r="H559" t="n">
+        <v>4590.96</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="n">
+        <v>46321.625</v>
+      </c>
+      <c r="B560" t="n">
+        <v>3230.55</v>
+      </c>
+      <c r="C560" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="D560" t="n">
+        <v>0</v>
+      </c>
+      <c r="E560" t="n">
+        <v>1133.82</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0</v>
+      </c>
+      <c r="G560" t="n">
+        <v>4414.79</v>
+      </c>
+      <c r="H560" t="n">
+        <v>4414.79</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="n">
+        <v>46321.64583333334</v>
+      </c>
+      <c r="B561" t="n">
+        <v>3226.75</v>
+      </c>
+      <c r="C561" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="D561" t="n">
+        <v>0</v>
+      </c>
+      <c r="E561" t="n">
+        <v>1143.94</v>
+      </c>
+      <c r="F561" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="G561" t="n">
+        <v>4418.93</v>
+      </c>
+      <c r="H561" t="n">
+        <v>4414.38</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="n">
+        <v>46321.66666666666</v>
+      </c>
+      <c r="B562" t="n">
+        <v>3163.65</v>
+      </c>
+      <c r="C562" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="D562" t="n">
+        <v>0</v>
+      </c>
+      <c r="E562" t="n">
+        <v>1135.04</v>
+      </c>
+      <c r="F562" t="n">
+        <v>0</v>
+      </c>
+      <c r="G562" t="n">
+        <v>4328</v>
+      </c>
+      <c r="H562" t="n">
+        <v>4328</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="n">
+        <v>46321.6875</v>
+      </c>
+      <c r="B563" t="n">
+        <v>3134.68</v>
+      </c>
+      <c r="C563" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="D563" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="E563" t="n">
+        <v>1140.44</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0</v>
+      </c>
+      <c r="G563" t="n">
+        <v>4312.190000000001</v>
+      </c>
+      <c r="H563" t="n">
+        <v>4312.190000000001</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="n">
+        <v>46321.70833333334</v>
+      </c>
+      <c r="B564" t="n">
+        <v>3114.11</v>
+      </c>
+      <c r="C564" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="D564" t="n">
+        <v>0</v>
+      </c>
+      <c r="E564" t="n">
+        <v>1142.23</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0</v>
+      </c>
+      <c r="G564" t="n">
+        <v>4278.71</v>
+      </c>
+      <c r="H564" t="n">
+        <v>4278.71</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="n">
+        <v>46321.72916666666</v>
+      </c>
+      <c r="B565" t="n">
+        <v>3085.14</v>
+      </c>
+      <c r="C565" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="D565" t="n">
+        <v>0</v>
+      </c>
+      <c r="E565" t="n">
+        <v>1136.58</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0</v>
+      </c>
+      <c r="G565" t="n">
+        <v>4239.6</v>
+      </c>
+      <c r="H565" t="n">
+        <v>4239.6</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="n">
+        <v>46321.75</v>
+      </c>
+      <c r="B566" t="n">
+        <v>3209.42</v>
+      </c>
+      <c r="C566" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="D566" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="E566" t="n">
+        <v>1130.79</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0</v>
+      </c>
+      <c r="G566" t="n">
+        <v>4380.120000000001</v>
+      </c>
+      <c r="H566" t="n">
+        <v>4380.120000000001</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="n">
+        <v>46321.77083333334</v>
+      </c>
+      <c r="B567" t="n">
+        <v>3486.49</v>
+      </c>
+      <c r="C567" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E567" t="n">
+        <v>1137.01</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0</v>
+      </c>
+      <c r="G567" t="n">
+        <v>4638.42</v>
+      </c>
+      <c r="H567" t="n">
+        <v>4638.42</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="n">
+        <v>46321.79166666666</v>
+      </c>
+      <c r="B568" t="n">
+        <v>3506.4</v>
+      </c>
+      <c r="C568" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="D568" t="n">
+        <v>0</v>
+      </c>
+      <c r="E568" t="n">
+        <v>1147.03</v>
+      </c>
+      <c r="F568" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="G568" t="n">
+        <v>4695.709999999999</v>
+      </c>
+      <c r="H568" t="n">
+        <v>4671.889999999999</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="n">
+        <v>46321.8125</v>
+      </c>
+      <c r="B569" t="n">
+        <v>3535.12</v>
+      </c>
+      <c r="C569" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D569" t="n">
+        <v>0</v>
+      </c>
+      <c r="E569" t="n">
+        <v>1152.39</v>
+      </c>
+      <c r="F569" t="n">
+        <v>0</v>
+      </c>
+      <c r="G569" t="n">
+        <v>4702.61</v>
+      </c>
+      <c r="H569" t="n">
+        <v>4702.61</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="n">
+        <v>46321.83333333334</v>
+      </c>
+      <c r="B570" t="n">
+        <v>3494.54</v>
+      </c>
+      <c r="C570" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="D570" t="n">
+        <v>0</v>
+      </c>
+      <c r="E570" t="n">
+        <v>1155.77</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0</v>
+      </c>
+      <c r="G570" t="n">
+        <v>4665.98</v>
+      </c>
+      <c r="H570" t="n">
+        <v>4665.98</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="n">
+        <v>46321.85416666666</v>
+      </c>
+      <c r="B571" t="n">
+        <v>3441.08</v>
+      </c>
+      <c r="C571" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="D571" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E571" t="n">
+        <v>1153.44</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0</v>
+      </c>
+      <c r="G571" t="n">
+        <v>4612.16</v>
+      </c>
+      <c r="H571" t="n">
+        <v>4612.16</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="n">
+        <v>46321.875</v>
+      </c>
+      <c r="B572" t="n">
+        <v>3343.95</v>
+      </c>
+      <c r="C572" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D572" t="n">
+        <v>0</v>
+      </c>
+      <c r="E572" t="n">
+        <v>1166.82</v>
+      </c>
+      <c r="F572" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="G572" t="n">
+        <v>4569.719999999999</v>
+      </c>
+      <c r="H572" t="n">
+        <v>4518.99</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="n">
+        <v>46321.89583333334</v>
+      </c>
+      <c r="B573" t="n">
+        <v>3222.07</v>
+      </c>
+      <c r="C573" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="D573" t="n">
+        <v>0</v>
+      </c>
+      <c r="E573" t="n">
+        <v>1164.46</v>
+      </c>
+      <c r="F573" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="G573" t="n">
+        <v>4413.84</v>
+      </c>
+      <c r="H573" t="n">
+        <v>4393.8</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="n">
+        <v>46321.91666666666</v>
+      </c>
+      <c r="B574" t="n">
+        <v>3098.88</v>
+      </c>
+      <c r="C574" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="D574" t="n">
+        <v>0</v>
+      </c>
+      <c r="E574" t="n">
+        <v>1164.85</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0</v>
+      </c>
+      <c r="G574" t="n">
+        <v>4270.809999999999</v>
+      </c>
+      <c r="H574" t="n">
+        <v>4270.809999999999</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="n">
+        <v>46321.9375</v>
+      </c>
+      <c r="B575" t="n">
+        <v>2954.35</v>
+      </c>
+      <c r="C575" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="D575" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="E575" t="n">
+        <v>1165.43</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0</v>
+      </c>
+      <c r="G575" t="n">
+        <v>4137.47</v>
+      </c>
+      <c r="H575" t="n">
+        <v>4137.47</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="n">
+        <v>46321.95833333334</v>
+      </c>
+      <c r="B576" t="n">
+        <v>2800.07</v>
+      </c>
+      <c r="C576" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="D576" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="E576" t="n">
+        <v>1158.97</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0</v>
+      </c>
+      <c r="G576" t="n">
+        <v>3973.31</v>
+      </c>
+      <c r="H576" t="n">
+        <v>3973.31</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="n">
+        <v>46321.97916666666</v>
+      </c>
+      <c r="B577" t="n">
+        <v>2681.22</v>
+      </c>
+      <c r="C577" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0</v>
+      </c>
+      <c r="E577" t="n">
+        <v>1159.25</v>
+      </c>
+      <c r="F577" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="G577" t="n">
+        <v>3853.19</v>
+      </c>
+      <c r="H577" t="n">
+        <v>3847.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,6 +1244,59 @@
       </c>
       <c r="Q13" t="n">
         <v>0.005</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98923</v>
+      </c>
+      <c r="C14" t="n">
+        <v>71940</v>
+      </c>
+      <c r="D14" t="n">
+        <v>26450</v>
+      </c>
+      <c r="E14" t="n">
+        <v>24810</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1641</v>
+      </c>
+      <c r="G14" t="n">
+        <v>498</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>65</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.122</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.998</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.003</v>
       </c>
     </row>
   </sheetData>
@@ -1257,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,27 +1341,27 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Delsitanisagua</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Delsitanisagua</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Agoyán</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Mazar</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Minas San Francisco</t>
         </is>
       </c>
     </row>
@@ -1329,19 +1382,19 @@
         <v>8114</v>
       </c>
       <c r="F2" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G2" t="n">
         <v>2768</v>
       </c>
-      <c r="G2" t="n">
-        <v>3724</v>
-      </c>
       <c r="H2" t="n">
+        <v>239</v>
+      </c>
+      <c r="I2" t="n">
         <v>2003</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2301</v>
-      </c>
-      <c r="J2" t="n">
-        <v>239</v>
       </c>
     </row>
     <row r="3">
@@ -1361,19 +1414,19 @@
         <v>8424</v>
       </c>
       <c r="F3" t="n">
+        <v>3644</v>
+      </c>
+      <c r="G3" t="n">
         <v>2477</v>
       </c>
-      <c r="G3" t="n">
-        <v>3644</v>
-      </c>
       <c r="H3" t="n">
+        <v>1531</v>
+      </c>
+      <c r="I3" t="n">
         <v>1820</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2554</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1531</v>
       </c>
     </row>
     <row r="4">
@@ -1393,19 +1446,19 @@
         <v>9735</v>
       </c>
       <c r="F4" t="n">
+        <v>3194</v>
+      </c>
+      <c r="G4" t="n">
         <v>2491</v>
       </c>
-      <c r="G4" t="n">
-        <v>3194</v>
-      </c>
       <c r="H4" t="n">
+        <v>306</v>
+      </c>
+      <c r="I4" t="n">
         <v>1820</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2604</v>
-      </c>
-      <c r="J4" t="n">
-        <v>306</v>
       </c>
     </row>
     <row r="5">
@@ -1425,19 +1478,19 @@
         <v>8469</v>
       </c>
       <c r="F5" t="n">
+        <v>3026</v>
+      </c>
+      <c r="G5" t="n">
         <v>2773</v>
       </c>
-      <c r="G5" t="n">
-        <v>3026</v>
-      </c>
       <c r="H5" t="n">
+        <v>721</v>
+      </c>
+      <c r="I5" t="n">
         <v>2009</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2307</v>
-      </c>
-      <c r="J5" t="n">
-        <v>721</v>
       </c>
     </row>
     <row r="6">
@@ -1457,19 +1510,19 @@
         <v>8416</v>
       </c>
       <c r="F6" t="n">
+        <v>3345</v>
+      </c>
+      <c r="G6" t="n">
         <v>2472</v>
       </c>
-      <c r="G6" t="n">
-        <v>3345</v>
-      </c>
       <c r="H6" t="n">
+        <v>750</v>
+      </c>
+      <c r="I6" t="n">
         <v>1847</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>3102</v>
-      </c>
-      <c r="J6" t="n">
-        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -1489,19 +1542,19 @@
         <v>5868</v>
       </c>
       <c r="F7" t="n">
+        <v>2963</v>
+      </c>
+      <c r="G7" t="n">
         <v>2512</v>
       </c>
-      <c r="G7" t="n">
-        <v>2963</v>
-      </c>
       <c r="H7" t="n">
+        <v>461</v>
+      </c>
+      <c r="I7" t="n">
         <v>1853</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2187</v>
-      </c>
-      <c r="J7" t="n">
-        <v>461</v>
       </c>
     </row>
     <row r="8">
@@ -1521,18 +1574,18 @@
         <v>2907</v>
       </c>
       <c r="F8" t="n">
+        <v>3431</v>
+      </c>
+      <c r="G8" t="n">
         <v>2854</v>
       </c>
-      <c r="G8" t="n">
-        <v>3431</v>
-      </c>
       <c r="H8" t="n">
+        <v>1105</v>
+      </c>
+      <c r="I8" t="n">
         <v>2034</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>1105</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1551,19 +1604,19 @@
         <v>8041</v>
       </c>
       <c r="F9" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G9" t="n">
         <v>2801</v>
       </c>
-      <c r="G9" t="n">
-        <v>2788</v>
-      </c>
       <c r="H9" t="n">
+        <v>1488</v>
+      </c>
+      <c r="I9" t="n">
         <v>2027</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1164</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1488</v>
       </c>
     </row>
     <row r="10">
@@ -1583,19 +1636,19 @@
         <v>9960</v>
       </c>
       <c r="F10" t="n">
+        <v>2675</v>
+      </c>
+      <c r="G10" t="n">
         <v>2566</v>
       </c>
-      <c r="G10" t="n">
-        <v>2675</v>
-      </c>
       <c r="H10" t="n">
+        <v>1870</v>
+      </c>
+      <c r="I10" t="n">
         <v>1907</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>2157</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1870</v>
       </c>
     </row>
     <row r="11">
@@ -1615,19 +1668,19 @@
         <v>9798</v>
       </c>
       <c r="F11" t="n">
+        <v>2526</v>
+      </c>
+      <c r="G11" t="n">
         <v>2706</v>
       </c>
-      <c r="G11" t="n">
-        <v>2526</v>
-      </c>
       <c r="H11" t="n">
+        <v>1693</v>
+      </c>
+      <c r="I11" t="n">
         <v>1966</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>2831</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1693</v>
       </c>
     </row>
     <row r="12">
@@ -1647,19 +1700,19 @@
         <v>9495</v>
       </c>
       <c r="F12" t="n">
+        <v>2565</v>
+      </c>
+      <c r="G12" t="n">
         <v>2525</v>
       </c>
-      <c r="G12" t="n">
-        <v>2565</v>
-      </c>
       <c r="H12" t="n">
+        <v>447</v>
+      </c>
+      <c r="I12" t="n">
         <v>1838</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>2551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>447</v>
       </c>
     </row>
     <row r="13">
@@ -1679,19 +1732,51 @@
         <v>4088</v>
       </c>
       <c r="F13" t="n">
+        <v>2495</v>
+      </c>
+      <c r="G13" t="n">
         <v>2823</v>
       </c>
-      <c r="G13" t="n">
-        <v>2495</v>
-      </c>
       <c r="H13" t="n">
+        <v>1264</v>
+      </c>
+      <c r="I13" t="n">
         <v>1997</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1358</v>
       </c>
-      <c r="J13" t="n">
-        <v>1264</v>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B14" t="n">
+        <v>24052</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20199</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11236</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5881</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2635</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2554</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2136</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1840</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1408</v>
       </c>
     </row>
   </sheetData>
@@ -1705,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2069,21 +2154,17 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46291</v>
+        <v>46322</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2092,7 +2173,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>24721</v>
+        <v>24052</v>
       </c>
     </row>
     <row r="15">
@@ -2100,7 +2181,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,7 +2204,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>23420</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="16">
@@ -2131,7 +2212,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,7 +2235,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>19992</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="17">
@@ -2162,7 +2243,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2185,7 +2266,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>17987</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="18">
@@ -2193,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2216,7 +2297,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>17990</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="19">
@@ -2224,7 +2305,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2247,7 +2328,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>22254</v>
+        <v>17990</v>
       </c>
     </row>
     <row r="20">
@@ -2255,7 +2336,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2278,7 +2359,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>26473</v>
+        <v>22254</v>
       </c>
     </row>
     <row r="21">
@@ -2286,7 +2367,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2309,7 +2390,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>23346</v>
+        <v>26473</v>
       </c>
     </row>
     <row r="22">
@@ -2317,7 +2398,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2340,7 +2421,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>19157</v>
+        <v>23346</v>
       </c>
     </row>
     <row r="23">
@@ -2348,7 +2429,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2371,7 +2452,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>19048</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="24">
@@ -2379,7 +2460,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46305</v>
+        <v>46302</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2402,7 +2483,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>16518</v>
+        <v>19048</v>
       </c>
     </row>
     <row r="25">
@@ -2410,7 +2491,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46321</v>
+        <v>46305</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2433,7 +2514,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>21674</v>
+        <v>16518</v>
       </c>
     </row>
     <row r="26">
@@ -2441,21 +2522,21 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2464,7 +2545,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>13964</v>
+        <v>21674</v>
       </c>
     </row>
     <row r="27">
@@ -2472,21 +2553,21 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46293</v>
+        <v>46322</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2495,7 +2576,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>16681</v>
+        <v>20199</v>
       </c>
     </row>
     <row r="28">
@@ -2503,7 +2584,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2526,7 +2607,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>17645</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="29">
@@ -2534,7 +2615,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2557,7 +2638,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>14882</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="30">
@@ -2565,7 +2646,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2588,7 +2669,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>14644</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="31">
@@ -2596,7 +2677,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2619,7 +2700,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>10078</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="32">
@@ -2627,7 +2708,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2650,7 +2731,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>5014</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="33">
@@ -2658,7 +2739,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2681,7 +2762,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>14358</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="34">
@@ -2689,7 +2770,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2712,7 +2793,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>18959</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="35">
@@ -2720,7 +2801,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2743,7 +2824,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>18347</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="36">
@@ -2751,7 +2832,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46305</v>
+        <v>46301</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2774,7 +2855,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>16208</v>
+        <v>18959</v>
       </c>
     </row>
     <row r="37">
@@ -2782,7 +2863,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46321</v>
+        <v>46302</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2805,7 +2886,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>6934</v>
+        <v>18347</v>
       </c>
     </row>
     <row r="38">
@@ -2813,11 +2894,11 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2836,7 +2917,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>8114</v>
+        <v>16208</v>
       </c>
     </row>
     <row r="39">
@@ -2844,11 +2925,11 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46293</v>
+        <v>46321</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2867,7 +2948,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>8424</v>
+        <v>6934</v>
       </c>
     </row>
     <row r="40">
@@ -2875,11 +2956,11 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46294</v>
+        <v>46322</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2898,7 +2979,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>9735</v>
+        <v>11236</v>
       </c>
     </row>
     <row r="41">
@@ -2906,7 +2987,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2929,7 +3010,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>8469</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="42">
@@ -2937,7 +3018,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2960,7 +3041,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>8416</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="43">
@@ -2968,7 +3049,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2991,7 +3072,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5868</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="44">
@@ -2999,7 +3080,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -3022,7 +3103,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2907</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="45">
@@ -3030,7 +3111,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3053,7 +3134,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>8041</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="46">
@@ -3061,7 +3142,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3084,7 +3165,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>9960</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="47">
@@ -3092,7 +3173,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46302</v>
+        <v>46298</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3115,7 +3196,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>9798</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="48">
@@ -3123,7 +3204,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3146,7 +3227,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>9495</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="49">
@@ -3154,7 +3235,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46321</v>
+        <v>46301</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3177,7 +3258,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4088</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="50">
@@ -3185,16 +3266,16 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46291</v>
+        <v>46302</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3208,7 +3289,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2768</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="51">
@@ -3216,16 +3297,16 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46293</v>
+        <v>46305</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3239,7 +3320,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2477</v>
+        <v>9495</v>
       </c>
     </row>
     <row r="52">
@@ -3247,16 +3328,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46294</v>
+        <v>46321</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3270,7 +3351,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2491</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="53">
@@ -3278,16 +3359,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46295</v>
+        <v>46322</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3301,7 +3382,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2773</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="54">
@@ -3309,21 +3390,21 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3332,7 +3413,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2472</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="55">
@@ -3340,21 +3421,21 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3363,7 +3444,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2512</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="56">
@@ -3371,21 +3452,21 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3394,7 +3475,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2854</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="57">
@@ -3402,21 +3483,21 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3425,7 +3506,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2801</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="58">
@@ -3433,21 +3514,21 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3456,7 +3537,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2566</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="59">
@@ -3464,21 +3545,21 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3487,7 +3568,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2706</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="60">
@@ -3495,21 +3576,21 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3518,7 +3599,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2525</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="61">
@@ -3526,21 +3607,21 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46321</v>
+        <v>46300</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3549,7 +3630,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2823</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="62">
@@ -3557,7 +3638,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46291</v>
+        <v>46301</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3580,7 +3661,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3724</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="63">
@@ -3588,7 +3669,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3611,7 +3692,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3644</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="64">
@@ -3619,7 +3700,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46294</v>
+        <v>46305</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3642,7 +3723,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>3194</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="65">
@@ -3650,7 +3731,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46295</v>
+        <v>46321</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3673,7 +3754,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3026</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="66">
@@ -3681,7 +3762,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46296</v>
+        <v>46322</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3704,7 +3785,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>3345</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="67">
@@ -3712,21 +3793,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3735,7 +3816,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2963</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="68">
@@ -3743,21 +3824,21 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46298</v>
+        <v>46293</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3766,7 +3847,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>3431</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="69">
@@ -3774,21 +3855,21 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46300</v>
+        <v>46294</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3797,7 +3878,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2788</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="70">
@@ -3805,21 +3886,21 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46301</v>
+        <v>46295</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3828,7 +3909,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2675</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="71">
@@ -3836,21 +3917,21 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3859,7 +3940,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2526</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="72">
@@ -3867,21 +3948,21 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46305</v>
+        <v>46297</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3890,7 +3971,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2565</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="73">
@@ -3898,21 +3979,21 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46321</v>
+        <v>46298</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3921,7 +4002,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2495</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="74">
@@ -3929,11 +4010,11 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3952,7 +4033,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2003</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="75">
@@ -3960,11 +4041,11 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3983,7 +4064,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1820</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="76">
@@ -3991,11 +4072,11 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4014,7 +4095,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1820</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="77">
@@ -4022,11 +4103,11 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4045,7 +4126,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2009</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="78">
@@ -4053,11 +4134,11 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46296</v>
+        <v>46321</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4076,7 +4157,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1847</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="79">
@@ -4084,11 +4165,11 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46297</v>
+        <v>46322</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4107,7 +4188,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1853</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="80">
@@ -4115,16 +4196,16 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4138,7 +4219,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2034</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81">
@@ -4146,16 +4227,16 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4169,7 +4250,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2027</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="82">
@@ -4177,16 +4258,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4200,7 +4281,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1907</v>
+        <v>306</v>
       </c>
     </row>
     <row r="83">
@@ -4208,16 +4289,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4231,7 +4312,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1966</v>
+        <v>721</v>
       </c>
     </row>
     <row r="84">
@@ -4239,16 +4320,16 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46305</v>
+        <v>46296</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4262,7 +4343,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1838</v>
+        <v>750</v>
       </c>
     </row>
     <row r="85">
@@ -4270,16 +4351,16 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46321</v>
+        <v>46297</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4293,7 +4374,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1997</v>
+        <v>461</v>
       </c>
     </row>
     <row r="86">
@@ -4301,11 +4382,11 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4324,7 +4405,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2301</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="87">
@@ -4332,11 +4413,11 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4355,7 +4436,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2554</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="88">
@@ -4363,11 +4444,11 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4386,7 +4467,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>2604</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="89">
@@ -4394,11 +4475,11 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4417,7 +4498,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2307</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="90">
@@ -4425,11 +4506,11 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46296</v>
+        <v>46305</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4448,7 +4529,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>3102</v>
+        <v>447</v>
       </c>
     </row>
     <row r="91">
@@ -4456,11 +4537,11 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46297</v>
+        <v>46321</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4479,7 +4560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>2187</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="92">
@@ -4487,11 +4568,11 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46300</v>
+        <v>46322</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4510,7 +4591,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1164</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="93">
@@ -4518,16 +4599,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46301</v>
+        <v>46291</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4541,7 +4622,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2157</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="94">
@@ -4549,16 +4630,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46302</v>
+        <v>46293</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4572,7 +4653,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2831</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="95">
@@ -4580,16 +4661,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46305</v>
+        <v>46294</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4603,7 +4684,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2551</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="96">
@@ -4611,16 +4692,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46321</v>
+        <v>46295</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4634,7 +4715,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1358</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="97">
@@ -4642,16 +4723,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4665,7 +4746,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>239</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="98">
@@ -4673,16 +4754,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4696,7 +4777,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1531</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="99">
@@ -4704,16 +4785,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4727,7 +4808,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>306</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="100">
@@ -4735,16 +4816,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4758,7 +4839,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>721</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="101">
@@ -4766,16 +4847,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4789,7 +4870,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>750</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="102">
@@ -4797,16 +4878,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4820,7 +4901,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>461</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="103">
@@ -4828,16 +4909,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4851,7 +4932,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1105</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="104">
@@ -4859,16 +4940,16 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4882,7 +4963,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1488</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="105">
@@ -4890,16 +4971,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46301</v>
+        <v>46322</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4913,7 +4994,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1870</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="106">
@@ -4921,11 +5002,11 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46302</v>
+        <v>46291</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4944,7 +5025,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1693</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="107">
@@ -4952,11 +5033,11 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46305</v>
+        <v>46293</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Mazar</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4975,7 +5056,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>447</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="108">
@@ -4983,30 +5064,309 @@
         <v>106</v>
       </c>
       <c r="B108" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2" t="n">
         <v>46321</v>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Minas San Francisco</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>1264</v>
+      <c r="G116" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1408</v>
       </c>
     </row>
   </sheetData>
@@ -5020,7 +5380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H577"/>
+  <dimension ref="A1:H625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20041,6 +20401,1254 @@
         <v>3847.56</v>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B578" t="n">
+        <v>2531.18</v>
+      </c>
+      <c r="C578" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0</v>
+      </c>
+      <c r="E578" t="n">
+        <v>1158.21</v>
+      </c>
+      <c r="F578" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="G578" t="n">
+        <v>3713.31</v>
+      </c>
+      <c r="H578" t="n">
+        <v>3696.46</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="n">
+        <v>46322.02083333334</v>
+      </c>
+      <c r="B579" t="n">
+        <v>2451.65</v>
+      </c>
+      <c r="C579" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D579" t="n">
+        <v>0</v>
+      </c>
+      <c r="E579" t="n">
+        <v>1133.44</v>
+      </c>
+      <c r="F579" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="G579" t="n">
+        <v>3599</v>
+      </c>
+      <c r="H579" t="n">
+        <v>3592.34</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="n">
+        <v>46322.04166666666</v>
+      </c>
+      <c r="B580" t="n">
+        <v>2346.17</v>
+      </c>
+      <c r="C580" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="D580" t="n">
+        <v>0</v>
+      </c>
+      <c r="E580" t="n">
+        <v>1150.58</v>
+      </c>
+      <c r="F580" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="G580" t="n">
+        <v>3522.79</v>
+      </c>
+      <c r="H580" t="n">
+        <v>3503.94</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="n">
+        <v>46322.0625</v>
+      </c>
+      <c r="B581" t="n">
+        <v>2310.34</v>
+      </c>
+      <c r="C581" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="D581" t="n">
+        <v>0</v>
+      </c>
+      <c r="E581" t="n">
+        <v>1118.49</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0</v>
+      </c>
+      <c r="G581" t="n">
+        <v>3437.35</v>
+      </c>
+      <c r="H581" t="n">
+        <v>3437.35</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="n">
+        <v>46322.08333333334</v>
+      </c>
+      <c r="B582" t="n">
+        <v>2248.79</v>
+      </c>
+      <c r="C582" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D582" t="n">
+        <v>0</v>
+      </c>
+      <c r="E582" t="n">
+        <v>1128.18</v>
+      </c>
+      <c r="F582" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G582" t="n">
+        <v>3392.32</v>
+      </c>
+      <c r="H582" t="n">
+        <v>3384.72</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="n">
+        <v>46322.10416666666</v>
+      </c>
+      <c r="B583" t="n">
+        <v>2188.27</v>
+      </c>
+      <c r="C583" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="D583" t="n">
+        <v>0</v>
+      </c>
+      <c r="E583" t="n">
+        <v>1139.17</v>
+      </c>
+      <c r="F583" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="G583" t="n">
+        <v>3338.61</v>
+      </c>
+      <c r="H583" t="n">
+        <v>3334.67</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="n">
+        <v>46322.125</v>
+      </c>
+      <c r="B584" t="n">
+        <v>2147.3</v>
+      </c>
+      <c r="C584" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D584" t="n">
+        <v>0</v>
+      </c>
+      <c r="E584" t="n">
+        <v>1145.18</v>
+      </c>
+      <c r="F584" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G584" t="n">
+        <v>3301.88</v>
+      </c>
+      <c r="H584" t="n">
+        <v>3299.68</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="n">
+        <v>46322.14583333334</v>
+      </c>
+      <c r="B585" t="n">
+        <v>2143.25</v>
+      </c>
+      <c r="C585" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="D585" t="n">
+        <v>0</v>
+      </c>
+      <c r="E585" t="n">
+        <v>1118.05</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0</v>
+      </c>
+      <c r="G585" t="n">
+        <v>3268.48</v>
+      </c>
+      <c r="H585" t="n">
+        <v>3268.48</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="n">
+        <v>46322.16666666666</v>
+      </c>
+      <c r="B586" t="n">
+        <v>2092.2</v>
+      </c>
+      <c r="C586" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="D586" t="n">
+        <v>0</v>
+      </c>
+      <c r="E586" t="n">
+        <v>1134.73</v>
+      </c>
+      <c r="F586" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G586" t="n">
+        <v>3236.02</v>
+      </c>
+      <c r="H586" t="n">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="n">
+        <v>46322.1875</v>
+      </c>
+      <c r="B587" t="n">
+        <v>2086.78</v>
+      </c>
+      <c r="C587" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="D587" t="n">
+        <v>0</v>
+      </c>
+      <c r="E587" t="n">
+        <v>1132.26</v>
+      </c>
+      <c r="F587" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G587" t="n">
+        <v>3228.02</v>
+      </c>
+      <c r="H587" t="n">
+        <v>3226.150000000001</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="n">
+        <v>46322.20833333334</v>
+      </c>
+      <c r="B588" t="n">
+        <v>2105.73</v>
+      </c>
+      <c r="C588" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="D588" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="E588" t="n">
+        <v>1144.99</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0</v>
+      </c>
+      <c r="G588" t="n">
+        <v>3270.4</v>
+      </c>
+      <c r="H588" t="n">
+        <v>3270.4</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="n">
+        <v>46322.22916666666</v>
+      </c>
+      <c r="B589" t="n">
+        <v>2208.67</v>
+      </c>
+      <c r="C589" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="D589" t="n">
+        <v>0</v>
+      </c>
+      <c r="E589" t="n">
+        <v>1139.62</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0</v>
+      </c>
+      <c r="G589" t="n">
+        <v>3354.62</v>
+      </c>
+      <c r="H589" t="n">
+        <v>3354.62</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="n">
+        <v>46322.25</v>
+      </c>
+      <c r="B590" t="n">
+        <v>2104.25</v>
+      </c>
+      <c r="C590" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D590" t="n">
+        <v>0</v>
+      </c>
+      <c r="E590" t="n">
+        <v>1141.78</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0</v>
+      </c>
+      <c r="G590" t="n">
+        <v>3251.91</v>
+      </c>
+      <c r="H590" t="n">
+        <v>3251.91</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="n">
+        <v>46322.27083333334</v>
+      </c>
+      <c r="B591" t="n">
+        <v>2046.03</v>
+      </c>
+      <c r="C591" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="D591" t="n">
+        <v>0</v>
+      </c>
+      <c r="E591" t="n">
+        <v>1146.31</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0</v>
+      </c>
+      <c r="G591" t="n">
+        <v>3199.22</v>
+      </c>
+      <c r="H591" t="n">
+        <v>3199.22</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="n">
+        <v>46322.29166666666</v>
+      </c>
+      <c r="B592" t="n">
+        <v>2066.06</v>
+      </c>
+      <c r="C592" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="D592" t="n">
+        <v>0</v>
+      </c>
+      <c r="E592" t="n">
+        <v>1138.71</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0</v>
+      </c>
+      <c r="G592" t="n">
+        <v>3211.78</v>
+      </c>
+      <c r="H592" t="n">
+        <v>3211.78</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="n">
+        <v>46322.3125</v>
+      </c>
+      <c r="B593" t="n">
+        <v>2221.63</v>
+      </c>
+      <c r="C593" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="D593" t="n">
+        <v>0</v>
+      </c>
+      <c r="E593" t="n">
+        <v>1144.8</v>
+      </c>
+      <c r="F593" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="G593" t="n">
+        <v>3386.62</v>
+      </c>
+      <c r="H593" t="n">
+        <v>3373.440000000001</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="n">
+        <v>46322.33333333334</v>
+      </c>
+      <c r="B594" t="n">
+        <v>2450.8</v>
+      </c>
+      <c r="C594" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="D594" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E594" t="n">
+        <v>1140.96</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0</v>
+      </c>
+      <c r="G594" t="n">
+        <v>3602.14</v>
+      </c>
+      <c r="H594" t="n">
+        <v>3602.14</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="n">
+        <v>46322.35416666666</v>
+      </c>
+      <c r="B595" t="n">
+        <v>2687.78</v>
+      </c>
+      <c r="C595" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="D595" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="E595" t="n">
+        <v>1127.03</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0</v>
+      </c>
+      <c r="G595" t="n">
+        <v>3825.62</v>
+      </c>
+      <c r="H595" t="n">
+        <v>3825.62</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="n">
+        <v>46322.375</v>
+      </c>
+      <c r="B596" t="n">
+        <v>2864.92</v>
+      </c>
+      <c r="C596" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="D596" t="n">
+        <v>0</v>
+      </c>
+      <c r="E596" t="n">
+        <v>1122.29</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0</v>
+      </c>
+      <c r="G596" t="n">
+        <v>3994.48</v>
+      </c>
+      <c r="H596" t="n">
+        <v>3994.48</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="n">
+        <v>46322.39583333334</v>
+      </c>
+      <c r="B597" t="n">
+        <v>3041.72</v>
+      </c>
+      <c r="C597" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="D597" t="n">
+        <v>0</v>
+      </c>
+      <c r="E597" t="n">
+        <v>1121.9</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0</v>
+      </c>
+      <c r="G597" t="n">
+        <v>4170.84</v>
+      </c>
+      <c r="H597" t="n">
+        <v>4170.84</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="n">
+        <v>46322.41666666666</v>
+      </c>
+      <c r="B598" t="n">
+        <v>3140.74</v>
+      </c>
+      <c r="C598" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="D598" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="E598" t="n">
+        <v>1129.98</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0</v>
+      </c>
+      <c r="G598" t="n">
+        <v>4303.29</v>
+      </c>
+      <c r="H598" t="n">
+        <v>4303.29</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="n">
+        <v>46322.4375</v>
+      </c>
+      <c r="B599" t="n">
+        <v>3235.31</v>
+      </c>
+      <c r="C599" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="D599" t="n">
+        <v>0</v>
+      </c>
+      <c r="E599" t="n">
+        <v>1126.54</v>
+      </c>
+      <c r="F599" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="G599" t="n">
+        <v>4421.72</v>
+      </c>
+      <c r="H599" t="n">
+        <v>4416.610000000001</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="n">
+        <v>46322.45833333334</v>
+      </c>
+      <c r="B600" t="n">
+        <v>3314.74</v>
+      </c>
+      <c r="C600" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="D600" t="n">
+        <v>0</v>
+      </c>
+      <c r="E600" t="n">
+        <v>1138.68</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0</v>
+      </c>
+      <c r="G600" t="n">
+        <v>4513.01</v>
+      </c>
+      <c r="H600" t="n">
+        <v>4513.01</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="n">
+        <v>46322.47916666666</v>
+      </c>
+      <c r="B601" t="n">
+        <v>3406.6</v>
+      </c>
+      <c r="C601" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="D601" t="n">
+        <v>0</v>
+      </c>
+      <c r="E601" t="n">
+        <v>1127.49</v>
+      </c>
+      <c r="F601" t="n">
+        <v>0</v>
+      </c>
+      <c r="G601" t="n">
+        <v>4595.25</v>
+      </c>
+      <c r="H601" t="n">
+        <v>4595.25</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="n">
+        <v>46322.5</v>
+      </c>
+      <c r="B602" t="n">
+        <v>3449.45</v>
+      </c>
+      <c r="C602" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="D602" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="E602" t="n">
+        <v>1123.34</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0</v>
+      </c>
+      <c r="G602" t="n">
+        <v>4639.549999999999</v>
+      </c>
+      <c r="H602" t="n">
+        <v>4639.549999999999</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="n">
+        <v>46322.52083333334</v>
+      </c>
+      <c r="B603" t="n">
+        <v>3521.82</v>
+      </c>
+      <c r="C603" t="n">
+        <v>63.89</v>
+      </c>
+      <c r="D603" t="n">
+        <v>0</v>
+      </c>
+      <c r="E603" t="n">
+        <v>1081.28</v>
+      </c>
+      <c r="F603" t="n">
+        <v>0</v>
+      </c>
+      <c r="G603" t="n">
+        <v>4666.99</v>
+      </c>
+      <c r="H603" t="n">
+        <v>4666.99</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="n">
+        <v>46322.54166666666</v>
+      </c>
+      <c r="B604" t="n">
+        <v>3551.95</v>
+      </c>
+      <c r="C604" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="D604" t="n">
+        <v>0</v>
+      </c>
+      <c r="E604" t="n">
+        <v>1099.5</v>
+      </c>
+      <c r="F604" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="G604" t="n">
+        <v>4718.599999999999</v>
+      </c>
+      <c r="H604" t="n">
+        <v>4714.139999999999</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="B605" t="n">
+        <v>3635.17</v>
+      </c>
+      <c r="C605" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="D605" t="n">
+        <v>0</v>
+      </c>
+      <c r="E605" t="n">
+        <v>1096.33</v>
+      </c>
+      <c r="F605" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G605" t="n">
+        <v>4799.33</v>
+      </c>
+      <c r="H605" t="n">
+        <v>4793.03</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="n">
+        <v>46322.58333333334</v>
+      </c>
+      <c r="B606" t="n">
+        <v>3661.46</v>
+      </c>
+      <c r="C606" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="D606" t="n">
+        <v>0</v>
+      </c>
+      <c r="E606" t="n">
+        <v>1094.75</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0</v>
+      </c>
+      <c r="G606" t="n">
+        <v>4811</v>
+      </c>
+      <c r="H606" t="n">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="n">
+        <v>46322.60416666666</v>
+      </c>
+      <c r="B607" t="n">
+        <v>3740.7</v>
+      </c>
+      <c r="C607" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="D607" t="n">
+        <v>0</v>
+      </c>
+      <c r="E607" t="n">
+        <v>1104.88</v>
+      </c>
+      <c r="F607" t="n">
+        <v>0</v>
+      </c>
+      <c r="G607" t="n">
+        <v>4907.7</v>
+      </c>
+      <c r="H607" t="n">
+        <v>4907.7</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="n">
+        <v>46322.625</v>
+      </c>
+      <c r="B608" t="n">
+        <v>3779.75</v>
+      </c>
+      <c r="C608" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="D608" t="n">
+        <v>0</v>
+      </c>
+      <c r="E608" t="n">
+        <v>1105.07</v>
+      </c>
+      <c r="F608" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="G608" t="n">
+        <v>4949.440000000001</v>
+      </c>
+      <c r="H608" t="n">
+        <v>4936.13</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="n">
+        <v>46322.64583333334</v>
+      </c>
+      <c r="B609" t="n">
+        <v>3825.06</v>
+      </c>
+      <c r="C609" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D609" t="n">
+        <v>0</v>
+      </c>
+      <c r="E609" t="n">
+        <v>1112.89</v>
+      </c>
+      <c r="F609" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="G609" t="n">
+        <v>4994.52</v>
+      </c>
+      <c r="H609" t="n">
+        <v>4976.45</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="n">
+        <v>46322.66666666666</v>
+      </c>
+      <c r="B610" t="n">
+        <v>3789.68</v>
+      </c>
+      <c r="C610" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="D610" t="n">
+        <v>0</v>
+      </c>
+      <c r="E610" t="n">
+        <v>1128.77</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0</v>
+      </c>
+      <c r="G610" t="n">
+        <v>4953.969999999999</v>
+      </c>
+      <c r="H610" t="n">
+        <v>4953.969999999999</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="n">
+        <v>46322.6875</v>
+      </c>
+      <c r="B611" t="n">
+        <v>3714.5</v>
+      </c>
+      <c r="C611" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="D611" t="n">
+        <v>0</v>
+      </c>
+      <c r="E611" t="n">
+        <v>1094.43</v>
+      </c>
+      <c r="F611" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G611" t="n">
+        <v>4862.76</v>
+      </c>
+      <c r="H611" t="n">
+        <v>4848.06</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>46322.70833333334</v>
+      </c>
+      <c r="B612" t="n">
+        <v>3518.09</v>
+      </c>
+      <c r="C612" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D612" t="n">
+        <v>0</v>
+      </c>
+      <c r="E612" t="n">
+        <v>1095.21</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0</v>
+      </c>
+      <c r="G612" t="n">
+        <v>4639.6</v>
+      </c>
+      <c r="H612" t="n">
+        <v>4639.6</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="n">
+        <v>46322.72916666666</v>
+      </c>
+      <c r="B613" t="n">
+        <v>3412.5</v>
+      </c>
+      <c r="C613" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="D613" t="n">
+        <v>0</v>
+      </c>
+      <c r="E613" t="n">
+        <v>1113.83</v>
+      </c>
+      <c r="F613" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G613" t="n">
+        <v>4539.19</v>
+      </c>
+      <c r="H613" t="n">
+        <v>4534.9</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="n">
+        <v>46322.75</v>
+      </c>
+      <c r="B614" t="n">
+        <v>3433.02</v>
+      </c>
+      <c r="C614" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="D614" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="E614" t="n">
+        <v>1131.62</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0</v>
+      </c>
+      <c r="G614" t="n">
+        <v>4576.940000000001</v>
+      </c>
+      <c r="H614" t="n">
+        <v>4576.940000000001</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="n">
+        <v>46322.77083333334</v>
+      </c>
+      <c r="B615" t="n">
+        <v>3800.91</v>
+      </c>
+      <c r="C615" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D615" t="n">
+        <v>0</v>
+      </c>
+      <c r="E615" t="n">
+        <v>1123.37</v>
+      </c>
+      <c r="F615" t="n">
+        <v>0</v>
+      </c>
+      <c r="G615" t="n">
+        <v>4932.379999999999</v>
+      </c>
+      <c r="H615" t="n">
+        <v>4932.379999999999</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="n">
+        <v>46322.79166666666</v>
+      </c>
+      <c r="B616" t="n">
+        <v>3814.42</v>
+      </c>
+      <c r="C616" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D616" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E616" t="n">
+        <v>1136.83</v>
+      </c>
+      <c r="F616" t="n">
+        <v>0</v>
+      </c>
+      <c r="G616" t="n">
+        <v>4962.32</v>
+      </c>
+      <c r="H616" t="n">
+        <v>4962.32</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="n">
+        <v>46322.8125</v>
+      </c>
+      <c r="B617" t="n">
+        <v>3940.67</v>
+      </c>
+      <c r="C617" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="D617" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E617" t="n">
+        <v>1138.26</v>
+      </c>
+      <c r="F617" t="n">
+        <v>0</v>
+      </c>
+      <c r="G617" t="n">
+        <v>5101.1</v>
+      </c>
+      <c r="H617" t="n">
+        <v>5101.1</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="n">
+        <v>46322.83333333334</v>
+      </c>
+      <c r="B618" t="n">
+        <v>3826.73</v>
+      </c>
+      <c r="C618" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="D618" t="n">
+        <v>0</v>
+      </c>
+      <c r="E618" t="n">
+        <v>1126.56</v>
+      </c>
+      <c r="F618" t="n">
+        <v>0</v>
+      </c>
+      <c r="G618" t="n">
+        <v>4962.860000000001</v>
+      </c>
+      <c r="H618" t="n">
+        <v>4962.860000000001</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="n">
+        <v>46322.85416666666</v>
+      </c>
+      <c r="B619" t="n">
+        <v>3878.33</v>
+      </c>
+      <c r="C619" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="D619" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="E619" t="n">
+        <v>1121.48</v>
+      </c>
+      <c r="F619" t="n">
+        <v>0</v>
+      </c>
+      <c r="G619" t="n">
+        <v>5012.58</v>
+      </c>
+      <c r="H619" t="n">
+        <v>5012.58</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="n">
+        <v>46322.875</v>
+      </c>
+      <c r="B620" t="n">
+        <v>3840.38</v>
+      </c>
+      <c r="C620" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="D620" t="n">
+        <v>0</v>
+      </c>
+      <c r="E620" t="n">
+        <v>1126.4</v>
+      </c>
+      <c r="F620" t="n">
+        <v>0</v>
+      </c>
+      <c r="G620" t="n">
+        <v>4974.31</v>
+      </c>
+      <c r="H620" t="n">
+        <v>4974.31</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="n">
+        <v>46322.89583333334</v>
+      </c>
+      <c r="B621" t="n">
+        <v>3722.92</v>
+      </c>
+      <c r="C621" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="D621" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E621" t="n">
+        <v>1126.34</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0</v>
+      </c>
+      <c r="G621" t="n">
+        <v>4861.38</v>
+      </c>
+      <c r="H621" t="n">
+        <v>4861.38</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="n">
+        <v>46322.91666666666</v>
+      </c>
+      <c r="B622" t="n">
+        <v>3596.34</v>
+      </c>
+      <c r="C622" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="D622" t="n">
+        <v>0</v>
+      </c>
+      <c r="E622" t="n">
+        <v>1131.46</v>
+      </c>
+      <c r="F622" t="n">
+        <v>0</v>
+      </c>
+      <c r="G622" t="n">
+        <v>4734.780000000001</v>
+      </c>
+      <c r="H622" t="n">
+        <v>4734.780000000001</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="n">
+        <v>46322.9375</v>
+      </c>
+      <c r="B623" t="n">
+        <v>3416.11</v>
+      </c>
+      <c r="C623" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="D623" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E623" t="n">
+        <v>1127.73</v>
+      </c>
+      <c r="F623" t="n">
+        <v>0</v>
+      </c>
+      <c r="G623" t="n">
+        <v>4557.719999999999</v>
+      </c>
+      <c r="H623" t="n">
+        <v>4557.719999999999</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="n">
+        <v>46322.95833333334</v>
+      </c>
+      <c r="B624" t="n">
+        <v>3207.14</v>
+      </c>
+      <c r="C624" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D624" t="n">
+        <v>0</v>
+      </c>
+      <c r="E624" t="n">
+        <v>1126.5</v>
+      </c>
+      <c r="F624" t="n">
+        <v>0</v>
+      </c>
+      <c r="G624" t="n">
+        <v>4340.58</v>
+      </c>
+      <c r="H624" t="n">
+        <v>4340.58</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="n">
+        <v>46322.97916666666</v>
+      </c>
+      <c r="B625" t="n">
+        <v>2995.05</v>
+      </c>
+      <c r="C625" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D625" t="n">
+        <v>0</v>
+      </c>
+      <c r="E625" t="n">
+        <v>1126.19</v>
+      </c>
+      <c r="F625" t="n">
+        <v>0</v>
+      </c>
+      <c r="G625" t="n">
+        <v>4128.14</v>
+      </c>
+      <c r="H625" t="n">
+        <v>4128.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,6 +1297,59 @@
       </c>
       <c r="Q14" t="n">
         <v>0.003</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B15" t="n">
+        <v>94014</v>
+      </c>
+      <c r="C15" t="n">
+        <v>67798</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25664</v>
+      </c>
+      <c r="E15" t="n">
+        <v>23954</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1710</v>
+      </c>
+      <c r="G15" t="n">
+        <v>442</v>
+      </c>
+      <c r="H15" t="n">
+        <v>110</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.917</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.004</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1326,14 +1379,14 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Paute</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Coca Codo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Paute</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
           <t>Sopladora</t>
@@ -1341,12 +1394,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Delsitanisagua</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1373,19 +1426,19 @@
         <v>16882</v>
       </c>
       <c r="C2" t="n">
+        <v>13964</v>
+      </c>
+      <c r="D2" t="n">
         <v>24721</v>
-      </c>
-      <c r="D2" t="n">
-        <v>13964</v>
       </c>
       <c r="E2" t="n">
         <v>8114</v>
       </c>
       <c r="F2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="G2" t="n">
         <v>3724</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2768</v>
       </c>
       <c r="H2" t="n">
         <v>239</v>
@@ -1405,19 +1458,19 @@
         <v>20069</v>
       </c>
       <c r="C3" t="n">
+        <v>16681</v>
+      </c>
+      <c r="D3" t="n">
         <v>23420</v>
-      </c>
-      <c r="D3" t="n">
-        <v>16681</v>
       </c>
       <c r="E3" t="n">
         <v>8424</v>
       </c>
       <c r="F3" t="n">
+        <v>2477</v>
+      </c>
+      <c r="G3" t="n">
         <v>3644</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2477</v>
       </c>
       <c r="H3" t="n">
         <v>1531</v>
@@ -1437,19 +1490,19 @@
         <v>19095</v>
       </c>
       <c r="C4" t="n">
+        <v>17645</v>
+      </c>
+      <c r="D4" t="n">
         <v>19992</v>
-      </c>
-      <c r="D4" t="n">
-        <v>17645</v>
       </c>
       <c r="E4" t="n">
         <v>9735</v>
       </c>
       <c r="F4" t="n">
+        <v>2491</v>
+      </c>
+      <c r="G4" t="n">
         <v>3194</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2491</v>
       </c>
       <c r="H4" t="n">
         <v>306</v>
@@ -1469,19 +1522,19 @@
         <v>19098</v>
       </c>
       <c r="C5" t="n">
+        <v>14882</v>
+      </c>
+      <c r="D5" t="n">
         <v>17987</v>
-      </c>
-      <c r="D5" t="n">
-        <v>14882</v>
       </c>
       <c r="E5" t="n">
         <v>8469</v>
       </c>
       <c r="F5" t="n">
+        <v>2773</v>
+      </c>
+      <c r="G5" t="n">
         <v>3026</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2773</v>
       </c>
       <c r="H5" t="n">
         <v>721</v>
@@ -1501,19 +1554,19 @@
         <v>20810</v>
       </c>
       <c r="C6" t="n">
+        <v>14644</v>
+      </c>
+      <c r="D6" t="n">
         <v>17990</v>
-      </c>
-      <c r="D6" t="n">
-        <v>14644</v>
       </c>
       <c r="E6" t="n">
         <v>8416</v>
       </c>
       <c r="F6" t="n">
+        <v>2472</v>
+      </c>
+      <c r="G6" t="n">
         <v>3345</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2472</v>
       </c>
       <c r="H6" t="n">
         <v>750</v>
@@ -1533,19 +1586,19 @@
         <v>19280</v>
       </c>
       <c r="C7" t="n">
+        <v>10078</v>
+      </c>
+      <c r="D7" t="n">
         <v>22254</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10078</v>
       </c>
       <c r="E7" t="n">
         <v>5868</v>
       </c>
       <c r="F7" t="n">
+        <v>2512</v>
+      </c>
+      <c r="G7" t="n">
         <v>2963</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2512</v>
       </c>
       <c r="H7" t="n">
         <v>461</v>
@@ -1565,19 +1618,19 @@
         <v>21755</v>
       </c>
       <c r="C8" t="n">
+        <v>5014</v>
+      </c>
+      <c r="D8" t="n">
         <v>26473</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5014</v>
       </c>
       <c r="E8" t="n">
         <v>2907</v>
       </c>
       <c r="F8" t="n">
+        <v>2854</v>
+      </c>
+      <c r="G8" t="n">
         <v>3431</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2854</v>
       </c>
       <c r="H8" t="n">
         <v>1105</v>
@@ -1595,19 +1648,19 @@
         <v>19704</v>
       </c>
       <c r="C9" t="n">
+        <v>14358</v>
+      </c>
+      <c r="D9" t="n">
         <v>23346</v>
-      </c>
-      <c r="D9" t="n">
-        <v>14358</v>
       </c>
       <c r="E9" t="n">
         <v>8041</v>
       </c>
       <c r="F9" t="n">
+        <v>2801</v>
+      </c>
+      <c r="G9" t="n">
         <v>2788</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2801</v>
       </c>
       <c r="H9" t="n">
         <v>1488</v>
@@ -1627,19 +1680,19 @@
         <v>18740</v>
       </c>
       <c r="C10" t="n">
+        <v>18959</v>
+      </c>
+      <c r="D10" t="n">
         <v>19157</v>
-      </c>
-      <c r="D10" t="n">
-        <v>18959</v>
       </c>
       <c r="E10" t="n">
         <v>9960</v>
       </c>
       <c r="F10" t="n">
+        <v>2566</v>
+      </c>
+      <c r="G10" t="n">
         <v>2675</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2566</v>
       </c>
       <c r="H10" t="n">
         <v>1870</v>
@@ -1659,19 +1712,19 @@
         <v>19903</v>
       </c>
       <c r="C11" t="n">
+        <v>18347</v>
+      </c>
+      <c r="D11" t="n">
         <v>19048</v>
-      </c>
-      <c r="D11" t="n">
-        <v>18347</v>
       </c>
       <c r="E11" t="n">
         <v>9798</v>
       </c>
       <c r="F11" t="n">
+        <v>2706</v>
+      </c>
+      <c r="G11" t="n">
         <v>2526</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2706</v>
       </c>
       <c r="H11" t="n">
         <v>1693</v>
@@ -1691,19 +1744,19 @@
         <v>20083</v>
       </c>
       <c r="C12" t="n">
+        <v>16208</v>
+      </c>
+      <c r="D12" t="n">
         <v>16518</v>
-      </c>
-      <c r="D12" t="n">
-        <v>16208</v>
       </c>
       <c r="E12" t="n">
         <v>9495</v>
       </c>
       <c r="F12" t="n">
+        <v>2525</v>
+      </c>
+      <c r="G12" t="n">
         <v>2565</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2525</v>
       </c>
       <c r="H12" t="n">
         <v>447</v>
@@ -1723,19 +1776,19 @@
         <v>24903</v>
       </c>
       <c r="C13" t="n">
+        <v>6934</v>
+      </c>
+      <c r="D13" t="n">
         <v>21674</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6934</v>
       </c>
       <c r="E13" t="n">
         <v>4088</v>
       </c>
       <c r="F13" t="n">
+        <v>2823</v>
+      </c>
+      <c r="G13" t="n">
         <v>2495</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2823</v>
       </c>
       <c r="H13" t="n">
         <v>1264</v>
@@ -1755,19 +1808,19 @@
         <v>24052</v>
       </c>
       <c r="C14" t="n">
+        <v>11236</v>
+      </c>
+      <c r="D14" t="n">
         <v>20199</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11236</v>
       </c>
       <c r="E14" t="n">
         <v>5881</v>
       </c>
       <c r="F14" t="n">
+        <v>2554</v>
+      </c>
+      <c r="G14" t="n">
         <v>2635</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2554</v>
       </c>
       <c r="H14" t="n">
         <v>2136</v>
@@ -1777,6 +1830,38 @@
       </c>
       <c r="J14" t="n">
         <v>1408</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B15" t="n">
+        <v>25337</v>
+      </c>
+      <c r="C15" t="n">
+        <v>13787</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8701</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7818</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3013</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2803</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2421</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2178</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1740</v>
       </c>
     </row>
   </sheetData>
@@ -1790,7 +1875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2181,21 +2266,17 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46291</v>
+        <v>46323</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Napo</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2204,7 +2285,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>24721</v>
+        <v>25337</v>
       </c>
     </row>
     <row r="16">
@@ -2212,21 +2293,21 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2235,7 +2316,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>23420</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="17">
@@ -2243,21 +2324,21 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2266,7 +2347,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>19992</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="18">
@@ -2274,21 +2355,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2297,7 +2378,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>17987</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="19">
@@ -2305,21 +2386,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2328,7 +2409,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>17990</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="20">
@@ -2336,21 +2417,21 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2359,7 +2440,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>22254</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="21">
@@ -2367,21 +2448,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2390,7 +2471,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>26473</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="22">
@@ -2398,21 +2479,21 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2421,7 +2502,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>23346</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="23">
@@ -2429,21 +2510,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2452,7 +2533,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>19157</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="24">
@@ -2460,21 +2541,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2483,7 +2564,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>19048</v>
+        <v>18959</v>
       </c>
     </row>
     <row r="25">
@@ -2491,21 +2572,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46305</v>
+        <v>46302</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2514,7 +2595,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>16518</v>
+        <v>18347</v>
       </c>
     </row>
     <row r="26">
@@ -2522,21 +2603,21 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46321</v>
+        <v>46305</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2545,7 +2626,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>21674</v>
+        <v>16208</v>
       </c>
     </row>
     <row r="27">
@@ -2553,21 +2634,21 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2576,7 +2657,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>20199</v>
+        <v>6934</v>
       </c>
     </row>
     <row r="28">
@@ -2584,7 +2665,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46291</v>
+        <v>46322</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2607,7 +2688,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>13964</v>
+        <v>11236</v>
       </c>
     </row>
     <row r="29">
@@ -2615,7 +2696,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46293</v>
+        <v>46323</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2638,7 +2719,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>16681</v>
+        <v>13787</v>
       </c>
     </row>
     <row r="30">
@@ -2646,21 +2727,21 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2669,7 +2750,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>17645</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="31">
@@ -2677,21 +2758,21 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2700,7 +2781,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>14882</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="32">
@@ -2708,21 +2789,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2731,7 +2812,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>14644</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="33">
@@ -2739,21 +2820,21 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2762,7 +2843,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>10078</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="34">
@@ -2770,21 +2851,21 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2793,7 +2874,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5014</v>
+        <v>17990</v>
       </c>
     </row>
     <row r="35">
@@ -2801,21 +2882,21 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2824,7 +2905,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>14358</v>
+        <v>22254</v>
       </c>
     </row>
     <row r="36">
@@ -2832,21 +2913,21 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2855,7 +2936,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>18959</v>
+        <v>26473</v>
       </c>
     </row>
     <row r="37">
@@ -2863,21 +2944,21 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2886,7 +2967,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>18347</v>
+        <v>23346</v>
       </c>
     </row>
     <row r="38">
@@ -2894,21 +2975,21 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46305</v>
+        <v>46301</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2917,7 +2998,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>16208</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="39">
@@ -2925,21 +3006,21 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46321</v>
+        <v>46302</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2948,7 +3029,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>6934</v>
+        <v>19048</v>
       </c>
     </row>
     <row r="40">
@@ -2956,21 +3037,21 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46322</v>
+        <v>46305</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2979,7 +3060,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>11236</v>
+        <v>16518</v>
       </c>
     </row>
     <row r="41">
@@ -2987,21 +3068,21 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3010,7 +3091,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>8114</v>
+        <v>21674</v>
       </c>
     </row>
     <row r="42">
@@ -3018,21 +3099,21 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46293</v>
+        <v>46322</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3041,7 +3122,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>8424</v>
+        <v>20199</v>
       </c>
     </row>
     <row r="43">
@@ -3049,21 +3130,21 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46294</v>
+        <v>46323</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3072,7 +3153,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>9735</v>
+        <v>8701</v>
       </c>
     </row>
     <row r="44">
@@ -3080,7 +3161,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -3103,7 +3184,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>8469</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="45">
@@ -3111,7 +3192,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3134,7 +3215,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>8416</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="46">
@@ -3142,7 +3223,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3165,7 +3246,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>5868</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="47">
@@ -3173,7 +3254,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3196,7 +3277,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2907</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="48">
@@ -3204,7 +3285,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3227,7 +3308,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>8041</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="49">
@@ -3235,7 +3316,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3258,7 +3339,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>9960</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="50">
@@ -3266,7 +3347,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46302</v>
+        <v>46298</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3289,7 +3370,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>9798</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="51">
@@ -3297,7 +3378,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3320,7 +3401,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>9495</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="52">
@@ -3328,7 +3409,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46321</v>
+        <v>46301</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3351,7 +3432,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>4088</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="53">
@@ -3359,7 +3440,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46322</v>
+        <v>46302</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3382,7 +3463,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>5881</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="54">
@@ -3390,21 +3471,21 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3413,7 +3494,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3724</v>
+        <v>9495</v>
       </c>
     </row>
     <row r="55">
@@ -3421,21 +3502,21 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46293</v>
+        <v>46321</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3444,7 +3525,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3644</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="56">
@@ -3452,21 +3533,21 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46294</v>
+        <v>46322</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3475,7 +3556,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3194</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="57">
@@ -3483,21 +3564,21 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46295</v>
+        <v>46323</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3506,7 +3587,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3026</v>
+        <v>7818</v>
       </c>
     </row>
     <row r="58">
@@ -3514,21 +3595,21 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3537,7 +3618,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3345</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="59">
@@ -3545,21 +3626,21 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3568,7 +3649,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2963</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="60">
@@ -3576,21 +3657,21 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3599,7 +3680,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3431</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="61">
@@ -3607,21 +3688,21 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3630,7 +3711,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2788</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="62">
@@ -3638,21 +3719,21 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3661,7 +3742,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2675</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="63">
@@ -3669,21 +3750,21 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3692,7 +3773,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2526</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="64">
@@ -3700,21 +3781,21 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3723,7 +3804,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2565</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="65">
@@ -3731,21 +3812,21 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46321</v>
+        <v>46300</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3754,7 +3835,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2495</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="66">
@@ -3762,21 +3843,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46322</v>
+        <v>46301</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3785,7 +3866,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2635</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="67">
@@ -3793,7 +3874,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46291</v>
+        <v>46302</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3816,7 +3897,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2768</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="68">
@@ -3824,7 +3905,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46293</v>
+        <v>46305</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3847,7 +3928,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2477</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="69">
@@ -3855,7 +3936,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46294</v>
+        <v>46321</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3878,7 +3959,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2491</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="70">
@@ -3886,7 +3967,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46295</v>
+        <v>46322</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3909,7 +3990,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2773</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="71">
@@ -3917,7 +3998,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46296</v>
+        <v>46323</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3940,7 +4021,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2472</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="72">
@@ -3948,21 +4029,21 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3971,7 +4052,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2512</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="73">
@@ -3979,21 +4060,21 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46298</v>
+        <v>46293</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4002,7 +4083,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2854</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="74">
@@ -4010,21 +4091,21 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46300</v>
+        <v>46294</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4033,7 +4114,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2801</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="75">
@@ -4041,21 +4122,21 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46301</v>
+        <v>46295</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4064,7 +4145,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2566</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="76">
@@ -4072,21 +4153,21 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4095,7 +4176,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2706</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="77">
@@ -4103,21 +4184,21 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46305</v>
+        <v>46297</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4126,7 +4207,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2525</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="78">
@@ -4134,21 +4215,21 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46321</v>
+        <v>46298</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4157,7 +4238,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2823</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="79">
@@ -4165,21 +4246,21 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46322</v>
+        <v>46300</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4188,7 +4269,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>2554</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="80">
@@ -4196,21 +4277,21 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46291</v>
+        <v>46301</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4219,7 +4300,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>239</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="81">
@@ -4227,21 +4308,21 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4250,7 +4331,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1531</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="82">
@@ -4258,21 +4339,21 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46294</v>
+        <v>46305</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4281,7 +4362,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>306</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="83">
@@ -4289,21 +4370,21 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46295</v>
+        <v>46321</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4312,7 +4393,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>721</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="84">
@@ -4320,21 +4401,21 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46296</v>
+        <v>46322</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4343,7 +4424,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>750</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="85">
@@ -4351,21 +4432,21 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46297</v>
+        <v>46323</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4374,7 +4455,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>461</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="86">
@@ -4382,7 +4463,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4405,7 +4486,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1105</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87">
@@ -4413,7 +4494,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4436,7 +4517,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1488</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="88">
@@ -4444,7 +4525,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4467,7 +4548,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1870</v>
+        <v>306</v>
       </c>
     </row>
     <row r="89">
@@ -4475,7 +4556,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4498,7 +4579,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1693</v>
+        <v>721</v>
       </c>
     </row>
     <row r="90">
@@ -4506,7 +4587,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46305</v>
+        <v>46296</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4529,7 +4610,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>447</v>
+        <v>750</v>
       </c>
     </row>
     <row r="91">
@@ -4537,7 +4618,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46321</v>
+        <v>46297</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4560,7 +4641,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1264</v>
+        <v>461</v>
       </c>
     </row>
     <row r="92">
@@ -4568,7 +4649,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46322</v>
+        <v>46298</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4591,7 +4672,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>2136</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="93">
@@ -4599,16 +4680,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4622,7 +4703,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2003</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="94">
@@ -4630,16 +4711,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4653,7 +4734,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1820</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="95">
@@ -4661,16 +4742,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4684,7 +4765,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1820</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="96">
@@ -4692,16 +4773,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4715,7 +4796,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2009</v>
+        <v>447</v>
       </c>
     </row>
     <row r="97">
@@ -4723,16 +4804,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46296</v>
+        <v>46321</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4746,7 +4827,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1847</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="98">
@@ -4754,16 +4835,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46297</v>
+        <v>46322</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4777,7 +4858,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1853</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="99">
@@ -4785,16 +4866,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46298</v>
+        <v>46323</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4808,7 +4889,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2034</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="100">
@@ -4816,7 +4897,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46300</v>
+        <v>46291</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4839,7 +4920,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>2027</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="101">
@@ -4847,7 +4928,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4870,7 +4951,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1907</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="102">
@@ -4878,7 +4959,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46302</v>
+        <v>46294</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4901,7 +4982,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1966</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="103">
@@ -4909,7 +4990,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46305</v>
+        <v>46295</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4932,7 +5013,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1838</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="104">
@@ -4940,7 +5021,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46321</v>
+        <v>46296</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4963,7 +5044,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1997</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="105">
@@ -4971,7 +5052,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46322</v>
+        <v>46297</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -4994,7 +5075,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1840</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="106">
@@ -5002,16 +5083,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5025,7 +5106,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2301</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="107">
@@ -5033,16 +5114,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5056,7 +5137,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2554</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="108">
@@ -5064,16 +5145,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5087,7 +5168,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2604</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="109">
@@ -5095,16 +5176,16 @@
         <v>107</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5118,7 +5199,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2307</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="110">
@@ -5126,16 +5207,16 @@
         <v>108</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46296</v>
+        <v>46305</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5149,7 +5230,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3102</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="111">
@@ -5157,16 +5238,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46297</v>
+        <v>46321</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5180,7 +5261,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2187</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="112">
@@ -5188,16 +5269,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46300</v>
+        <v>46322</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5211,7 +5292,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1164</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="113">
@@ -5219,16 +5300,16 @@
         <v>111</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46301</v>
+        <v>46323</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5242,7 +5323,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2157</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="114">
@@ -5250,7 +5331,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46302</v>
+        <v>46291</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5273,7 +5354,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2831</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="115">
@@ -5281,7 +5362,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46305</v>
+        <v>46293</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5304,7 +5385,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>2551</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="116">
@@ -5312,7 +5393,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46321</v>
+        <v>46294</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5335,7 +5416,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1358</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="117">
@@ -5343,30 +5424,309 @@
         <v>115</v>
       </c>
       <c r="B117" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="2" t="n">
         <v>46322</v>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Mazar</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G117" t="n">
+      <c r="G125" t="n">
         <v>1408</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1740</v>
       </c>
     </row>
   </sheetData>
@@ -5380,7 +5740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H625"/>
+  <dimension ref="A1:H673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21649,6 +22009,1254 @@
         <v>4128.14</v>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B626" t="n">
+        <v>2742.85</v>
+      </c>
+      <c r="C626" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="D626" t="n">
+        <v>0</v>
+      </c>
+      <c r="E626" t="n">
+        <v>1129.83</v>
+      </c>
+      <c r="F626" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="G626" t="n">
+        <v>3905.63</v>
+      </c>
+      <c r="H626" t="n">
+        <v>3879.86</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="n">
+        <v>46323.02083333334</v>
+      </c>
+      <c r="B627" t="n">
+        <v>2620.72</v>
+      </c>
+      <c r="C627" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="D627" t="n">
+        <v>0</v>
+      </c>
+      <c r="E627" t="n">
+        <v>1095.71</v>
+      </c>
+      <c r="F627" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="G627" t="n">
+        <v>3736.67</v>
+      </c>
+      <c r="H627" t="n">
+        <v>3722.62</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="n">
+        <v>46323.04166666666</v>
+      </c>
+      <c r="B628" t="n">
+        <v>2516.78</v>
+      </c>
+      <c r="C628" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D628" t="n">
+        <v>0</v>
+      </c>
+      <c r="E628" t="n">
+        <v>1087.65</v>
+      </c>
+      <c r="F628" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="G628" t="n">
+        <v>3623.42</v>
+      </c>
+      <c r="H628" t="n">
+        <v>3610.63</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="n">
+        <v>46323.0625</v>
+      </c>
+      <c r="B629" t="n">
+        <v>2490.39</v>
+      </c>
+      <c r="C629" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D629" t="n">
+        <v>0</v>
+      </c>
+      <c r="E629" t="n">
+        <v>1020.75</v>
+      </c>
+      <c r="F629" t="n">
+        <v>0</v>
+      </c>
+      <c r="G629" t="n">
+        <v>3517.34</v>
+      </c>
+      <c r="H629" t="n">
+        <v>3517.34</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="n">
+        <v>46323.08333333334</v>
+      </c>
+      <c r="B630" t="n">
+        <v>2418.44</v>
+      </c>
+      <c r="C630" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="D630" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E630" t="n">
+        <v>1030.71</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0</v>
+      </c>
+      <c r="G630" t="n">
+        <v>3457.84</v>
+      </c>
+      <c r="H630" t="n">
+        <v>3457.84</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="n">
+        <v>46323.10416666666</v>
+      </c>
+      <c r="B631" t="n">
+        <v>2287.16</v>
+      </c>
+      <c r="C631" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="D631" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="E631" t="n">
+        <v>1059.02</v>
+      </c>
+      <c r="F631" t="n">
+        <v>0</v>
+      </c>
+      <c r="G631" t="n">
+        <v>3372.19</v>
+      </c>
+      <c r="H631" t="n">
+        <v>3372.19</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="n">
+        <v>46323.125</v>
+      </c>
+      <c r="B632" t="n">
+        <v>2258.02</v>
+      </c>
+      <c r="C632" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D632" t="n">
+        <v>0</v>
+      </c>
+      <c r="E632" t="n">
+        <v>1053.48</v>
+      </c>
+      <c r="F632" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G632" t="n">
+        <v>3320.87</v>
+      </c>
+      <c r="H632" t="n">
+        <v>3318.45</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="n">
+        <v>46323.14583333334</v>
+      </c>
+      <c r="B633" t="n">
+        <v>2212.35</v>
+      </c>
+      <c r="C633" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="D633" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E633" t="n">
+        <v>1053.32</v>
+      </c>
+      <c r="F633" t="n">
+        <v>0</v>
+      </c>
+      <c r="G633" t="n">
+        <v>3274.74</v>
+      </c>
+      <c r="H633" t="n">
+        <v>3274.74</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="n">
+        <v>46323.16666666666</v>
+      </c>
+      <c r="B634" t="n">
+        <v>2156.3</v>
+      </c>
+      <c r="C634" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="D634" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="E634" t="n">
+        <v>1068.22</v>
+      </c>
+      <c r="F634" t="n">
+        <v>0</v>
+      </c>
+      <c r="G634" t="n">
+        <v>3239.09</v>
+      </c>
+      <c r="H634" t="n">
+        <v>3239.09</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="n">
+        <v>46323.1875</v>
+      </c>
+      <c r="B635" t="n">
+        <v>2142.75</v>
+      </c>
+      <c r="C635" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="D635" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="E635" t="n">
+        <v>1071.43</v>
+      </c>
+      <c r="F635" t="n">
+        <v>0</v>
+      </c>
+      <c r="G635" t="n">
+        <v>3235.18</v>
+      </c>
+      <c r="H635" t="n">
+        <v>3235.18</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="n">
+        <v>46323.20833333334</v>
+      </c>
+      <c r="B636" t="n">
+        <v>2183</v>
+      </c>
+      <c r="C636" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D636" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="E636" t="n">
+        <v>1065.89</v>
+      </c>
+      <c r="F636" t="n">
+        <v>0</v>
+      </c>
+      <c r="G636" t="n">
+        <v>3259.08</v>
+      </c>
+      <c r="H636" t="n">
+        <v>3259.08</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="n">
+        <v>46323.22916666666</v>
+      </c>
+      <c r="B637" t="n">
+        <v>2259</v>
+      </c>
+      <c r="C637" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D637" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="E637" t="n">
+        <v>1071.67</v>
+      </c>
+      <c r="F637" t="n">
+        <v>0</v>
+      </c>
+      <c r="G637" t="n">
+        <v>3341.15</v>
+      </c>
+      <c r="H637" t="n">
+        <v>3341.15</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="n">
+        <v>46323.25</v>
+      </c>
+      <c r="B638" t="n">
+        <v>2248.9</v>
+      </c>
+      <c r="C638" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="D638" t="n">
+        <v>0</v>
+      </c>
+      <c r="E638" t="n">
+        <v>1084.33</v>
+      </c>
+      <c r="F638" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="G638" t="n">
+        <v>3368.54</v>
+      </c>
+      <c r="H638" t="n">
+        <v>3339.21</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="n">
+        <v>46323.27083333334</v>
+      </c>
+      <c r="B639" t="n">
+        <v>2090.3</v>
+      </c>
+      <c r="C639" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="D639" t="n">
+        <v>0</v>
+      </c>
+      <c r="E639" t="n">
+        <v>1091.5</v>
+      </c>
+      <c r="F639" t="n">
+        <v>0</v>
+      </c>
+      <c r="G639" t="n">
+        <v>3187.83</v>
+      </c>
+      <c r="H639" t="n">
+        <v>3187.83</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="n">
+        <v>46323.29166666666</v>
+      </c>
+      <c r="B640" t="n">
+        <v>2039.26</v>
+      </c>
+      <c r="C640" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="D640" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="E640" t="n">
+        <v>1086.19</v>
+      </c>
+      <c r="F640" t="n">
+        <v>0</v>
+      </c>
+      <c r="G640" t="n">
+        <v>3145.92</v>
+      </c>
+      <c r="H640" t="n">
+        <v>3145.92</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="n">
+        <v>46323.3125</v>
+      </c>
+      <c r="B641" t="n">
+        <v>2156.27</v>
+      </c>
+      <c r="C641" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D641" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E641" t="n">
+        <v>1083.05</v>
+      </c>
+      <c r="F641" t="n">
+        <v>0</v>
+      </c>
+      <c r="G641" t="n">
+        <v>3256.25</v>
+      </c>
+      <c r="H641" t="n">
+        <v>3256.25</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="n">
+        <v>46323.33333333334</v>
+      </c>
+      <c r="B642" t="n">
+        <v>2268.29</v>
+      </c>
+      <c r="C642" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D642" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E642" t="n">
+        <v>1083.21</v>
+      </c>
+      <c r="F642" t="n">
+        <v>0</v>
+      </c>
+      <c r="G642" t="n">
+        <v>3370.84</v>
+      </c>
+      <c r="H642" t="n">
+        <v>3370.84</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="n">
+        <v>46323.35416666666</v>
+      </c>
+      <c r="B643" t="n">
+        <v>2423.63</v>
+      </c>
+      <c r="C643" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="D643" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E643" t="n">
+        <v>1082.52</v>
+      </c>
+      <c r="F643" t="n">
+        <v>0</v>
+      </c>
+      <c r="G643" t="n">
+        <v>3522.04</v>
+      </c>
+      <c r="H643" t="n">
+        <v>3522.04</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="n">
+        <v>46323.375</v>
+      </c>
+      <c r="B644" t="n">
+        <v>2537.53</v>
+      </c>
+      <c r="C644" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="D644" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="E644" t="n">
+        <v>1084.56</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0</v>
+      </c>
+      <c r="G644" t="n">
+        <v>3634.68</v>
+      </c>
+      <c r="H644" t="n">
+        <v>3634.68</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="n">
+        <v>46323.39583333334</v>
+      </c>
+      <c r="B645" t="n">
+        <v>2664.71</v>
+      </c>
+      <c r="C645" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="D645" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E645" t="n">
+        <v>1083.49</v>
+      </c>
+      <c r="F645" t="n">
+        <v>0</v>
+      </c>
+      <c r="G645" t="n">
+        <v>3756.06</v>
+      </c>
+      <c r="H645" t="n">
+        <v>3756.06</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="n">
+        <v>46323.41666666666</v>
+      </c>
+      <c r="B646" t="n">
+        <v>2765.11</v>
+      </c>
+      <c r="C646" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="D646" t="n">
+        <v>0</v>
+      </c>
+      <c r="E646" t="n">
+        <v>1086.26</v>
+      </c>
+      <c r="F646" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="G646" t="n">
+        <v>3890.52</v>
+      </c>
+      <c r="H646" t="n">
+        <v>3857.429999999999</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="n">
+        <v>46323.4375</v>
+      </c>
+      <c r="B647" t="n">
+        <v>2870.79</v>
+      </c>
+      <c r="C647" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D647" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="E647" t="n">
+        <v>1086.46</v>
+      </c>
+      <c r="F647" t="n">
+        <v>0</v>
+      </c>
+      <c r="G647" t="n">
+        <v>3975.32</v>
+      </c>
+      <c r="H647" t="n">
+        <v>3975.32</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="n">
+        <v>46323.45833333334</v>
+      </c>
+      <c r="B648" t="n">
+        <v>2948.31</v>
+      </c>
+      <c r="C648" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="D648" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E648" t="n">
+        <v>1079.4</v>
+      </c>
+      <c r="F648" t="n">
+        <v>0</v>
+      </c>
+      <c r="G648" t="n">
+        <v>4057.83</v>
+      </c>
+      <c r="H648" t="n">
+        <v>4057.83</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="n">
+        <v>46323.47916666666</v>
+      </c>
+      <c r="B649" t="n">
+        <v>2987.64</v>
+      </c>
+      <c r="C649" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="D649" t="n">
+        <v>0</v>
+      </c>
+      <c r="E649" t="n">
+        <v>1073.39</v>
+      </c>
+      <c r="F649" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="G649" t="n">
+        <v>4139.54</v>
+      </c>
+      <c r="H649" t="n">
+        <v>4111.97</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="n">
+        <v>46323.5</v>
+      </c>
+      <c r="B650" t="n">
+        <v>3057.37</v>
+      </c>
+      <c r="C650" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="D650" t="n">
+        <v>0</v>
+      </c>
+      <c r="E650" t="n">
+        <v>1082</v>
+      </c>
+      <c r="F650" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G650" t="n">
+        <v>4202.860000000001</v>
+      </c>
+      <c r="H650" t="n">
+        <v>4200.700000000001</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="n">
+        <v>46323.52083333334</v>
+      </c>
+      <c r="B651" t="n">
+        <v>3079.59</v>
+      </c>
+      <c r="C651" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="D651" t="n">
+        <v>0</v>
+      </c>
+      <c r="E651" t="n">
+        <v>1074.26</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0</v>
+      </c>
+      <c r="G651" t="n">
+        <v>4216.43</v>
+      </c>
+      <c r="H651" t="n">
+        <v>4216.43</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="n">
+        <v>46323.54166666666</v>
+      </c>
+      <c r="B652" t="n">
+        <v>3117.49</v>
+      </c>
+      <c r="C652" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="D652" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="E652" t="n">
+        <v>1065.93</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0</v>
+      </c>
+      <c r="G652" t="n">
+        <v>4255.48</v>
+      </c>
+      <c r="H652" t="n">
+        <v>4255.48</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="B653" t="n">
+        <v>3211.65</v>
+      </c>
+      <c r="C653" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="D653" t="n">
+        <v>0</v>
+      </c>
+      <c r="E653" t="n">
+        <v>1063.22</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0</v>
+      </c>
+      <c r="G653" t="n">
+        <v>4338.13</v>
+      </c>
+      <c r="H653" t="n">
+        <v>4338.13</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="n">
+        <v>46323.58333333334</v>
+      </c>
+      <c r="B654" t="n">
+        <v>3241.51</v>
+      </c>
+      <c r="C654" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="D654" t="n">
+        <v>0</v>
+      </c>
+      <c r="E654" t="n">
+        <v>1092.42</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0</v>
+      </c>
+      <c r="G654" t="n">
+        <v>4397.24</v>
+      </c>
+      <c r="H654" t="n">
+        <v>4397.24</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="n">
+        <v>46323.60416666666</v>
+      </c>
+      <c r="B655" t="n">
+        <v>3313.68</v>
+      </c>
+      <c r="C655" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="D655" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E655" t="n">
+        <v>1088.86</v>
+      </c>
+      <c r="F655" t="n">
+        <v>0</v>
+      </c>
+      <c r="G655" t="n">
+        <v>4464.549999999999</v>
+      </c>
+      <c r="H655" t="n">
+        <v>4464.549999999999</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="n">
+        <v>46323.625</v>
+      </c>
+      <c r="B656" t="n">
+        <v>3362.52</v>
+      </c>
+      <c r="C656" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="D656" t="n">
+        <v>0</v>
+      </c>
+      <c r="E656" t="n">
+        <v>1075.99</v>
+      </c>
+      <c r="F656" t="n">
+        <v>0</v>
+      </c>
+      <c r="G656" t="n">
+        <v>4490.6</v>
+      </c>
+      <c r="H656" t="n">
+        <v>4490.6</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="n">
+        <v>46323.64583333334</v>
+      </c>
+      <c r="B657" t="n">
+        <v>3378.75</v>
+      </c>
+      <c r="C657" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D657" t="n">
+        <v>0</v>
+      </c>
+      <c r="E657" t="n">
+        <v>1082.1</v>
+      </c>
+      <c r="F657" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="G657" t="n">
+        <v>4519.64</v>
+      </c>
+      <c r="H657" t="n">
+        <v>4507.25</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="n">
+        <v>46323.66666666666</v>
+      </c>
+      <c r="B658" t="n">
+        <v>3361.14</v>
+      </c>
+      <c r="C658" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="D658" t="n">
+        <v>0</v>
+      </c>
+      <c r="E658" t="n">
+        <v>1099.9</v>
+      </c>
+      <c r="F658" t="n">
+        <v>0</v>
+      </c>
+      <c r="G658" t="n">
+        <v>4496.860000000001</v>
+      </c>
+      <c r="H658" t="n">
+        <v>4496.860000000001</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="n">
+        <v>46323.6875</v>
+      </c>
+      <c r="B659" t="n">
+        <v>3346.85</v>
+      </c>
+      <c r="C659" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="D659" t="n">
+        <v>0</v>
+      </c>
+      <c r="E659" t="n">
+        <v>1101.93</v>
+      </c>
+      <c r="F659" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G659" t="n">
+        <v>4484.67</v>
+      </c>
+      <c r="H659" t="n">
+        <v>4478.97</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="n">
+        <v>46323.70833333334</v>
+      </c>
+      <c r="B660" t="n">
+        <v>3240.2</v>
+      </c>
+      <c r="C660" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="D660" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="E660" t="n">
+        <v>1105.26</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0</v>
+      </c>
+      <c r="G660" t="n">
+        <v>4381.29</v>
+      </c>
+      <c r="H660" t="n">
+        <v>4381.29</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="n">
+        <v>46323.72916666666</v>
+      </c>
+      <c r="B661" t="n">
+        <v>3165.37</v>
+      </c>
+      <c r="C661" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="D661" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="E661" t="n">
+        <v>1116.45</v>
+      </c>
+      <c r="F661" t="n">
+        <v>0</v>
+      </c>
+      <c r="G661" t="n">
+        <v>4313.6</v>
+      </c>
+      <c r="H661" t="n">
+        <v>4313.6</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="n">
+        <v>46323.75</v>
+      </c>
+      <c r="B662" t="n">
+        <v>3281.71</v>
+      </c>
+      <c r="C662" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="D662" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E662" t="n">
+        <v>1114.97</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0</v>
+      </c>
+      <c r="G662" t="n">
+        <v>4409.76</v>
+      </c>
+      <c r="H662" t="n">
+        <v>4409.76</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="n">
+        <v>46323.77083333334</v>
+      </c>
+      <c r="B663" t="n">
+        <v>3592.53</v>
+      </c>
+      <c r="C663" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="D663" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="E663" t="n">
+        <v>1115.5</v>
+      </c>
+      <c r="F663" t="n">
+        <v>0</v>
+      </c>
+      <c r="G663" t="n">
+        <v>4742.690000000001</v>
+      </c>
+      <c r="H663" t="n">
+        <v>4742.690000000001</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="n">
+        <v>46323.79166666666</v>
+      </c>
+      <c r="B664" t="n">
+        <v>3691.48</v>
+      </c>
+      <c r="C664" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="D664" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="E664" t="n">
+        <v>1099.36</v>
+      </c>
+      <c r="F664" t="n">
+        <v>0</v>
+      </c>
+      <c r="G664" t="n">
+        <v>4821.67</v>
+      </c>
+      <c r="H664" t="n">
+        <v>4821.67</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="n">
+        <v>46323.8125</v>
+      </c>
+      <c r="B665" t="n">
+        <v>3729.77</v>
+      </c>
+      <c r="C665" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D665" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E665" t="n">
+        <v>1099.66</v>
+      </c>
+      <c r="F665" t="n">
+        <v>0</v>
+      </c>
+      <c r="G665" t="n">
+        <v>4842.22</v>
+      </c>
+      <c r="H665" t="n">
+        <v>4842.22</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="n">
+        <v>46323.83333333334</v>
+      </c>
+      <c r="B666" t="n">
+        <v>3713.59</v>
+      </c>
+      <c r="C666" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="D666" t="n">
+        <v>0</v>
+      </c>
+      <c r="E666" t="n">
+        <v>1104.18</v>
+      </c>
+      <c r="F666" t="n">
+        <v>0</v>
+      </c>
+      <c r="G666" t="n">
+        <v>4824.85</v>
+      </c>
+      <c r="H666" t="n">
+        <v>4824.85</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="n">
+        <v>46323.85416666666</v>
+      </c>
+      <c r="B667" t="n">
+        <v>3657.69</v>
+      </c>
+      <c r="C667" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="D667" t="n">
+        <v>0</v>
+      </c>
+      <c r="E667" t="n">
+        <v>1126.89</v>
+      </c>
+      <c r="F667" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="G667" t="n">
+        <v>4795.12</v>
+      </c>
+      <c r="H667" t="n">
+        <v>4790.8</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="n">
+        <v>46323.875</v>
+      </c>
+      <c r="B668" t="n">
+        <v>3573.21</v>
+      </c>
+      <c r="C668" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D668" t="n">
+        <v>0</v>
+      </c>
+      <c r="E668" t="n">
+        <v>1145.1</v>
+      </c>
+      <c r="F668" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G668" t="n">
+        <v>4729.33</v>
+      </c>
+      <c r="H668" t="n">
+        <v>4723.38</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="n">
+        <v>46323.89583333334</v>
+      </c>
+      <c r="B669" t="n">
+        <v>3447.18</v>
+      </c>
+      <c r="C669" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="D669" t="n">
+        <v>0</v>
+      </c>
+      <c r="E669" t="n">
+        <v>1163.49</v>
+      </c>
+      <c r="F669" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="G669" t="n">
+        <v>4637.52</v>
+      </c>
+      <c r="H669" t="n">
+        <v>4615.7</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="n">
+        <v>46323.91666666666</v>
+      </c>
+      <c r="B670" t="n">
+        <v>3310.22</v>
+      </c>
+      <c r="C670" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D670" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="E670" t="n">
+        <v>1168.87</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0</v>
+      </c>
+      <c r="G670" t="n">
+        <v>4498.719999999999</v>
+      </c>
+      <c r="H670" t="n">
+        <v>4498.719999999999</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="n">
+        <v>46323.9375</v>
+      </c>
+      <c r="B671" t="n">
+        <v>3164.25</v>
+      </c>
+      <c r="C671" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="D671" t="n">
+        <v>0</v>
+      </c>
+      <c r="E671" t="n">
+        <v>1157.77</v>
+      </c>
+      <c r="F671" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="G671" t="n">
+        <v>4334.78</v>
+      </c>
+      <c r="H671" t="n">
+        <v>4327.67</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="n">
+        <v>46323.95833333334</v>
+      </c>
+      <c r="B672" t="n">
+        <v>3012.34</v>
+      </c>
+      <c r="C672" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="D672" t="n">
+        <v>0</v>
+      </c>
+      <c r="E672" t="n">
+        <v>1159.83</v>
+      </c>
+      <c r="F672" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="G672" t="n">
+        <v>4185.37</v>
+      </c>
+      <c r="H672" t="n">
+        <v>4177.73</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="n">
+        <v>46323.97916666666</v>
+      </c>
+      <c r="B673" t="n">
+        <v>2857.14</v>
+      </c>
+      <c r="C673" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="D673" t="n">
+        <v>0</v>
+      </c>
+      <c r="E673" t="n">
+        <v>1154.32</v>
+      </c>
+      <c r="F673" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G673" t="n">
+        <v>4019.18</v>
+      </c>
+      <c r="H673" t="n">
+        <v>4017.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -22023,16 +22023,16 @@
         <v>0</v>
       </c>
       <c r="E626" t="n">
-        <v>1129.83</v>
+        <v>1081.4</v>
       </c>
       <c r="F626" t="n">
         <v>25.77</v>
       </c>
       <c r="G626" t="n">
-        <v>3905.63</v>
+        <v>3857.2</v>
       </c>
       <c r="H626" t="n">
-        <v>3879.86</v>
+        <v>3831.43</v>
       </c>
     </row>
     <row r="627">
@@ -22049,16 +22049,16 @@
         <v>0</v>
       </c>
       <c r="E627" t="n">
-        <v>1095.71</v>
+        <v>1052.93</v>
       </c>
       <c r="F627" t="n">
         <v>14.05</v>
       </c>
       <c r="G627" t="n">
-        <v>3736.67</v>
+        <v>3693.89</v>
       </c>
       <c r="H627" t="n">
-        <v>3722.62</v>
+        <v>3679.84</v>
       </c>
     </row>
     <row r="628">
@@ -22075,16 +22075,16 @@
         <v>0</v>
       </c>
       <c r="E628" t="n">
-        <v>1087.65</v>
+        <v>1046.72</v>
       </c>
       <c r="F628" t="n">
         <v>12.79</v>
       </c>
       <c r="G628" t="n">
-        <v>3623.42</v>
+        <v>3582.49</v>
       </c>
       <c r="H628" t="n">
-        <v>3610.63</v>
+        <v>3569.7</v>
       </c>
     </row>
     <row r="629">
@@ -22101,16 +22101,16 @@
         <v>0</v>
       </c>
       <c r="E629" t="n">
-        <v>1020.75</v>
+        <v>980.45</v>
       </c>
       <c r="F629" t="n">
         <v>0</v>
       </c>
       <c r="G629" t="n">
-        <v>3517.34</v>
+        <v>3477.04</v>
       </c>
       <c r="H629" t="n">
-        <v>3517.34</v>
+        <v>3477.04</v>
       </c>
     </row>
     <row r="630">
@@ -22127,16 +22127,16 @@
         <v>1.76</v>
       </c>
       <c r="E630" t="n">
-        <v>1030.71</v>
+        <v>987.62</v>
       </c>
       <c r="F630" t="n">
         <v>0</v>
       </c>
       <c r="G630" t="n">
-        <v>3457.84</v>
+        <v>3414.75</v>
       </c>
       <c r="H630" t="n">
-        <v>3457.84</v>
+        <v>3414.75</v>
       </c>
     </row>
     <row r="631">
@@ -22153,16 +22153,16 @@
         <v>19.05</v>
       </c>
       <c r="E631" t="n">
-        <v>1059.02</v>
+        <v>1010.63</v>
       </c>
       <c r="F631" t="n">
         <v>0</v>
       </c>
       <c r="G631" t="n">
-        <v>3372.19</v>
+        <v>3323.8</v>
       </c>
       <c r="H631" t="n">
-        <v>3372.19</v>
+        <v>3323.8</v>
       </c>
     </row>
     <row r="632">
@@ -22179,16 +22179,16 @@
         <v>0</v>
       </c>
       <c r="E632" t="n">
-        <v>1053.48</v>
+        <v>1004.91</v>
       </c>
       <c r="F632" t="n">
         <v>2.42</v>
       </c>
       <c r="G632" t="n">
-        <v>3320.87</v>
+        <v>3272.3</v>
       </c>
       <c r="H632" t="n">
-        <v>3318.45</v>
+        <v>3269.88</v>
       </c>
     </row>
     <row r="633">
@@ -22205,16 +22205,16 @@
         <v>2.14</v>
       </c>
       <c r="E633" t="n">
-        <v>1053.32</v>
+        <v>1004.9</v>
       </c>
       <c r="F633" t="n">
         <v>0</v>
       </c>
       <c r="G633" t="n">
-        <v>3274.74</v>
+        <v>3226.32</v>
       </c>
       <c r="H633" t="n">
-        <v>3274.74</v>
+        <v>3226.32</v>
       </c>
     </row>
     <row r="634">
@@ -22231,16 +22231,16 @@
         <v>7.61</v>
       </c>
       <c r="E634" t="n">
-        <v>1068.22</v>
+        <v>1019.66</v>
       </c>
       <c r="F634" t="n">
         <v>0</v>
       </c>
       <c r="G634" t="n">
-        <v>3239.09</v>
+        <v>3190.53</v>
       </c>
       <c r="H634" t="n">
-        <v>3239.09</v>
+        <v>3190.53</v>
       </c>
     </row>
     <row r="635">
@@ -22257,16 +22257,16 @@
         <v>14.08</v>
       </c>
       <c r="E635" t="n">
-        <v>1071.43</v>
+        <v>1022.86</v>
       </c>
       <c r="F635" t="n">
         <v>0</v>
       </c>
       <c r="G635" t="n">
-        <v>3235.18</v>
+        <v>3186.61</v>
       </c>
       <c r="H635" t="n">
-        <v>3235.18</v>
+        <v>3186.61</v>
       </c>
     </row>
     <row r="636">
@@ -22283,16 +22283,16 @@
         <v>3.22</v>
       </c>
       <c r="E636" t="n">
-        <v>1065.89</v>
+        <v>1017.42</v>
       </c>
       <c r="F636" t="n">
         <v>0</v>
       </c>
       <c r="G636" t="n">
-        <v>3259.08</v>
+        <v>3210.61</v>
       </c>
       <c r="H636" t="n">
-        <v>3259.08</v>
+        <v>3210.61</v>
       </c>
     </row>
     <row r="637">
@@ -22309,16 +22309,16 @@
         <v>3.51</v>
       </c>
       <c r="E637" t="n">
-        <v>1071.67</v>
+        <v>1023.14</v>
       </c>
       <c r="F637" t="n">
         <v>0</v>
       </c>
       <c r="G637" t="n">
-        <v>3341.15</v>
+        <v>3292.62</v>
       </c>
       <c r="H637" t="n">
-        <v>3341.15</v>
+        <v>3292.62</v>
       </c>
     </row>
     <row r="638">
@@ -22335,16 +22335,16 @@
         <v>0</v>
       </c>
       <c r="E638" t="n">
-        <v>1084.33</v>
+        <v>1035.68</v>
       </c>
       <c r="F638" t="n">
         <v>29.33</v>
       </c>
       <c r="G638" t="n">
-        <v>3368.54</v>
+        <v>3319.89</v>
       </c>
       <c r="H638" t="n">
-        <v>3339.21</v>
+        <v>3290.56</v>
       </c>
     </row>
     <row r="639">
@@ -22361,16 +22361,16 @@
         <v>0</v>
       </c>
       <c r="E639" t="n">
-        <v>1091.5</v>
+        <v>1042.97</v>
       </c>
       <c r="F639" t="n">
         <v>0</v>
       </c>
       <c r="G639" t="n">
-        <v>3187.83</v>
+        <v>3139.3</v>
       </c>
       <c r="H639" t="n">
-        <v>3187.83</v>
+        <v>3139.3</v>
       </c>
     </row>
     <row r="640">
@@ -22387,16 +22387,16 @@
         <v>13.45</v>
       </c>
       <c r="E640" t="n">
-        <v>1086.19</v>
+        <v>1037.57</v>
       </c>
       <c r="F640" t="n">
         <v>0</v>
       </c>
       <c r="G640" t="n">
-        <v>3145.92</v>
+        <v>3097.3</v>
       </c>
       <c r="H640" t="n">
-        <v>3145.92</v>
+        <v>3097.3</v>
       </c>
     </row>
     <row r="641">
@@ -22413,16 +22413,16 @@
         <v>9.779999999999999</v>
       </c>
       <c r="E641" t="n">
-        <v>1083.05</v>
+        <v>1034.63</v>
       </c>
       <c r="F641" t="n">
         <v>0</v>
       </c>
       <c r="G641" t="n">
-        <v>3256.25</v>
+        <v>3207.83</v>
       </c>
       <c r="H641" t="n">
-        <v>3256.25</v>
+        <v>3207.83</v>
       </c>
     </row>
     <row r="642">
@@ -22439,16 +22439,16 @@
         <v>12.39</v>
       </c>
       <c r="E642" t="n">
-        <v>1083.21</v>
+        <v>1034.71</v>
       </c>
       <c r="F642" t="n">
         <v>0</v>
       </c>
       <c r="G642" t="n">
-        <v>3370.84</v>
+        <v>3322.34</v>
       </c>
       <c r="H642" t="n">
-        <v>3370.84</v>
+        <v>3322.34</v>
       </c>
     </row>
     <row r="643">
@@ -22465,16 +22465,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="E643" t="n">
-        <v>1082.52</v>
+        <v>1033.98</v>
       </c>
       <c r="F643" t="n">
         <v>0</v>
       </c>
       <c r="G643" t="n">
-        <v>3522.04</v>
+        <v>3473.5</v>
       </c>
       <c r="H643" t="n">
-        <v>3522.04</v>
+        <v>3473.5</v>
       </c>
     </row>
     <row r="644">
@@ -22491,16 +22491,16 @@
         <v>6.56</v>
       </c>
       <c r="E644" t="n">
-        <v>1084.56</v>
+        <v>1035.94</v>
       </c>
       <c r="F644" t="n">
         <v>0</v>
       </c>
       <c r="G644" t="n">
-        <v>3634.68</v>
+        <v>3586.06</v>
       </c>
       <c r="H644" t="n">
-        <v>3634.68</v>
+        <v>3586.06</v>
       </c>
     </row>
     <row r="645">
@@ -22517,16 +22517,16 @@
         <v>1.77</v>
       </c>
       <c r="E645" t="n">
-        <v>1083.49</v>
+        <v>1034.61</v>
       </c>
       <c r="F645" t="n">
         <v>0</v>
       </c>
       <c r="G645" t="n">
-        <v>3756.06</v>
+        <v>3707.18</v>
       </c>
       <c r="H645" t="n">
-        <v>3756.06</v>
+        <v>3707.18</v>
       </c>
     </row>
     <row r="646">
@@ -22543,16 +22543,16 @@
         <v>0</v>
       </c>
       <c r="E646" t="n">
-        <v>1086.26</v>
+        <v>1037.79</v>
       </c>
       <c r="F646" t="n">
         <v>33.09</v>
       </c>
       <c r="G646" t="n">
-        <v>3890.52</v>
+        <v>3842.05</v>
       </c>
       <c r="H646" t="n">
-        <v>3857.429999999999</v>
+        <v>3808.96</v>
       </c>
     </row>
     <row r="647">
@@ -22569,16 +22569,16 @@
         <v>10.77</v>
       </c>
       <c r="E647" t="n">
-        <v>1086.46</v>
+        <v>1036.72</v>
       </c>
       <c r="F647" t="n">
         <v>0</v>
       </c>
       <c r="G647" t="n">
-        <v>3975.32</v>
+        <v>3925.58</v>
       </c>
       <c r="H647" t="n">
-        <v>3975.32</v>
+        <v>3925.58</v>
       </c>
     </row>
     <row r="648">
@@ -22595,16 +22595,16 @@
         <v>4.17</v>
       </c>
       <c r="E648" t="n">
-        <v>1079.4</v>
+        <v>1029.13</v>
       </c>
       <c r="F648" t="n">
         <v>0</v>
       </c>
       <c r="G648" t="n">
-        <v>4057.83</v>
+        <v>4007.56</v>
       </c>
       <c r="H648" t="n">
-        <v>4057.83</v>
+        <v>4007.56</v>
       </c>
     </row>
     <row r="649">
@@ -22621,16 +22621,16 @@
         <v>0</v>
       </c>
       <c r="E649" t="n">
-        <v>1073.39</v>
+        <v>1023.4</v>
       </c>
       <c r="F649" t="n">
         <v>27.57</v>
       </c>
       <c r="G649" t="n">
-        <v>4139.54</v>
+        <v>4089.55</v>
       </c>
       <c r="H649" t="n">
-        <v>4111.97</v>
+        <v>4061.98</v>
       </c>
     </row>
     <row r="650">
@@ -22647,16 +22647,16 @@
         <v>0</v>
       </c>
       <c r="E650" t="n">
-        <v>1082</v>
+        <v>1031</v>
       </c>
       <c r="F650" t="n">
         <v>2.16</v>
       </c>
       <c r="G650" t="n">
-        <v>4202.860000000001</v>
+        <v>4151.860000000001</v>
       </c>
       <c r="H650" t="n">
-        <v>4200.700000000001</v>
+        <v>4149.700000000001</v>
       </c>
     </row>
     <row r="651">
@@ -22673,16 +22673,16 @@
         <v>0</v>
       </c>
       <c r="E651" t="n">
-        <v>1074.26</v>
+        <v>1023.61</v>
       </c>
       <c r="F651" t="n">
         <v>0</v>
       </c>
       <c r="G651" t="n">
-        <v>4216.43</v>
+        <v>4165.78</v>
       </c>
       <c r="H651" t="n">
-        <v>4216.43</v>
+        <v>4165.78</v>
       </c>
     </row>
     <row r="652">
@@ -22699,16 +22699,16 @@
         <v>5.59</v>
       </c>
       <c r="E652" t="n">
-        <v>1065.93</v>
+        <v>1015.45</v>
       </c>
       <c r="F652" t="n">
         <v>0</v>
       </c>
       <c r="G652" t="n">
-        <v>4255.48</v>
+        <v>4205</v>
       </c>
       <c r="H652" t="n">
-        <v>4255.48</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="653">
@@ -22725,16 +22725,16 @@
         <v>0</v>
       </c>
       <c r="E653" t="n">
-        <v>1063.22</v>
+        <v>1013.95</v>
       </c>
       <c r="F653" t="n">
         <v>0</v>
       </c>
       <c r="G653" t="n">
-        <v>4338.13</v>
+        <v>4288.860000000001</v>
       </c>
       <c r="H653" t="n">
-        <v>4338.13</v>
+        <v>4288.860000000001</v>
       </c>
     </row>
     <row r="654">
@@ -22751,16 +22751,16 @@
         <v>0</v>
       </c>
       <c r="E654" t="n">
-        <v>1092.42</v>
+        <v>1043.17</v>
       </c>
       <c r="F654" t="n">
         <v>0</v>
       </c>
       <c r="G654" t="n">
-        <v>4397.24</v>
+        <v>4347.99</v>
       </c>
       <c r="H654" t="n">
-        <v>4397.24</v>
+        <v>4347.99</v>
       </c>
     </row>
     <row r="655">
@@ -22777,16 +22777,16 @@
         <v>3.85</v>
       </c>
       <c r="E655" t="n">
-        <v>1088.86</v>
+        <v>1039.45</v>
       </c>
       <c r="F655" t="n">
         <v>0</v>
       </c>
       <c r="G655" t="n">
-        <v>4464.549999999999</v>
+        <v>4415.139999999999</v>
       </c>
       <c r="H655" t="n">
-        <v>4464.549999999999</v>
+        <v>4415.139999999999</v>
       </c>
     </row>
     <row r="656">
@@ -22803,16 +22803,16 @@
         <v>0</v>
       </c>
       <c r="E656" t="n">
-        <v>1075.99</v>
+        <v>1026.93</v>
       </c>
       <c r="F656" t="n">
         <v>0</v>
       </c>
       <c r="G656" t="n">
-        <v>4490.6</v>
+        <v>4441.54</v>
       </c>
       <c r="H656" t="n">
-        <v>4490.6</v>
+        <v>4441.54</v>
       </c>
     </row>
     <row r="657">
@@ -22829,16 +22829,16 @@
         <v>0</v>
       </c>
       <c r="E657" t="n">
-        <v>1082.1</v>
+        <v>1033</v>
       </c>
       <c r="F657" t="n">
         <v>12.39</v>
       </c>
       <c r="G657" t="n">
-        <v>4519.64</v>
+        <v>4470.54</v>
       </c>
       <c r="H657" t="n">
-        <v>4507.25</v>
+        <v>4458.15</v>
       </c>
     </row>
     <row r="658">
@@ -22855,16 +22855,16 @@
         <v>0</v>
       </c>
       <c r="E658" t="n">
-        <v>1099.9</v>
+        <v>1050.71</v>
       </c>
       <c r="F658" t="n">
         <v>0</v>
       </c>
       <c r="G658" t="n">
-        <v>4496.860000000001</v>
+        <v>4447.67</v>
       </c>
       <c r="H658" t="n">
-        <v>4496.860000000001</v>
+        <v>4447.67</v>
       </c>
     </row>
     <row r="659">
@@ -22881,16 +22881,16 @@
         <v>0</v>
       </c>
       <c r="E659" t="n">
-        <v>1101.93</v>
+        <v>1052.76</v>
       </c>
       <c r="F659" t="n">
         <v>5.7</v>
       </c>
       <c r="G659" t="n">
-        <v>4484.67</v>
+        <v>4435.5</v>
       </c>
       <c r="H659" t="n">
-        <v>4478.97</v>
+        <v>4429.8</v>
       </c>
     </row>
     <row r="660">
@@ -22907,16 +22907,16 @@
         <v>14.07</v>
       </c>
       <c r="E660" t="n">
-        <v>1105.26</v>
+        <v>1055.02</v>
       </c>
       <c r="F660" t="n">
         <v>0</v>
       </c>
       <c r="G660" t="n">
-        <v>4381.29</v>
+        <v>4331.05</v>
       </c>
       <c r="H660" t="n">
-        <v>4381.29</v>
+        <v>4331.05</v>
       </c>
     </row>
     <row r="661">
@@ -22933,16 +22933,16 @@
         <v>19.61</v>
       </c>
       <c r="E661" t="n">
-        <v>1116.45</v>
+        <v>1064.89</v>
       </c>
       <c r="F661" t="n">
         <v>0</v>
       </c>
       <c r="G661" t="n">
-        <v>4313.6</v>
+        <v>4262.04</v>
       </c>
       <c r="H661" t="n">
-        <v>4313.6</v>
+        <v>4262.04</v>
       </c>
     </row>
     <row r="662">
@@ -22959,16 +22959,16 @@
         <v>2.02</v>
       </c>
       <c r="E662" t="n">
-        <v>1114.97</v>
+        <v>1063.3</v>
       </c>
       <c r="F662" t="n">
         <v>0</v>
       </c>
       <c r="G662" t="n">
-        <v>4409.76</v>
+        <v>4358.09</v>
       </c>
       <c r="H662" t="n">
-        <v>4409.76</v>
+        <v>4358.09</v>
       </c>
     </row>
     <row r="663">
@@ -22985,16 +22985,16 @@
         <v>20.12</v>
       </c>
       <c r="E663" t="n">
-        <v>1115.5</v>
+        <v>1063.85</v>
       </c>
       <c r="F663" t="n">
         <v>0</v>
       </c>
       <c r="G663" t="n">
-        <v>4742.690000000001</v>
+        <v>4691.04</v>
       </c>
       <c r="H663" t="n">
-        <v>4742.690000000001</v>
+        <v>4691.04</v>
       </c>
     </row>
     <row r="664">
@@ -23011,16 +23011,16 @@
         <v>17.12</v>
       </c>
       <c r="E664" t="n">
-        <v>1099.36</v>
+        <v>1047.79</v>
       </c>
       <c r="F664" t="n">
         <v>0</v>
       </c>
       <c r="G664" t="n">
-        <v>4821.67</v>
+        <v>4770.1</v>
       </c>
       <c r="H664" t="n">
-        <v>4821.67</v>
+        <v>4770.1</v>
       </c>
     </row>
     <row r="665">
@@ -23037,16 +23037,16 @@
         <v>3.29</v>
       </c>
       <c r="E665" t="n">
-        <v>1099.66</v>
+        <v>1047.94</v>
       </c>
       <c r="F665" t="n">
         <v>0</v>
       </c>
       <c r="G665" t="n">
-        <v>4842.22</v>
+        <v>4790.5</v>
       </c>
       <c r="H665" t="n">
-        <v>4842.22</v>
+        <v>4790.5</v>
       </c>
     </row>
     <row r="666">
@@ -23063,16 +23063,16 @@
         <v>0</v>
       </c>
       <c r="E666" t="n">
-        <v>1104.18</v>
+        <v>1052.54</v>
       </c>
       <c r="F666" t="n">
         <v>0</v>
       </c>
       <c r="G666" t="n">
-        <v>4824.85</v>
+        <v>4773.21</v>
       </c>
       <c r="H666" t="n">
-        <v>4824.85</v>
+        <v>4773.21</v>
       </c>
     </row>
     <row r="667">
@@ -23089,16 +23089,16 @@
         <v>0</v>
       </c>
       <c r="E667" t="n">
-        <v>1126.89</v>
+        <v>1075.28</v>
       </c>
       <c r="F667" t="n">
         <v>4.32</v>
       </c>
       <c r="G667" t="n">
-        <v>4795.12</v>
+        <v>4743.509999999999</v>
       </c>
       <c r="H667" t="n">
-        <v>4790.8</v>
+        <v>4739.19</v>
       </c>
     </row>
     <row r="668">
@@ -23115,16 +23115,16 @@
         <v>0</v>
       </c>
       <c r="E668" t="n">
-        <v>1145.1</v>
+        <v>1093.36</v>
       </c>
       <c r="F668" t="n">
         <v>5.95</v>
       </c>
       <c r="G668" t="n">
-        <v>4729.33</v>
+        <v>4677.59</v>
       </c>
       <c r="H668" t="n">
-        <v>4723.38</v>
+        <v>4671.64</v>
       </c>
     </row>
     <row r="669">
@@ -23141,16 +23141,16 @@
         <v>0</v>
       </c>
       <c r="E669" t="n">
-        <v>1163.49</v>
+        <v>1111.96</v>
       </c>
       <c r="F669" t="n">
         <v>21.82</v>
       </c>
       <c r="G669" t="n">
-        <v>4637.52</v>
+        <v>4585.99</v>
       </c>
       <c r="H669" t="n">
-        <v>4615.7</v>
+        <v>4564.17</v>
       </c>
     </row>
     <row r="670">
@@ -23167,16 +23167,16 @@
         <v>14.23</v>
       </c>
       <c r="E670" t="n">
-        <v>1168.87</v>
+        <v>1117.33</v>
       </c>
       <c r="F670" t="n">
         <v>0</v>
       </c>
       <c r="G670" t="n">
-        <v>4498.719999999999</v>
+        <v>4447.18</v>
       </c>
       <c r="H670" t="n">
-        <v>4498.719999999999</v>
+        <v>4447.18</v>
       </c>
     </row>
     <row r="671">
@@ -23193,16 +23193,16 @@
         <v>0</v>
       </c>
       <c r="E671" t="n">
-        <v>1157.77</v>
+        <v>1106.13</v>
       </c>
       <c r="F671" t="n">
         <v>7.11</v>
       </c>
       <c r="G671" t="n">
-        <v>4334.78</v>
+        <v>4283.14</v>
       </c>
       <c r="H671" t="n">
-        <v>4327.67</v>
+        <v>4276.030000000001</v>
       </c>
     </row>
     <row r="672">
@@ -23219,16 +23219,16 @@
         <v>0</v>
       </c>
       <c r="E672" t="n">
-        <v>1159.83</v>
+        <v>1108.12</v>
       </c>
       <c r="F672" t="n">
         <v>7.64</v>
       </c>
       <c r="G672" t="n">
-        <v>4185.37</v>
+        <v>4133.660000000001</v>
       </c>
       <c r="H672" t="n">
-        <v>4177.73</v>
+        <v>4126.02</v>
       </c>
     </row>
     <row r="673">
@@ -23245,16 +23245,16 @@
         <v>0</v>
       </c>
       <c r="E673" t="n">
-        <v>1154.32</v>
+        <v>1103</v>
       </c>
       <c r="F673" t="n">
         <v>2.15</v>
       </c>
       <c r="G673" t="n">
-        <v>4019.18</v>
+        <v>3967.86</v>
       </c>
       <c r="H673" t="n">
-        <v>4017.03</v>
+        <v>3965.71</v>
       </c>
     </row>
   </sheetData>

--- a/south_america/ecuador_generation.xlsx
+++ b/south_america/ecuador_generation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,6 +1349,59 @@
         <v>0.005</v>
       </c>
       <c r="Q15" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97881</v>
+      </c>
+      <c r="C16" t="n">
+        <v>69904</v>
+      </c>
+      <c r="D16" t="n">
+        <v>27466</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25013</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2453</v>
+      </c>
+      <c r="G16" t="n">
+        <v>451</v>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>95</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.078</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.913</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -1363,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1379,32 +1432,32 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Coca Codo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Paute</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Coca Codo</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Minas San Francisco</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delsitanisagua</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Sopladora</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Delsitanisagua</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -1426,22 +1479,22 @@
         <v>16882</v>
       </c>
       <c r="C2" t="n">
+        <v>24721</v>
+      </c>
+      <c r="D2" t="n">
         <v>13964</v>
       </c>
-      <c r="D2" t="n">
-        <v>24721</v>
-      </c>
       <c r="E2" t="n">
+        <v>239</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="H2" t="n">
         <v>8114</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2768</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3724</v>
-      </c>
-      <c r="H2" t="n">
-        <v>239</v>
       </c>
       <c r="I2" t="n">
         <v>2003</v>
@@ -1458,22 +1511,22 @@
         <v>20069</v>
       </c>
       <c r="C3" t="n">
+        <v>23420</v>
+      </c>
+      <c r="D3" t="n">
         <v>16681</v>
       </c>
-      <c r="D3" t="n">
-        <v>23420</v>
-      </c>
       <c r="E3" t="n">
+        <v>1531</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3644</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2477</v>
+      </c>
+      <c r="H3" t="n">
         <v>8424</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2477</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3644</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1531</v>
       </c>
       <c r="I3" t="n">
         <v>1820</v>
@@ -1490,22 +1543,22 @@
         <v>19095</v>
       </c>
       <c r="C4" t="n">
+        <v>19992</v>
+      </c>
+      <c r="D4" t="n">
         <v>17645</v>
       </c>
-      <c r="D4" t="n">
-        <v>19992</v>
-      </c>
       <c r="E4" t="n">
+        <v>306</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3194</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2491</v>
+      </c>
+      <c r="H4" t="n">
         <v>9735</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2491</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3194</v>
-      </c>
-      <c r="H4" t="n">
-        <v>306</v>
       </c>
       <c r="I4" t="n">
         <v>1820</v>
@@ -1522,22 +1575,22 @@
         <v>19098</v>
       </c>
       <c r="C5" t="n">
+        <v>17987</v>
+      </c>
+      <c r="D5" t="n">
         <v>14882</v>
       </c>
-      <c r="D5" t="n">
-        <v>17987</v>
-      </c>
       <c r="E5" t="n">
+        <v>721</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3026</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2773</v>
+      </c>
+      <c r="H5" t="n">
         <v>8469</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2773</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3026</v>
-      </c>
-      <c r="H5" t="n">
-        <v>721</v>
       </c>
       <c r="I5" t="n">
         <v>2009</v>
@@ -1554,22 +1607,22 @@
         <v>20810</v>
       </c>
       <c r="C6" t="n">
+        <v>17990</v>
+      </c>
+      <c r="D6" t="n">
         <v>14644</v>
       </c>
-      <c r="D6" t="n">
-        <v>17990</v>
-      </c>
       <c r="E6" t="n">
+        <v>750</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3345</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2472</v>
+      </c>
+      <c r="H6" t="n">
         <v>8416</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2472</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3345</v>
-      </c>
-      <c r="H6" t="n">
-        <v>750</v>
       </c>
       <c r="I6" t="n">
         <v>1847</v>
@@ -1586,22 +1639,22 @@
         <v>19280</v>
       </c>
       <c r="C7" t="n">
+        <v>22254</v>
+      </c>
+      <c r="D7" t="n">
         <v>10078</v>
       </c>
-      <c r="D7" t="n">
-        <v>22254</v>
-      </c>
       <c r="E7" t="n">
+        <v>461</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2963</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2512</v>
+      </c>
+      <c r="H7" t="n">
         <v>5868</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2512</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2963</v>
-      </c>
-      <c r="H7" t="n">
-        <v>461</v>
       </c>
       <c r="I7" t="n">
         <v>1853</v>
@@ -1618,22 +1671,22 @@
         <v>21755</v>
       </c>
       <c r="C8" t="n">
+        <v>26473</v>
+      </c>
+      <c r="D8" t="n">
         <v>5014</v>
       </c>
-      <c r="D8" t="n">
-        <v>26473</v>
-      </c>
       <c r="E8" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3431</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2854</v>
+      </c>
+      <c r="H8" t="n">
         <v>2907</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2854</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3431</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1105</v>
       </c>
       <c r="I8" t="n">
         <v>2034</v>
@@ -1648,22 +1701,22 @@
         <v>19704</v>
       </c>
       <c r="C9" t="n">
+        <v>23346</v>
+      </c>
+      <c r="D9" t="n">
         <v>14358</v>
       </c>
-      <c r="D9" t="n">
-        <v>23346</v>
-      </c>
       <c r="E9" t="n">
+        <v>1488</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2801</v>
+      </c>
+      <c r="H9" t="n">
         <v>8041</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2801</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2788</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1488</v>
       </c>
       <c r="I9" t="n">
         <v>2027</v>
@@ -1680,22 +1733,22 @@
         <v>18740</v>
       </c>
       <c r="C10" t="n">
+        <v>19157</v>
+      </c>
+      <c r="D10" t="n">
         <v>18959</v>
       </c>
-      <c r="D10" t="n">
-        <v>19157</v>
-      </c>
       <c r="E10" t="n">
+        <v>1870</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2675</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2566</v>
+      </c>
+      <c r="H10" t="n">
         <v>9960</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2566</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2675</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1870</v>
       </c>
       <c r="I10" t="n">
         <v>1907</v>
@@ -1712,22 +1765,22 @@
         <v>19903</v>
       </c>
       <c r="C11" t="n">
+        <v>19048</v>
+      </c>
+      <c r="D11" t="n">
         <v>18347</v>
       </c>
-      <c r="D11" t="n">
-        <v>19048</v>
-      </c>
       <c r="E11" t="n">
+        <v>1693</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2526</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2706</v>
+      </c>
+      <c r="H11" t="n">
         <v>9798</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2706</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2526</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1693</v>
       </c>
       <c r="I11" t="n">
         <v>1966</v>
@@ -1744,22 +1797,22 @@
         <v>20083</v>
       </c>
       <c r="C12" t="n">
+        <v>16518</v>
+      </c>
+      <c r="D12" t="n">
         <v>16208</v>
       </c>
-      <c r="D12" t="n">
-        <v>16518</v>
-      </c>
       <c r="E12" t="n">
+        <v>447</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2565</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2525</v>
+      </c>
+      <c r="H12" t="n">
         <v>9495</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2525</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2565</v>
-      </c>
-      <c r="H12" t="n">
-        <v>447</v>
       </c>
       <c r="I12" t="n">
         <v>1838</v>
@@ -1776,22 +1829,22 @@
         <v>24903</v>
       </c>
       <c r="C13" t="n">
+        <v>21674</v>
+      </c>
+      <c r="D13" t="n">
         <v>6934</v>
       </c>
-      <c r="D13" t="n">
-        <v>21674</v>
-      </c>
       <c r="E13" t="n">
+        <v>1264</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2495</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2823</v>
+      </c>
+      <c r="H13" t="n">
         <v>4088</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2823</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2495</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1264</v>
       </c>
       <c r="I13" t="n">
         <v>1997</v>
@@ -1808,22 +1861,22 @@
         <v>24052</v>
       </c>
       <c r="C14" t="n">
+        <v>20199</v>
+      </c>
+      <c r="D14" t="n">
         <v>11236</v>
       </c>
-      <c r="D14" t="n">
-        <v>20199</v>
-      </c>
       <c r="E14" t="n">
+        <v>2136</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2635</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2554</v>
+      </c>
+      <c r="H14" t="n">
         <v>5881</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2554</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2635</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2136</v>
       </c>
       <c r="I14" t="n">
         <v>1840</v>
@@ -1840,28 +1893,60 @@
         <v>25337</v>
       </c>
       <c r="C15" t="n">
+        <v>8701</v>
+      </c>
+      <c r="D15" t="n">
         <v>13787</v>
       </c>
-      <c r="D15" t="n">
-        <v>8701</v>
-      </c>
       <c r="E15" t="n">
+        <v>2421</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2803</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3013</v>
+      </c>
+      <c r="H15" t="n">
         <v>7818</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3013</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2803</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2421</v>
       </c>
       <c r="I15" t="n">
         <v>2178</v>
       </c>
       <c r="J15" t="n">
         <v>1740</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B16" t="n">
+        <v>25844</v>
+      </c>
+      <c r="C16" t="n">
+        <v>20296</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5424</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4856</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4104</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3115</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3047</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2270</v>
+      </c>
+      <c r="J16" t="n">
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -1875,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2293,21 +2378,17 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46291</v>
+        <v>46324</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paute</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Azuay</t>
-        </is>
-      </c>
+          <t>Otras Hidro</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Nacional (agregado)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2316,7 +2397,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>13964</v>
+        <v>25844</v>
       </c>
     </row>
     <row r="17">
@@ -2324,21 +2405,21 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2347,7 +2428,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>16681</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="18">
@@ -2355,21 +2436,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2378,7 +2459,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>17645</v>
+        <v>23420</v>
       </c>
     </row>
     <row r="19">
@@ -2386,21 +2467,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2409,7 +2490,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>14882</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="20">
@@ -2417,21 +2498,21 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2440,7 +2521,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>14644</v>
+        <v>17987</v>
       </c>
     </row>
     <row r="21">
@@ -2448,21 +2529,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2471,7 +2552,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>10078</v>
+        <v>17990</v>
       </c>
     </row>
     <row r="22">
@@ -2479,21 +2560,21 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2502,7 +2583,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5014</v>
+        <v>22254</v>
       </c>
     </row>
     <row r="23">
@@ -2510,21 +2591,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2533,7 +2614,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>14358</v>
+        <v>26473</v>
       </c>
     </row>
     <row r="24">
@@ -2541,21 +2622,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2564,7 +2645,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>18959</v>
+        <v>23346</v>
       </c>
     </row>
     <row r="25">
@@ -2572,21 +2653,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2595,7 +2676,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>18347</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="26">
@@ -2603,21 +2684,21 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46305</v>
+        <v>46302</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2626,7 +2707,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>16208</v>
+        <v>19048</v>
       </c>
     </row>
     <row r="27">
@@ -2634,21 +2715,21 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46321</v>
+        <v>46305</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2657,7 +2738,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6934</v>
+        <v>16518</v>
       </c>
     </row>
     <row r="28">
@@ -2665,21 +2746,21 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2688,7 +2769,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>11236</v>
+        <v>21674</v>
       </c>
     </row>
     <row r="29">
@@ -2696,21 +2777,21 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Paute</t>
+          <t>Coca Codo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Napo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2719,7 +2800,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>13787</v>
+        <v>20199</v>
       </c>
     </row>
     <row r="30">
@@ -2727,7 +2808,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46291</v>
+        <v>46323</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2750,7 +2831,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>24721</v>
+        <v>8701</v>
       </c>
     </row>
     <row r="31">
@@ -2758,7 +2839,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46293</v>
+        <v>46324</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2781,7 +2862,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>23420</v>
+        <v>20296</v>
       </c>
     </row>
     <row r="32">
@@ -2789,21 +2870,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2812,7 +2893,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>19992</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="33">
@@ -2820,21 +2901,21 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2843,7 +2924,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>17987</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="34">
@@ -2851,21 +2932,21 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2874,7 +2955,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>17990</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="35">
@@ -2882,21 +2963,21 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2905,7 +2986,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>22254</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="36">
@@ -2913,21 +2994,21 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2936,7 +3017,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>26473</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="37">
@@ -2944,21 +3025,21 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2967,7 +3048,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>23346</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="38">
@@ -2975,21 +3056,21 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2998,7 +3079,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>19157</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="39">
@@ -3006,21 +3087,21 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3029,7 +3110,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>19048</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="40">
@@ -3037,21 +3118,21 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46305</v>
+        <v>46301</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3060,7 +3141,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>16518</v>
+        <v>18959</v>
       </c>
     </row>
     <row r="41">
@@ -3068,21 +3149,21 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46321</v>
+        <v>46302</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3091,7 +3172,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>21674</v>
+        <v>18347</v>
       </c>
     </row>
     <row r="42">
@@ -3099,21 +3180,21 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46322</v>
+        <v>46305</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3122,7 +3203,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>20199</v>
+        <v>16208</v>
       </c>
     </row>
     <row r="43">
@@ -3130,21 +3211,21 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46323</v>
+        <v>46321</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coca Codo</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Napo</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3153,7 +3234,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>8701</v>
+        <v>6934</v>
       </c>
     </row>
     <row r="44">
@@ -3161,11 +3242,11 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46291</v>
+        <v>46322</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3184,7 +3265,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>8114</v>
+        <v>11236</v>
       </c>
     </row>
     <row r="45">
@@ -3192,11 +3273,11 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46293</v>
+        <v>46323</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3215,7 +3296,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>8424</v>
+        <v>13787</v>
       </c>
     </row>
     <row r="46">
@@ -3223,11 +3304,11 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46294</v>
+        <v>46324</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Paute</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3246,7 +3327,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>9735</v>
+        <v>5424</v>
       </c>
     </row>
     <row r="47">
@@ -3254,11 +3335,11 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3277,7 +3358,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>8469</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48">
@@ -3285,11 +3366,11 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3308,7 +3389,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>8416</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="49">
@@ -3316,11 +3397,11 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3339,7 +3420,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>5868</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50">
@@ -3347,11 +3428,11 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3370,7 +3451,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2907</v>
+        <v>721</v>
       </c>
     </row>
     <row r="51">
@@ -3378,11 +3459,11 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3401,7 +3482,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>8041</v>
+        <v>750</v>
       </c>
     </row>
     <row r="52">
@@ -3409,11 +3490,11 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3432,7 +3513,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>9960</v>
+        <v>461</v>
       </c>
     </row>
     <row r="53">
@@ -3440,11 +3521,11 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46302</v>
+        <v>46298</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3463,7 +3544,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>9798</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="54">
@@ -3471,11 +3552,11 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3494,7 +3575,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>9495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="55">
@@ -3502,11 +3583,11 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46321</v>
+        <v>46301</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3525,7 +3606,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>4088</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="56">
@@ -3533,11 +3614,11 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46322</v>
+        <v>46302</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3556,7 +3637,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5881</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="57">
@@ -3564,11 +3645,11 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46323</v>
+        <v>46305</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sopladora</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3587,7 +3668,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>7818</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58">
@@ -3595,16 +3676,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3618,7 +3699,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2768</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="59">
@@ -3626,16 +3707,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46293</v>
+        <v>46322</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3649,7 +3730,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2477</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="60">
@@ -3657,16 +3738,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46294</v>
+        <v>46323</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3680,7 +3761,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2491</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="61">
@@ -3688,16 +3769,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46295</v>
+        <v>46324</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Minas San Francisco</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3711,7 +3792,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2773</v>
+        <v>4856</v>
       </c>
     </row>
     <row r="62">
@@ -3719,21 +3800,21 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3742,7 +3823,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2472</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="63">
@@ -3750,21 +3831,21 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3773,7 +3854,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2512</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="64">
@@ -3781,21 +3862,21 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3804,7 +3885,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2854</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="65">
@@ -3812,21 +3893,21 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3835,7 +3916,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2801</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="66">
@@ -3843,21 +3924,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3866,7 +3947,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2566</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="67">
@@ -3874,21 +3955,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3897,7 +3978,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2706</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="68">
@@ -3905,21 +3986,21 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3928,7 +4009,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2525</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="69">
@@ -3936,21 +4017,21 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46321</v>
+        <v>46300</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3959,7 +4040,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2823</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="70">
@@ -3967,21 +4048,21 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46322</v>
+        <v>46301</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3990,7 +4071,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2554</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="71">
@@ -3998,21 +4079,21 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46323</v>
+        <v>46302</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Delsitanisagua</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Zamora Chinchipe</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Oriente</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4021,7 +4102,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>3013</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="72">
@@ -4029,7 +4110,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4052,7 +4133,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3724</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="73">
@@ -4060,7 +4141,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46293</v>
+        <v>46321</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4083,7 +4164,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>3644</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="74">
@@ -4091,7 +4172,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46294</v>
+        <v>46322</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4114,7 +4195,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3194</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="75">
@@ -4122,7 +4203,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46295</v>
+        <v>46323</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4145,7 +4226,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>3026</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="76">
@@ -4153,7 +4234,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46296</v>
+        <v>46324</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4176,7 +4257,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>3345</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="77">
@@ -4184,21 +4265,21 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4207,7 +4288,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2963</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="78">
@@ -4215,21 +4296,21 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46298</v>
+        <v>46293</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4238,7 +4319,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>3431</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="79">
@@ -4246,21 +4327,21 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46300</v>
+        <v>46294</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4269,7 +4350,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>2788</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="80">
@@ -4277,21 +4358,21 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46301</v>
+        <v>46295</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4300,7 +4381,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2675</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="81">
@@ -4308,21 +4389,21 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4331,7 +4412,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2526</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="82">
@@ -4339,21 +4420,21 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46305</v>
+        <v>46297</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4362,7 +4443,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>2565</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="83">
@@ -4370,21 +4451,21 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46321</v>
+        <v>46298</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4393,7 +4474,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2495</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="84">
@@ -4401,21 +4482,21 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46322</v>
+        <v>46300</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4424,7 +4505,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>2635</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="85">
@@ -4432,21 +4513,21 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46323</v>
+        <v>46301</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Delsitanisagua</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Zamora Chinchipe</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4455,7 +4536,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2803</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="86">
@@ -4463,16 +4544,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46291</v>
+        <v>46302</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4486,7 +4567,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>239</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="87">
@@ -4494,16 +4575,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46293</v>
+        <v>46305</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4517,7 +4598,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1531</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="88">
@@ -4525,16 +4606,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46294</v>
+        <v>46321</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4548,7 +4629,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>306</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="89">
@@ -4556,16 +4637,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46295</v>
+        <v>46322</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4579,7 +4660,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>721</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="90">
@@ -4587,16 +4668,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46296</v>
+        <v>46323</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4610,7 +4691,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>750</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="91">
@@ -4618,16 +4699,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46297</v>
+        <v>46324</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4641,7 +4722,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>461</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="92">
@@ -4649,11 +4730,11 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4672,7 +4753,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1105</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="93">
@@ -4680,11 +4761,11 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4703,7 +4784,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1488</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="94">
@@ -4711,11 +4792,11 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4734,7 +4815,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1870</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="95">
@@ -4742,11 +4823,11 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4765,7 +4846,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1693</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="96">
@@ -4773,11 +4854,11 @@
         <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46305</v>
+        <v>46296</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4796,7 +4877,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>447</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="97">
@@ -4804,11 +4885,11 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46321</v>
+        <v>46297</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4827,7 +4908,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1264</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="98">
@@ -4835,11 +4916,11 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46322</v>
+        <v>46298</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4858,7 +4939,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>2136</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="99">
@@ -4866,11 +4947,11 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46323</v>
+        <v>46300</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Minas San Francisco</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4889,7 +4970,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2421</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="100">
@@ -4897,16 +4978,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46291</v>
+        <v>46301</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4920,7 +5001,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>2003</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="101">
@@ -4928,16 +5009,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4951,7 +5032,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1820</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="102">
@@ -4959,16 +5040,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46294</v>
+        <v>46305</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4982,7 +5063,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1820</v>
+        <v>9495</v>
       </c>
     </row>
     <row r="103">
@@ -4990,16 +5071,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46295</v>
+        <v>46321</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5013,7 +5094,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2009</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="104">
@@ -5021,16 +5102,16 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46296</v>
+        <v>46322</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5044,7 +5125,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1847</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="105">
@@ -5052,16 +5133,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46297</v>
+        <v>46323</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5075,7 +5156,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1853</v>
+        <v>7818</v>
       </c>
     </row>
     <row r="106">
@@ -5083,16 +5164,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46298</v>
+        <v>46324</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Agoyán</t>
+          <t>Sopladora</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tungurahua</t>
+          <t>Azuay</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5106,7 +5187,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2034</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="107">
@@ -5114,7 +5195,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46300</v>
+        <v>46291</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5137,7 +5218,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2027</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="108">
@@ -5145,7 +5226,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5168,7 +5249,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1907</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="109">
@@ -5176,7 +5257,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46302</v>
+        <v>46294</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5199,7 +5280,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1966</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="110">
@@ -5207,7 +5288,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46305</v>
+        <v>46295</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5230,7 +5311,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1838</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="111">
@@ -5238,7 +5319,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46321</v>
+        <v>46296</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5261,7 +5342,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1997</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="112">
@@ -5269,7 +5350,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46322</v>
+        <v>46297</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5292,7 +5373,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1840</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="113">
@@ -5300,7 +5381,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46323</v>
+        <v>46298</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5323,7 +5404,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2178</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="114">
@@ -5331,16 +5412,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5354,7 +5435,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2301</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="115">
@@ -5362,16 +5443,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5385,7 +5466,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>2554</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="116">
@@ -5393,16 +5474,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5416,7 +5497,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>2604</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="117">
@@ -5424,16 +5505,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5447,7 +5528,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>2307</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="118">
@@ -5455,16 +5536,16 @@
         <v>116</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46296</v>
+        <v>46321</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5478,7 +5559,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>3102</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="119">
@@ -5486,16 +5567,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46297</v>
+        <v>46322</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5509,7 +5590,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2187</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="120">
@@ -5517,16 +5598,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46300</v>
+        <v>46323</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5540,7 +5621,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1164</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="121">
@@ -5548,16 +5629,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46301</v>
+        <v>46324</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Mazar</t>
+          <t>Agoyán</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Azuay</t>
+          <t>Tungurahua</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5571,7 +5652,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2157</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="122">
@@ -5579,7 +5660,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46302</v>
+        <v>46291</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5602,7 +5683,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>2831</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="123">
@@ -5610,7 +5691,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46305</v>
+        <v>46293</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -5633,7 +5714,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2551</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="124">
@@ -5641,7 +5722,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46321</v>
+        <v>46294</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -5664,7 +5745,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1358</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="125">
@@ -5672,7 +5753,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46322</v>
+        <v>46295</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -5695,7 +5776,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1408</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="126">
@@ -5703,30 +5784,309 @@
         <v>124</v>
       </c>
       <c r="B126" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2" t="n">
         <v>46323</v>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Mazar</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>Azuay</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>Sierra</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="G126" t="n">
+      <c r="G134" t="n">
         <v>1740</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Mazar</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -5740,7 +6100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H673"/>
+  <dimension ref="A1:H721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23257,6 +23617,1254 @@
         <v>3965.71</v>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B674" t="n">
+        <v>2703.86</v>
+      </c>
+      <c r="C674" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="D674" t="n">
+        <v>0</v>
+      </c>
+      <c r="E674" t="n">
+        <v>1158.19</v>
+      </c>
+      <c r="F674" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G674" t="n">
+        <v>3883.28</v>
+      </c>
+      <c r="H674" t="n">
+        <v>3875.48</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="n">
+        <v>46324.02083333334</v>
+      </c>
+      <c r="B675" t="n">
+        <v>2751.67</v>
+      </c>
+      <c r="C675" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="D675" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E675" t="n">
+        <v>1124.82</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0</v>
+      </c>
+      <c r="G675" t="n">
+        <v>3884.28</v>
+      </c>
+      <c r="H675" t="n">
+        <v>3884.28</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="n">
+        <v>46324.04166666666</v>
+      </c>
+      <c r="B676" t="n">
+        <v>2660.76</v>
+      </c>
+      <c r="C676" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="D676" t="n">
+        <v>0</v>
+      </c>
+      <c r="E676" t="n">
+        <v>1125.63</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0</v>
+      </c>
+      <c r="G676" t="n">
+        <v>3791.95</v>
+      </c>
+      <c r="H676" t="n">
+        <v>3791.95</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="n">
+        <v>46324.0625</v>
+      </c>
+      <c r="B677" t="n">
+        <v>2577.61</v>
+      </c>
+      <c r="C677" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D677" t="n">
+        <v>0</v>
+      </c>
+      <c r="E677" t="n">
+        <v>1131.27</v>
+      </c>
+      <c r="F677" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G677" t="n">
+        <v>3716.64</v>
+      </c>
+      <c r="H677" t="n">
+        <v>3714.78</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="n">
+        <v>46324.08333333334</v>
+      </c>
+      <c r="B678" t="n">
+        <v>2494.45</v>
+      </c>
+      <c r="C678" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="D678" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E678" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F678" t="n">
+        <v>0</v>
+      </c>
+      <c r="G678" t="n">
+        <v>3649.09</v>
+      </c>
+      <c r="H678" t="n">
+        <v>3649.09</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="n">
+        <v>46324.10416666666</v>
+      </c>
+      <c r="B679" t="n">
+        <v>2428.28</v>
+      </c>
+      <c r="C679" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D679" t="n">
+        <v>0</v>
+      </c>
+      <c r="E679" t="n">
+        <v>1137.1</v>
+      </c>
+      <c r="F679" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G679" t="n">
+        <v>3582.78</v>
+      </c>
+      <c r="H679" t="n">
+        <v>3575.68</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n">
+        <v>46324.125</v>
+      </c>
+      <c r="B680" t="n">
+        <v>2380.07</v>
+      </c>
+      <c r="C680" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="D680" t="n">
+        <v>0</v>
+      </c>
+      <c r="E680" t="n">
+        <v>1147.52</v>
+      </c>
+      <c r="F680" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="G680" t="n">
+        <v>3544.76</v>
+      </c>
+      <c r="H680" t="n">
+        <v>3534.45</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="n">
+        <v>46324.14583333334</v>
+      </c>
+      <c r="B681" t="n">
+        <v>2361.19</v>
+      </c>
+      <c r="C681" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D681" t="n">
+        <v>0</v>
+      </c>
+      <c r="E681" t="n">
+        <v>1136.01</v>
+      </c>
+      <c r="F681" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G681" t="n">
+        <v>3507.29</v>
+      </c>
+      <c r="H681" t="n">
+        <v>3504.1</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="n">
+        <v>46324.16666666666</v>
+      </c>
+      <c r="B682" t="n">
+        <v>2314.68</v>
+      </c>
+      <c r="C682" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D682" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="E682" t="n">
+        <v>1140.02</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0</v>
+      </c>
+      <c r="G682" t="n">
+        <v>3480.01</v>
+      </c>
+      <c r="H682" t="n">
+        <v>3480.01</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="n">
+        <v>46324.1875</v>
+      </c>
+      <c r="B683" t="n">
+        <v>2330.66</v>
+      </c>
+      <c r="C683" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="D683" t="n">
+        <v>0</v>
+      </c>
+      <c r="E683" t="n">
+        <v>1138.23</v>
+      </c>
+      <c r="F683" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G683" t="n">
+        <v>3478.41</v>
+      </c>
+      <c r="H683" t="n">
+        <v>3476.6</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="n">
+        <v>46324.20833333334</v>
+      </c>
+      <c r="B684" t="n">
+        <v>2341.29</v>
+      </c>
+      <c r="C684" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="D684" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E684" t="n">
+        <v>1130.71</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0</v>
+      </c>
+      <c r="G684" t="n">
+        <v>3498.21</v>
+      </c>
+      <c r="H684" t="n">
+        <v>3498.21</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="n">
+        <v>46324.22916666666</v>
+      </c>
+      <c r="B685" t="n">
+        <v>2411.01</v>
+      </c>
+      <c r="C685" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D685" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="E685" t="n">
+        <v>1154</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0</v>
+      </c>
+      <c r="G685" t="n">
+        <v>3586.12</v>
+      </c>
+      <c r="H685" t="n">
+        <v>3586.12</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="n">
+        <v>46324.25</v>
+      </c>
+      <c r="B686" t="n">
+        <v>2435.61</v>
+      </c>
+      <c r="C686" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D686" t="n">
+        <v>0</v>
+      </c>
+      <c r="E686" t="n">
+        <v>1135.81</v>
+      </c>
+      <c r="F686" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="G686" t="n">
+        <v>3593.59</v>
+      </c>
+      <c r="H686" t="n">
+        <v>3582.22</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="n">
+        <v>46324.27083333334</v>
+      </c>
+      <c r="B687" t="n">
+        <v>2276.34</v>
+      </c>
+      <c r="C687" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="D687" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E687" t="n">
+        <v>1109.87</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0</v>
+      </c>
+      <c r="G687" t="n">
+        <v>3401.35</v>
+      </c>
+      <c r="H687" t="n">
+        <v>3401.35</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="n">
+        <v>46324.29166666666</v>
+      </c>
+      <c r="B688" t="n">
+        <v>2255.11</v>
+      </c>
+      <c r="C688" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D688" t="n">
+        <v>0</v>
+      </c>
+      <c r="E688" t="n">
+        <v>1100.44</v>
+      </c>
+      <c r="F688" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G688" t="n">
+        <v>3371.48</v>
+      </c>
+      <c r="H688" t="n">
+        <v>3368.75</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="n">
+        <v>46324.3125</v>
+      </c>
+      <c r="B689" t="n">
+        <v>2356.61</v>
+      </c>
+      <c r="C689" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="D689" t="n">
+        <v>0</v>
+      </c>
+      <c r="E689" t="n">
+        <v>1138.9</v>
+      </c>
+      <c r="F689" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="G689" t="n">
+        <v>3513.76</v>
+      </c>
+      <c r="H689" t="n">
+        <v>3509.03</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="n">
+        <v>46324.33333333334</v>
+      </c>
+      <c r="B690" t="n">
+        <v>2476.77</v>
+      </c>
+      <c r="C690" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="D690" t="n">
+        <v>0</v>
+      </c>
+      <c r="E690" t="n">
+        <v>1149.15</v>
+      </c>
+      <c r="F690" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="G690" t="n">
+        <v>3642.75</v>
+      </c>
+      <c r="H690" t="n">
+        <v>3639.36</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="n">
+        <v>46324.35416666666</v>
+      </c>
+      <c r="B691" t="n">
+        <v>2604.05</v>
+      </c>
+      <c r="C691" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="D691" t="n">
+        <v>0</v>
+      </c>
+      <c r="E691" t="n">
+        <v>1155.99</v>
+      </c>
+      <c r="F691" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="G691" t="n">
+        <v>3804.1</v>
+      </c>
+      <c r="H691" t="n">
+        <v>3775.08</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="n">
+        <v>46324.375</v>
+      </c>
+      <c r="B692" t="n">
+        <v>2720.76</v>
+      </c>
+      <c r="C692" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="D692" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="E692" t="n">
+        <v>1147.93</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0</v>
+      </c>
+      <c r="G692" t="n">
+        <v>3903.55</v>
+      </c>
+      <c r="H692" t="n">
+        <v>3903.55</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="n">
+        <v>46324.39583333334</v>
+      </c>
+      <c r="B693" t="n">
+        <v>2934.11</v>
+      </c>
+      <c r="C693" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D693" t="n">
+        <v>0</v>
+      </c>
+      <c r="E693" t="n">
+        <v>1133.59</v>
+      </c>
+      <c r="F693" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="G693" t="n">
+        <v>4087.88</v>
+      </c>
+      <c r="H693" t="n">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="n">
+        <v>46324.41666666666</v>
+      </c>
+      <c r="B694" t="n">
+        <v>3032.34</v>
+      </c>
+      <c r="C694" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="D694" t="n">
+        <v>0</v>
+      </c>
+      <c r="E694" t="n">
+        <v>1118.02</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0</v>
+      </c>
+      <c r="G694" t="n">
+        <v>4156.700000000001</v>
+      </c>
+      <c r="H694" t="n">
+        <v>4156.700000000001</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="n">
+        <v>46324.4375</v>
+      </c>
+      <c r="B695" t="n">
+        <v>3092.53</v>
+      </c>
+      <c r="C695" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="D695" t="n">
+        <v>0</v>
+      </c>
+      <c r="E695" t="n">
+        <v>1118.59</v>
+      </c>
+      <c r="F695" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="G695" t="n">
+        <v>4220.66</v>
+      </c>
+      <c r="H695" t="n">
+        <v>4216.03</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="n">
+        <v>46324.45833333334</v>
+      </c>
+      <c r="B696" t="n">
+        <v>3097.68</v>
+      </c>
+      <c r="C696" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="D696" t="n">
+        <v>0</v>
+      </c>
+      <c r="E696" t="n">
+        <v>1171.44</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0</v>
+      </c>
+      <c r="G696" t="n">
+        <v>4300.74</v>
+      </c>
+      <c r="H696" t="n">
+        <v>4300.74</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>46324.47916666666</v>
+      </c>
+      <c r="B697" t="n">
+        <v>3178.8</v>
+      </c>
+      <c r="C697" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="D697" t="n">
+        <v>0</v>
+      </c>
+      <c r="E697" t="n">
+        <v>1162.14</v>
+      </c>
+      <c r="F697" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="G697" t="n">
+        <v>4386.68</v>
+      </c>
+      <c r="H697" t="n">
+        <v>4383</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n">
+        <v>46324.5</v>
+      </c>
+      <c r="B698" t="n">
+        <v>3188.92</v>
+      </c>
+      <c r="C698" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="D698" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E698" t="n">
+        <v>1164.92</v>
+      </c>
+      <c r="F698" t="n">
+        <v>0</v>
+      </c>
+      <c r="G698" t="n">
+        <v>4404.200000000001</v>
+      </c>
+      <c r="H698" t="n">
+        <v>4404.200000000001</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n">
+        <v>46324.52083333334</v>
+      </c>
+      <c r="B699" t="n">
+        <v>3220.53</v>
+      </c>
+      <c r="C699" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="D699" t="n">
+        <v>0</v>
+      </c>
+      <c r="E699" t="n">
+        <v>1167.85</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0</v>
+      </c>
+      <c r="G699" t="n">
+        <v>4422.3</v>
+      </c>
+      <c r="H699" t="n">
+        <v>4422.3</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>46324.54166666666</v>
+      </c>
+      <c r="B700" t="n">
+        <v>3237.16</v>
+      </c>
+      <c r="C700" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="D700" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="E700" t="n">
+        <v>1170.29</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0</v>
+      </c>
+      <c r="G700" t="n">
+        <v>4449.95</v>
+      </c>
+      <c r="H700" t="n">
+        <v>4449.95</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="B701" t="n">
+        <v>3292.11</v>
+      </c>
+      <c r="C701" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="D701" t="n">
+        <v>0</v>
+      </c>
+      <c r="E701" t="n">
+        <v>1173.09</v>
+      </c>
+      <c r="F701" t="n">
+        <v>0</v>
+      </c>
+      <c r="G701" t="n">
+        <v>4499.98</v>
+      </c>
+      <c r="H701" t="n">
+        <v>4499.98</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>46324.58333333334</v>
+      </c>
+      <c r="B702" t="n">
+        <v>3375.21</v>
+      </c>
+      <c r="C702" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="D702" t="n">
+        <v>0</v>
+      </c>
+      <c r="E702" t="n">
+        <v>1173.07</v>
+      </c>
+      <c r="F702" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="G702" t="n">
+        <v>4580.889999999999</v>
+      </c>
+      <c r="H702" t="n">
+        <v>4570.32</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="n">
+        <v>46324.60416666666</v>
+      </c>
+      <c r="B703" t="n">
+        <v>3433.87</v>
+      </c>
+      <c r="C703" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="D703" t="n">
+        <v>0</v>
+      </c>
+      <c r="E703" t="n">
+        <v>1190.28</v>
+      </c>
+      <c r="F703" t="n">
+        <v>0</v>
+      </c>
+      <c r="G703" t="n">
+        <v>4642.42</v>
+      </c>
+      <c r="H703" t="n">
+        <v>4642.42</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="n">
+        <v>46324.625</v>
+      </c>
+      <c r="B704" t="n">
+        <v>3403.47</v>
+      </c>
+      <c r="C704" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="D704" t="n">
+        <v>0</v>
+      </c>
+      <c r="E704" t="n">
+        <v>1199.06</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0</v>
+      </c>
+      <c r="G704" t="n">
+        <v>4621.12</v>
+      </c>
+      <c r="H704" t="n">
+        <v>4621.12</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="n">
+        <v>46324.64583333334</v>
+      </c>
+      <c r="B705" t="n">
+        <v>3406.68</v>
+      </c>
+      <c r="C705" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="D705" t="n">
+        <v>0</v>
+      </c>
+      <c r="E705" t="n">
+        <v>1196.03</v>
+      </c>
+      <c r="F705" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G705" t="n">
+        <v>4638.89</v>
+      </c>
+      <c r="H705" t="n">
+        <v>4631.72</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="n">
+        <v>46324.66666666666</v>
+      </c>
+      <c r="B706" t="n">
+        <v>3333.79</v>
+      </c>
+      <c r="C706" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="D706" t="n">
+        <v>0</v>
+      </c>
+      <c r="E706" t="n">
+        <v>1207.02</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0</v>
+      </c>
+      <c r="G706" t="n">
+        <v>4572.110000000001</v>
+      </c>
+      <c r="H706" t="n">
+        <v>4572.110000000001</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="n">
+        <v>46324.6875</v>
+      </c>
+      <c r="B707" t="n">
+        <v>3309.5</v>
+      </c>
+      <c r="C707" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="D707" t="n">
+        <v>0</v>
+      </c>
+      <c r="E707" t="n">
+        <v>1211.91</v>
+      </c>
+      <c r="F707" t="n">
+        <v>0</v>
+      </c>
+      <c r="G707" t="n">
+        <v>4562.59</v>
+      </c>
+      <c r="H707" t="n">
+        <v>4562.59</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="n">
+        <v>46324.70833333334</v>
+      </c>
+      <c r="B708" t="n">
+        <v>3203.85</v>
+      </c>
+      <c r="C708" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="D708" t="n">
+        <v>0</v>
+      </c>
+      <c r="E708" t="n">
+        <v>1222.78</v>
+      </c>
+      <c r="F708" t="n">
+        <v>0</v>
+      </c>
+      <c r="G708" t="n">
+        <v>4466.309999999999</v>
+      </c>
+      <c r="H708" t="n">
+        <v>4466.309999999999</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="n">
+        <v>46324.72916666666</v>
+      </c>
+      <c r="B709" t="n">
+        <v>3128.58</v>
+      </c>
+      <c r="C709" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="D709" t="n">
+        <v>0</v>
+      </c>
+      <c r="E709" t="n">
+        <v>1209.46</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0</v>
+      </c>
+      <c r="G709" t="n">
+        <v>4380.719999999999</v>
+      </c>
+      <c r="H709" t="n">
+        <v>4380.719999999999</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="n">
+        <v>46324.75</v>
+      </c>
+      <c r="B710" t="n">
+        <v>3247.64</v>
+      </c>
+      <c r="C710" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="D710" t="n">
+        <v>0</v>
+      </c>
+      <c r="E710" t="n">
+        <v>1220.62</v>
+      </c>
+      <c r="F710" t="n">
+        <v>0</v>
+      </c>
+      <c r="G710" t="n">
+        <v>4517.19</v>
+      </c>
+      <c r="H710" t="n">
+        <v>4517.19</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="n">
+        <v>46324.77083333334</v>
+      </c>
+      <c r="B711" t="n">
+        <v>3433.87</v>
+      </c>
+      <c r="C711" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="D711" t="n">
+        <v>0</v>
+      </c>
+      <c r="E711" t="n">
+        <v>1244.11</v>
+      </c>
+      <c r="F711" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G711" t="n">
+        <v>4725.32</v>
+      </c>
+      <c r="H711" t="n">
+        <v>4723.34</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="n">
+        <v>46324.79166666666</v>
+      </c>
+      <c r="B712" t="n">
+        <v>3518.82</v>
+      </c>
+      <c r="C712" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="D712" t="n">
+        <v>0</v>
+      </c>
+      <c r="E712" t="n">
+        <v>1257.85</v>
+      </c>
+      <c r="F712" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="G712" t="n">
+        <v>4822.61</v>
+      </c>
+      <c r="H712" t="n">
+        <v>4810.58</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="n">
+        <v>46324.8125</v>
+      </c>
+      <c r="B713" t="n">
+        <v>3585.98</v>
+      </c>
+      <c r="C713" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="D713" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="E713" t="n">
+        <v>1189.14</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0</v>
+      </c>
+      <c r="G713" t="n">
+        <v>4804.95</v>
+      </c>
+      <c r="H713" t="n">
+        <v>4804.95</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="n">
+        <v>46324.83333333334</v>
+      </c>
+      <c r="B714" t="n">
+        <v>3570.1</v>
+      </c>
+      <c r="C714" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="D714" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E714" t="n">
+        <v>1199.5</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0</v>
+      </c>
+      <c r="G714" t="n">
+        <v>4795.17</v>
+      </c>
+      <c r="H714" t="n">
+        <v>4795.17</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="n">
+        <v>46324.85416666666</v>
+      </c>
+      <c r="B715" t="n">
+        <v>3607.62</v>
+      </c>
+      <c r="C715" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="D715" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="E715" t="n">
+        <v>1203.67</v>
+      </c>
+      <c r="F715" t="n">
+        <v>0</v>
+      </c>
+      <c r="G715" t="n">
+        <v>4839.88</v>
+      </c>
+      <c r="H715" t="n">
+        <v>4839.88</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="n">
+        <v>46324.875</v>
+      </c>
+      <c r="B716" t="n">
+        <v>3559.76</v>
+      </c>
+      <c r="C716" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="D716" t="n">
+        <v>0</v>
+      </c>
+      <c r="E716" t="n">
+        <v>1199.22</v>
+      </c>
+      <c r="F716" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="G716" t="n">
+        <v>4783.969999999999</v>
+      </c>
+      <c r="H716" t="n">
+        <v>4767.53</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="n">
+        <v>46324.89583333334</v>
+      </c>
+      <c r="B717" t="n">
+        <v>3491.96</v>
+      </c>
+      <c r="C717" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D717" t="n">
+        <v>0</v>
+      </c>
+      <c r="E717" t="n">
+        <v>1200.58</v>
+      </c>
+      <c r="F717" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="G717" t="n">
+        <v>4719.25</v>
+      </c>
+      <c r="H717" t="n">
+        <v>4699.34</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="n">
+        <v>46324.91666666666</v>
+      </c>
+      <c r="B718" t="n">
+        <v>3361.6</v>
+      </c>
+      <c r="C718" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="D718" t="n">
+        <v>0</v>
+      </c>
+      <c r="E718" t="n">
+        <v>1202.59</v>
+      </c>
+      <c r="F718" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="G718" t="n">
+        <v>4577.259999999999</v>
+      </c>
+      <c r="H718" t="n">
+        <v>4570.53</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n">
+        <v>46324.9375</v>
+      </c>
+      <c r="B719" t="n">
+        <v>3247.05</v>
+      </c>
+      <c r="C719" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="D719" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E719" t="n">
+        <v>1201.82</v>
+      </c>
+      <c r="F719" t="n">
+        <v>0</v>
+      </c>
+      <c r="G719" t="n">
+        <v>4458.28</v>
+      </c>
+      <c r="H719" t="n">
+        <v>4458.28</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="n">
+        <v>46324.95833333334</v>
+      </c>
+      <c r="B720" t="n">
+        <v>3103.4</v>
+      </c>
+      <c r="C720" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="D720" t="n">
+        <v>0</v>
+      </c>
+      <c r="E720" t="n">
+        <v>1204.07</v>
+      </c>
+      <c r="F720" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="G720" t="n">
+        <v>4332.21</v>
+      </c>
+      <c r="H720" t="n">
+        <v>4318.7</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="n">
+        <v>46324.97916666666</v>
+      </c>
+      <c r="B721" t="n">
+        <v>2984.16</v>
+      </c>
+      <c r="C721" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="D721" t="n">
+        <v>0</v>
+      </c>
+      <c r="E721" t="n">
+        <v>1207.46</v>
+      </c>
+      <c r="F721" t="n">
+        <v>0</v>
+      </c>
+      <c r="G721" t="n">
+        <v>4199.38</v>
+      </c>
+      <c r="H721" t="n">
+        <v>4199.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
